--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -5352,7 +5352,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>2000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -5364,7 +5364,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2000</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -16849,7 +16849,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16872,7 +16872,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -17746,22 +17746,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17769,22 +17769,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D646" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E646" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -19333,22 +19333,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D714" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E714" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19356,22 +19356,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -19333,22 +19333,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D714" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E714" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19356,22 +19356,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17746,22 +17746,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17769,22 +17769,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D646" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E646" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16849,7 +16849,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16872,7 +16872,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -19333,22 +19333,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D714" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E714" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19356,22 +19356,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17746,22 +17746,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17769,22 +17769,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D646" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E646" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -18114,13 +18114,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18129,7 +18129,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18137,13 +18137,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18152,7 +18152,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -19333,22 +19333,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D714" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E714" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19356,22 +19356,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17746,22 +17746,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17769,22 +17769,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D646" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E646" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16849,7 +16849,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16872,7 +16872,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -18114,13 +18114,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18129,7 +18129,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18137,13 +18137,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18152,7 +18152,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -9018,10 +9018,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F265" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G265" s="1">
-        <x:v>150000</x:v>
+        <x:v>157000</x:v>
       </x:c>
     </x:row>
     <x:row r="266" spans="1:7">
@@ -9075,13 +9075,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C268" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D268" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E268" s="1">
         <x:v>0</x:v>
@@ -9090,7 +9090,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="269" spans="1:7">
@@ -9098,13 +9098,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B269" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C269" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D269" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E269" s="1">
         <x:v>0</x:v>
@@ -9113,7 +9113,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G269" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="270" spans="1:7">
@@ -16849,7 +16849,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16872,7 +16872,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -9075,13 +9075,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C268" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D268" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E268" s="1">
         <x:v>0</x:v>
@@ -9090,7 +9090,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="269" spans="1:7">
@@ -9098,13 +9098,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B269" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C269" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D269" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E269" s="1">
         <x:v>0</x:v>
@@ -9113,7 +9113,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G269" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="270" spans="1:7">
@@ -18114,13 +18114,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18129,7 +18129,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18137,13 +18137,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18152,7 +18152,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -18114,13 +18114,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18129,7 +18129,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18137,13 +18137,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18152,7 +18152,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -307,10 +307,10 @@
     <x:t>BOOKER, CORY A.</x:t>
   </x:si>
   <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
     <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
   </x:si>
   <x:si>
     <x:t>BOOZMAN, SEN. JOHN</x:t>
@@ -4248,7 +4248,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C58" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>0</x:v>
@@ -4257,10 +4257,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>2800</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G58" s="1">
-        <x:v>2800</x:v>
+        <x:v>18250</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
@@ -4271,7 +4271,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C59" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>0</x:v>
@@ -4280,10 +4280,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>18200</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G59" s="1">
-        <x:v>18250</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
@@ -4935,7 +4935,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C88" s="1">
         <x:v>0</x:v>
@@ -5878,7 +5878,7 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C129" s="1">
         <x:v>0</x:v>
@@ -5993,7 +5993,7 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C134" s="1">
         <x:v>50</x:v>
@@ -6108,7 +6108,7 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C139" s="1">
         <x:v>0</x:v>
@@ -7189,7 +7189,7 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C186" s="1">
         <x:v>0</x:v>
@@ -9052,7 +9052,7 @@
         <x:v>320</x:v>
       </x:c>
       <x:c r="B267" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C267" s="1">
         <x:v>4550</x:v>
@@ -9558,7 +9558,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="B289" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C289" s="1">
         <x:v>0</x:v>
@@ -9696,7 +9696,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="B295" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C295" s="1">
         <x:v>0</x:v>
@@ -10478,7 +10478,7 @@
         <x:v>383</x:v>
       </x:c>
       <x:c r="B329" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C329" s="1">
         <x:v>0</x:v>
@@ -11168,7 +11168,7 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C359" s="1">
         <x:v>0</x:v>
@@ -11214,7 +11214,7 @@
         <x:v>416</x:v>
       </x:c>
       <x:c r="B361" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C361" s="1">
         <x:v>0</x:v>
@@ -11421,7 +11421,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B370" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C370" s="1">
         <x:v>0</x:v>
@@ -11467,7 +11467,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="B372" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C372" s="1">
         <x:v>0</x:v>
@@ -11559,7 +11559,7 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B376" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C376" s="1">
         <x:v>50</x:v>
@@ -12870,7 +12870,7 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="B433" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C433" s="1">
         <x:v>50</x:v>
@@ -13238,7 +13238,7 @@
         <x:v>505</x:v>
       </x:c>
       <x:c r="B449" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C449" s="1">
         <x:v>0</x:v>
@@ -13813,7 +13813,7 @@
         <x:v>530</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C474" s="1">
         <x:v>1550</x:v>
@@ -14917,7 +14917,7 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C522" s="1">
         <x:v>50</x:v>
@@ -15078,7 +15078,7 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C529" s="1">
         <x:v>0</x:v>
@@ -15147,7 +15147,7 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C532" s="1">
         <x:v>0</x:v>
@@ -15331,7 +15331,7 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C540" s="1">
         <x:v>50</x:v>
@@ -15400,7 +15400,7 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C543" s="1">
         <x:v>50</x:v>
@@ -15492,7 +15492,7 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C547" s="1">
         <x:v>50</x:v>
@@ -15653,7 +15653,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C554" s="1">
         <x:v>0</x:v>
@@ -16021,7 +16021,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>1000</x:v>
@@ -16113,7 +16113,7 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C574" s="1">
         <x:v>0</x:v>
@@ -16665,7 +16665,7 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>0</x:v>
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -18022,7 +18022,7 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C657" s="1">
         <x:v>1050</x:v>
@@ -18160,7 +18160,7 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C663" s="1">
         <x:v>50</x:v>
@@ -18229,7 +18229,7 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C666" s="1">
         <x:v>50</x:v>
@@ -18689,7 +18689,7 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>0</x:v>
@@ -19609,7 +19609,7 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C726" s="1">
         <x:v>0</x:v>
@@ -19701,7 +19701,7 @@
         <x:v>785</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C730" s="1">
         <x:v>0</x:v>
@@ -19885,7 +19885,7 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C738" s="1">
         <x:v>50</x:v>
@@ -20368,7 +20368,7 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C759" s="1">
         <x:v>0</x:v>
@@ -20920,7 +20920,7 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C783" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -307,10 +307,10 @@
     <x:t>BOOKER, CORY A.</x:t>
   </x:si>
   <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
     <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
   </x:si>
   <x:si>
     <x:t>BOOZMAN, SEN. JOHN</x:t>
@@ -4248,7 +4248,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C58" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>0</x:v>
@@ -4257,10 +4257,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>18200</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G58" s="1">
-        <x:v>18250</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
@@ -4271,7 +4271,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C59" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>0</x:v>
@@ -4280,10 +4280,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>2800</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G59" s="1">
-        <x:v>2800</x:v>
+        <x:v>18250</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
@@ -4935,7 +4935,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C88" s="1">
         <x:v>0</x:v>
@@ -5878,7 +5878,7 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C129" s="1">
         <x:v>0</x:v>
@@ -5993,7 +5993,7 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C134" s="1">
         <x:v>50</x:v>
@@ -6108,7 +6108,7 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C139" s="1">
         <x:v>0</x:v>
@@ -7189,7 +7189,7 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C186" s="1">
         <x:v>0</x:v>
@@ -9052,7 +9052,7 @@
         <x:v>320</x:v>
       </x:c>
       <x:c r="B267" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C267" s="1">
         <x:v>4550</x:v>
@@ -9558,7 +9558,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="B289" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C289" s="1">
         <x:v>0</x:v>
@@ -9696,7 +9696,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="B295" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C295" s="1">
         <x:v>0</x:v>
@@ -10478,7 +10478,7 @@
         <x:v>383</x:v>
       </x:c>
       <x:c r="B329" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C329" s="1">
         <x:v>0</x:v>
@@ -11168,7 +11168,7 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C359" s="1">
         <x:v>0</x:v>
@@ -11214,7 +11214,7 @@
         <x:v>416</x:v>
       </x:c>
       <x:c r="B361" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C361" s="1">
         <x:v>0</x:v>
@@ -11421,7 +11421,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B370" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C370" s="1">
         <x:v>0</x:v>
@@ -11467,7 +11467,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="B372" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C372" s="1">
         <x:v>0</x:v>
@@ -11559,7 +11559,7 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B376" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C376" s="1">
         <x:v>50</x:v>
@@ -12870,7 +12870,7 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="B433" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C433" s="1">
         <x:v>50</x:v>
@@ -13238,7 +13238,7 @@
         <x:v>505</x:v>
       </x:c>
       <x:c r="B449" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C449" s="1">
         <x:v>0</x:v>
@@ -13813,7 +13813,7 @@
         <x:v>530</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C474" s="1">
         <x:v>1550</x:v>
@@ -14917,7 +14917,7 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C522" s="1">
         <x:v>50</x:v>
@@ -15078,7 +15078,7 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C529" s="1">
         <x:v>0</x:v>
@@ -15147,7 +15147,7 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C532" s="1">
         <x:v>0</x:v>
@@ -15331,7 +15331,7 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C540" s="1">
         <x:v>50</x:v>
@@ -15400,7 +15400,7 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C543" s="1">
         <x:v>50</x:v>
@@ -15492,7 +15492,7 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C547" s="1">
         <x:v>50</x:v>
@@ -15653,7 +15653,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C554" s="1">
         <x:v>0</x:v>
@@ -16021,7 +16021,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>1000</x:v>
@@ -16113,7 +16113,7 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C574" s="1">
         <x:v>0</x:v>
@@ -16665,7 +16665,7 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>0</x:v>
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -18022,7 +18022,7 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C657" s="1">
         <x:v>1050</x:v>
@@ -18160,7 +18160,7 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C663" s="1">
         <x:v>50</x:v>
@@ -18229,7 +18229,7 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C666" s="1">
         <x:v>50</x:v>
@@ -18689,7 +18689,7 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>0</x:v>
@@ -19609,7 +19609,7 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C726" s="1">
         <x:v>0</x:v>
@@ -19701,7 +19701,7 @@
         <x:v>785</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C730" s="1">
         <x:v>0</x:v>
@@ -19885,7 +19885,7 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C738" s="1">
         <x:v>50</x:v>
@@ -20368,7 +20368,7 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C759" s="1">
         <x:v>0</x:v>
@@ -20920,7 +20920,7 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C783" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16849,7 +16849,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16872,7 +16872,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3791,7 +3791,7 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>1016284</x:v>
+        <x:v>2008868</x:v>
       </x:c>
       <x:c r="E38" s="1">
         <x:v>0</x:v>
@@ -3800,7 +3800,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G38" s="1">
-        <x:v>1018784</x:v>
+        <x:v>2011368</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -5217,7 +5217,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D100" s="1">
-        <x:v>547042</x:v>
+        <x:v>1058984</x:v>
       </x:c>
       <x:c r="E100" s="1">
         <x:v>0</x:v>
@@ -5226,7 +5226,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G100" s="1">
-        <x:v>547042</x:v>
+        <x:v>1058984</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
@@ -10438,7 +10438,7 @@
         <x:v>12850</x:v>
       </x:c>
       <x:c r="D327" s="1">
-        <x:v>1858047</x:v>
+        <x:v>3394035</x:v>
       </x:c>
       <x:c r="E327" s="1">
         <x:v>0</x:v>
@@ -10447,7 +10447,7 @@
         <x:v>35533</x:v>
       </x:c>
       <x:c r="G327" s="1">
-        <x:v>1906430</x:v>
+        <x:v>3442418</x:v>
       </x:c>
     </x:row>
     <x:row r="328" spans="1:7">
@@ -12436,7 +12436,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="C414" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D414" s="1">
         <x:v>700000</x:v>
@@ -12448,7 +12448,7 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="G414" s="1">
-        <x:v>712000</x:v>
+        <x:v>714500</x:v>
       </x:c>
     </x:row>
     <x:row r="415" spans="1:7">
@@ -13612,7 +13612,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D465" s="1">
-        <x:v>506917</x:v>
+        <x:v>1013834</x:v>
       </x:c>
       <x:c r="E465" s="1">
         <x:v>0</x:v>
@@ -13621,7 +13621,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G465" s="1">
-        <x:v>506917</x:v>
+        <x:v>1013834</x:v>
       </x:c>
     </x:row>
     <x:row r="466" spans="1:7">
@@ -16648,7 +16648,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D597" s="1">
-        <x:v>275541</x:v>
+        <x:v>2707641</x:v>
       </x:c>
       <x:c r="E597" s="1">
         <x:v>0</x:v>
@@ -16657,7 +16657,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G597" s="1">
-        <x:v>275541</x:v>
+        <x:v>2707641</x:v>
       </x:c>
     </x:row>
     <x:row r="598" spans="1:7">
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -18669,7 +18669,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>25550</x:v>
+        <x:v>28050</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>764206</x:v>
@@ -18681,7 +18681,7 @@
         <x:v>20501</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>810257</x:v>
+        <x:v>812757</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -18810,7 +18810,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D691" s="1">
-        <x:v>619349</x:v>
+        <x:v>1131345</x:v>
       </x:c>
       <x:c r="E691" s="1">
         <x:v>0</x:v>
@@ -18819,7 +18819,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>619399</x:v>
+        <x:v>1131395</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -19132,7 +19132,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>2772295</x:v>
+        <x:v>2771797</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
@@ -19141,7 +19141,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>2772295</x:v>
+        <x:v>2771797</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -20305,7 +20305,7 @@
         <x:v>19050</x:v>
       </x:c>
       <x:c r="D756" s="1">
-        <x:v>1350000</x:v>
+        <x:v>2700000</x:v>
       </x:c>
       <x:c r="E756" s="1">
         <x:v>0</x:v>
@@ -20314,7 +20314,7 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>1371550</x:v>
+        <x:v>2721550</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16849,7 +16849,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16872,7 +16872,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -17746,22 +17746,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17769,22 +17769,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D646" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E646" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -19333,22 +19333,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D714" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E714" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19356,22 +19356,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16849,7 +16849,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16872,7 +16872,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17746,22 +17746,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17769,22 +17769,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D646" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E646" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -18114,13 +18114,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18129,7 +18129,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18137,13 +18137,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18152,7 +18152,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -2613,8 +2613,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G788" totalsRowShown="0">
-  <x:autoFilter ref="A1:G788"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G790" totalsRowShown="0">
+  <x:autoFilter ref="A1:G790"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2916,7 +2916,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G788"/>
+  <x:dimension ref="A1:G790"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4622,7 +4622,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E74" s="1">
-        <x:v>0</x:v>
+        <x:v>34386390</x:v>
       </x:c>
       <x:c r="F74" s="1">
         <x:v>26600</x:v>
@@ -5427,7 +5427,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E109" s="1">
-        <x:v>0</x:v>
+        <x:v>5731065</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>0</x:v>
@@ -10530,7 +10530,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D331" s="1">
-        <x:v>0</x:v>
+        <x:v>11461082</x:v>
       </x:c>
       <x:c r="E331" s="1">
         <x:v>0</x:v>
@@ -10539,7 +10539,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G331" s="1">
-        <x:v>26000</x:v>
+        <x:v>11487082</x:v>
       </x:c>
     </x:row>
     <x:row r="332" spans="1:7">
@@ -18114,13 +18114,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18129,7 +18129,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18137,13 +18137,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18152,7 +18152,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18548,10 +18548,10 @@
     </x:row>
     <x:row r="680" spans="1:7">
       <x:c r="A680" s="1" t="s">
-        <x:v>736</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C680" s="1">
         <x:v>0</x:v>
@@ -18560,7 +18560,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E680" s="1">
-        <x:v>1531015</x:v>
+        <x:v>5731065</x:v>
       </x:c>
       <x:c r="F680" s="1">
         <x:v>0</x:v>
@@ -18571,62 +18571,62 @@
     </x:row>
     <x:row r="681" spans="1:7">
       <x:c r="A681" s="1" t="s">
-        <x:v>737</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D681" s="1">
-        <x:v>157560</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E681" s="1">
-        <x:v>0</x:v>
+        <x:v>5731065</x:v>
       </x:c>
       <x:c r="F681" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>157610</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
       <x:c r="A682" s="1" t="s">
-        <x:v>738</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E682" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F682" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
       <x:c r="A683" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D683" s="1">
-        <x:v>5583432</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="E683" s="1">
         <x:v>0</x:v>
@@ -18635,15 +18635,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>5584432</x:v>
+        <x:v>157610</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
       <x:c r="A684" s="1" t="s">
-        <x:v>740</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C684" s="1">
         <x:v>50</x:v>
@@ -18663,36 +18663,36 @@
     </x:row>
     <x:row r="685" spans="1:7">
       <x:c r="A685" s="1" t="s">
-        <x:v>741</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>28050</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D685" s="1">
-        <x:v>764206</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E685" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>20501</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>812757</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
       <x:c r="A686" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -18701,44 +18701,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
       <x:c r="A687" s="1" t="s">
-        <x:v>743</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>0</x:v>
+        <x:v>28050</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E687" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F687" s="1">
-        <x:v>0</x:v>
+        <x:v>20501</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>1543316</x:v>
+        <x:v>812757</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
       <x:c r="A688" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D688" s="1">
         <x:v>0</x:v>
@@ -18747,24 +18747,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F688" s="1">
-        <x:v>14500</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>14550</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
       <x:c r="A689" s="1" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C689" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D689" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E689" s="1">
         <x:v>0</x:v>
@@ -18773,15 +18773,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G689" s="1">
-        <x:v>50</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:7">
       <x:c r="A690" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C690" s="1">
         <x:v>50</x:v>
@@ -18793,24 +18793,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
       <x:c r="A691" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C691" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D691" s="1">
-        <x:v>1131345</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E691" s="1">
         <x:v>0</x:v>
@@ -18819,110 +18819,110 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>1131395</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
       <x:c r="A692" s="1" t="s">
-        <x:v>748</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E692" s="1">
-        <x:v>10135449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
       <x:c r="A693" s="1" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C693" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D693" s="1">
-        <x:v>103020</x:v>
+        <x:v>1131345</x:v>
       </x:c>
       <x:c r="E693" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F693" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>106354</x:v>
+        <x:v>1131395</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
       <x:c r="A694" s="1" t="s">
-        <x:v>750</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C694" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D694" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E694" s="1">
-        <x:v>0</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="F694" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
       <x:c r="A695" s="1" t="s">
-        <x:v>751</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C695" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D695" s="1">
-        <x:v>106947</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="E695" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F695" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>106947</x:v>
+        <x:v>106354</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
       <x:c r="A696" s="1" t="s">
-        <x:v>752</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>2050</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D696" s="1">
         <x:v>0</x:v>
@@ -18931,44 +18931,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>27050</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
       <x:c r="A697" s="1" t="s">
-        <x:v>753</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>1050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D697" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E697" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>910226</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
       <x:c r="A698" s="1" t="s">
-        <x:v>754</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C698" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D698" s="1">
         <x:v>0</x:v>
@@ -18977,44 +18977,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F698" s="1">
-        <x:v>25500</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>25550</x:v>
+        <x:v>27050</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
       <x:c r="A699" s="1" t="s">
-        <x:v>755</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C699" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D699" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E699" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F699" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>50</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
       <x:c r="A700" s="1" t="s">
-        <x:v>756</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C700" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D700" s="1">
         <x:v>0</x:v>
@@ -19023,21 +19023,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F700" s="1">
-        <x:v>14000</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>14000</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
       <x:c r="A701" s="1" t="s">
-        <x:v>757</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D701" s="1">
         <x:v>0</x:v>
@@ -19046,21 +19046,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>6200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
       <x:c r="A702" s="1" t="s">
-        <x:v>758</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C702" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D702" s="1">
         <x:v>0</x:v>
@@ -19069,21 +19069,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
       <x:c r="A703" s="1" t="s">
-        <x:v>759</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C703" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D703" s="1">
         <x:v>0</x:v>
@@ -19092,18 +19092,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F703" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>1000</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
       <x:c r="A704" s="1" t="s">
-        <x:v>760</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C704" s="1">
         <x:v>50</x:v>
@@ -19115,24 +19115,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>6650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
       <x:c r="A705" s="1" t="s">
-        <x:v>761</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>2771797</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
@@ -19141,18 +19141,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>2771797</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
       <x:c r="A706" s="1" t="s">
-        <x:v>762</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D706" s="1">
         <x:v>0</x:v>
@@ -19161,24 +19161,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>5000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>5000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
       <x:c r="A707" s="1" t="s">
-        <x:v>763</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D707" s="1">
-        <x:v>0</x:v>
+        <x:v>2771797</x:v>
       </x:c>
       <x:c r="E707" s="1">
         <x:v>0</x:v>
@@ -19187,18 +19187,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>50</x:v>
+        <x:v>2771797</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
       <x:c r="A708" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>6550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D708" s="1">
         <x:v>0</x:v>
@@ -19207,18 +19207,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>3300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>9850</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
       <x:c r="A709" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C709" s="1">
         <x:v>50</x:v>
@@ -19238,13 +19238,13 @@
     </x:row>
     <x:row r="710" spans="1:7">
       <x:c r="A710" s="1" t="s">
-        <x:v>766</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C710" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D710" s="1">
         <x:v>0</x:v>
@@ -19253,21 +19253,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>50</x:v>
+        <x:v>9850</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
       <x:c r="A711" s="1" t="s">
-        <x:v>767</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C711" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D711" s="1">
         <x:v>0</x:v>
@@ -19276,21 +19276,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
       <x:c r="A712" s="1" t="s">
-        <x:v>768</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
@@ -19299,21 +19299,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
       <x:c r="A713" s="1" t="s">
-        <x:v>769</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19322,21 +19322,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>50</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
       <x:c r="A714" s="1" t="s">
-        <x:v>770</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D714" s="1">
         <x:v>0</x:v>
@@ -19345,24 +19345,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>5800</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>9350</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
       <x:c r="A715" s="1" t="s">
-        <x:v>770</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
@@ -19371,44 +19371,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>1100000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
       <x:c r="A716" s="1" t="s">
-        <x:v>771</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D716" s="1">
-        <x:v>2835078</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E716" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>5500</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>2840628</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
       <x:c r="A717" s="1" t="s">
-        <x:v>772</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D717" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E717" s="1">
         <x:v>0</x:v>
@@ -19417,38 +19417,38 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>50</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
       <x:c r="A718" s="1" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C718" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D718" s="1">
-        <x:v>0</x:v>
+        <x:v>2835078</x:v>
       </x:c>
       <x:c r="E718" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F718" s="1">
-        <x:v>5750</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>5800</x:v>
+        <x:v>2840628</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
       <x:c r="A719" s="1" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C719" s="1">
         <x:v>50</x:v>
@@ -19468,13 +19468,13 @@
     </x:row>
     <x:row r="720" spans="1:7">
       <x:c r="A720" s="1" t="s">
-        <x:v>775</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D720" s="1">
         <x:v>0</x:v>
@@ -19483,18 +19483,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>3300</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>3300</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
       <x:c r="A721" s="1" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C721" s="1">
         <x:v>50</x:v>
@@ -19514,13 +19514,13 @@
     </x:row>
     <x:row r="722" spans="1:7">
       <x:c r="A722" s="1" t="s">
-        <x:v>777</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D722" s="1">
         <x:v>0</x:v>
@@ -19529,18 +19529,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F722" s="1">
-        <x:v>5700</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>5750</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
       <x:c r="A723" s="1" t="s">
-        <x:v>778</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C723" s="1">
         <x:v>50</x:v>
@@ -19560,10 +19560,10 @@
     </x:row>
     <x:row r="724" spans="1:7">
       <x:c r="A724" s="1" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C724" s="1">
         <x:v>50</x:v>
@@ -19575,44 +19575,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>0</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
       <x:c r="A725" s="1" t="s">
-        <x:v>780</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D725" s="1">
-        <x:v>2192272</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E725" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F725" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>2209772</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
       <x:c r="A726" s="1" t="s">
-        <x:v>781</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D726" s="1">
         <x:v>0</x:v>
@@ -19621,44 +19621,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
       <x:c r="A727" s="1" t="s">
-        <x:v>782</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D727" s="1">
-        <x:v>0</x:v>
+        <x:v>2192272</x:v>
       </x:c>
       <x:c r="E727" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F727" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>50</x:v>
+        <x:v>2209772</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
       <x:c r="A728" s="1" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C728" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D728" s="1">
         <x:v>0</x:v>
@@ -19667,18 +19667,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>11500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>13500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
       <x:c r="A729" s="1" t="s">
-        <x:v>784</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C729" s="1">
         <x:v>50</x:v>
@@ -19698,36 +19698,36 @@
     </x:row>
     <x:row r="730" spans="1:7">
       <x:c r="A730" s="1" t="s">
-        <x:v>785</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C730" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D730" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E730" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F730" s="1">
-        <x:v>0</x:v>
+        <x:v>11500</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>40000</x:v>
+        <x:v>13500</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
       <x:c r="A731" s="1" t="s">
-        <x:v>786</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C731" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D731" s="1">
         <x:v>0</x:v>
@@ -19739,21 +19739,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
       <x:c r="A732" s="1" t="s">
-        <x:v>787</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C732" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D732" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E732" s="1">
         <x:v>0</x:v>
@@ -19762,18 +19762,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>50</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
       <x:c r="A733" s="1" t="s">
-        <x:v>788</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C733" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D733" s="1">
         <x:v>0</x:v>
@@ -19782,18 +19782,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F733" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G733" s="1">
-        <x:v>5200</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:7">
       <x:c r="A734" s="1" t="s">
-        <x:v>789</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C734" s="1">
         <x:v>50</x:v>
@@ -19813,13 +19813,13 @@
     </x:row>
     <x:row r="735" spans="1:7">
       <x:c r="A735" s="1" t="s">
-        <x:v>790</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19828,18 +19828,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
       <x:c r="A736" s="1" t="s">
-        <x:v>791</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C736" s="1">
         <x:v>50</x:v>
@@ -19851,24 +19851,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
       <x:c r="A737" s="1" t="s">
-        <x:v>792</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C737" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D737" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E737" s="1">
         <x:v>0</x:v>
@@ -19877,15 +19877,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G737" s="1">
-        <x:v>3920589</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="738" spans="1:7">
       <x:c r="A738" s="1" t="s">
-        <x:v>793</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C738" s="1">
         <x:v>50</x:v>
@@ -19897,24 +19897,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F738" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
       <x:c r="A739" s="1" t="s">
-        <x:v>794</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C739" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D739" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E739" s="1">
         <x:v>0</x:v>
@@ -19923,15 +19923,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>1000</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
       <x:c r="A740" s="1" t="s">
-        <x:v>795</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C740" s="1">
         <x:v>50</x:v>
@@ -19951,13 +19951,13 @@
     </x:row>
     <x:row r="741" spans="1:7">
       <x:c r="A741" s="1" t="s">
-        <x:v>796</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C741" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D741" s="1">
         <x:v>0</x:v>
@@ -19969,18 +19969,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
       <x:c r="A742" s="1" t="s">
-        <x:v>797</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C742" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D742" s="1">
         <x:v>0</x:v>
@@ -19989,21 +19989,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F742" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>9334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
       <x:c r="A743" s="1" t="s">
-        <x:v>798</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C743" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D743" s="1">
         <x:v>0</x:v>
@@ -20015,18 +20015,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G743" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="744" spans="1:7">
       <x:c r="A744" s="1" t="s">
-        <x:v>799</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C744" s="1">
-        <x:v>50</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D744" s="1">
         <x:v>0</x:v>
@@ -20035,21 +20035,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F744" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>50</x:v>
+        <x:v>9334</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">
       <x:c r="A745" s="1" t="s">
-        <x:v>800</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C745" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D745" s="1">
         <x:v>0</x:v>
@@ -20061,21 +20061,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G745" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:7">
       <x:c r="A746" s="1" t="s">
-        <x:v>801</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D746" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E746" s="1">
         <x:v>0</x:v>
@@ -20084,15 +20084,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
       <x:c r="A747" s="1" t="s">
-        <x:v>802</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C747" s="1">
         <x:v>50</x:v>
@@ -20112,33 +20112,33 @@
     </x:row>
     <x:row r="748" spans="1:7">
       <x:c r="A748" s="1" t="s">
-        <x:v>803</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>19600</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D748" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E748" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F748" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>36600</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
       <x:c r="A749" s="1" t="s">
-        <x:v>804</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C749" s="1">
         <x:v>50</x:v>
@@ -20158,13 +20158,13 @@
     </x:row>
     <x:row r="750" spans="1:7">
       <x:c r="A750" s="1" t="s">
-        <x:v>805</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>50</x:v>
+        <x:v>19600</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20173,18 +20173,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>50</x:v>
+        <x:v>36600</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
       <x:c r="A751" s="1" t="s">
-        <x:v>806</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C751" s="1">
         <x:v>50</x:v>
@@ -20204,16 +20204,16 @@
     </x:row>
     <x:row r="752" spans="1:7">
       <x:c r="A752" s="1" t="s">
-        <x:v>807</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D752" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E752" s="1">
         <x:v>0</x:v>
@@ -20222,15 +20222,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
       <x:c r="A753" s="1" t="s">
-        <x:v>808</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C753" s="1">
         <x:v>50</x:v>
@@ -20250,33 +20250,33 @@
     </x:row>
     <x:row r="754" spans="1:7">
       <x:c r="A754" s="1" t="s">
-        <x:v>809</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C754" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D754" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E754" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F754" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>30000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
       <x:c r="A755" s="1" t="s">
-        <x:v>810</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C755" s="1">
         <x:v>50</x:v>
@@ -20296,36 +20296,36 @@
     </x:row>
     <x:row r="756" spans="1:7">
       <x:c r="A756" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>19050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D756" s="1">
-        <x:v>2700000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E756" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F756" s="1">
-        <x:v>2500</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>2721550</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
       <x:c r="A757" s="1" t="s">
-        <x:v>812</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20337,41 +20337,41 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
       <x:c r="A758" s="1" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D758" s="1">
-        <x:v>0</x:v>
+        <x:v>2700000</x:v>
       </x:c>
       <x:c r="E758" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>50</x:v>
+        <x:v>2721550</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
       <x:c r="A759" s="1" t="s">
-        <x:v>813</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C759" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D759" s="1">
         <x:v>0</x:v>
@@ -20380,18 +20380,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>35</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
       <x:c r="A760" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C760" s="1">
         <x:v>50</x:v>
@@ -20411,13 +20411,13 @@
     </x:row>
     <x:row r="761" spans="1:7">
       <x:c r="A761" s="1" t="s">
-        <x:v>815</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C761" s="1">
-        <x:v>6450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D761" s="1">
         <x:v>0</x:v>
@@ -20426,18 +20426,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F761" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>6450</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
       <x:c r="A762" s="1" t="s">
-        <x:v>816</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C762" s="1">
         <x:v>50</x:v>
@@ -20457,13 +20457,13 @@
     </x:row>
     <x:row r="763" spans="1:7">
       <x:c r="A763" s="1" t="s">
-        <x:v>817</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C763" s="1">
-        <x:v>0</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D763" s="1">
         <x:v>0</x:v>
@@ -20472,18 +20472,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F763" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G763" s="1">
-        <x:v>1000</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="764" spans="1:7">
       <x:c r="A764" s="1" t="s">
-        <x:v>818</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C764" s="1">
         <x:v>50</x:v>
@@ -20495,21 +20495,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F764" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G764" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:7">
       <x:c r="A765" s="1" t="s">
-        <x:v>819</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C765" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D765" s="1">
         <x:v>0</x:v>
@@ -20518,21 +20518,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F765" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G765" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:7">
       <x:c r="A766" s="1" t="s">
-        <x:v>820</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C766" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D766" s="1">
         <x:v>0</x:v>
@@ -20541,18 +20541,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>13200</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>13200</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
       <x:c r="A767" s="1" t="s">
-        <x:v>821</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C767" s="1">
         <x:v>50</x:v>
@@ -20572,13 +20572,13 @@
     </x:row>
     <x:row r="768" spans="1:7">
       <x:c r="A768" s="1" t="s">
-        <x:v>822</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C768" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D768" s="1">
         <x:v>0</x:v>
@@ -20587,24 +20587,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
       <x:c r="A769" s="1" t="s">
-        <x:v>823</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C769" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D769" s="1">
-        <x:v>943006</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E769" s="1">
         <x:v>0</x:v>
@@ -20613,15 +20613,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>943056</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
       <x:c r="A770" s="1" t="s">
-        <x:v>824</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C770" s="1">
         <x:v>50</x:v>
@@ -20641,16 +20641,16 @@
     </x:row>
     <x:row r="771" spans="1:7">
       <x:c r="A771" s="1" t="s">
-        <x:v>825</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C771" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D771" s="1">
-        <x:v>0</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="E771" s="1">
         <x:v>0</x:v>
@@ -20659,38 +20659,38 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G771" s="1">
-        <x:v>50</x:v>
+        <x:v>943056</x:v>
       </x:c>
     </x:row>
     <x:row r="772" spans="1:7">
       <x:c r="A772" s="1" t="s">
-        <x:v>826</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C772" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D772" s="1">
-        <x:v>487174</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E772" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F772" s="1">
-        <x:v>8500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G772" s="1">
-        <x:v>496674</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:7">
       <x:c r="A773" s="1" t="s">
-        <x:v>827</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C773" s="1">
         <x:v>50</x:v>
@@ -20699,7 +20699,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E773" s="1">
-        <x:v>0</x:v>
+        <x:v>5731065</x:v>
       </x:c>
       <x:c r="F773" s="1">
         <x:v>0</x:v>
@@ -20710,36 +20710,36 @@
     </x:row>
     <x:row r="774" spans="1:7">
       <x:c r="A774" s="1" t="s">
-        <x:v>828</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C774" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D774" s="1">
-        <x:v>0</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="E774" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F774" s="1">
-        <x:v>4999</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>5049</x:v>
+        <x:v>496674</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
       <x:c r="A775" s="1" t="s">
-        <x:v>829</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C775" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D775" s="1">
         <x:v>0</x:v>
@@ -20748,18 +20748,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>16500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
       <x:c r="A776" s="1" t="s">
-        <x:v>830</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C776" s="1">
         <x:v>50</x:v>
@@ -20771,21 +20771,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>0</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>50</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
       <x:c r="A777" s="1" t="s">
-        <x:v>831</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C777" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D777" s="1">
         <x:v>0</x:v>
@@ -20794,18 +20794,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F777" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G777" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:7">
       <x:c r="A778" s="1" t="s">
-        <x:v>832</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C778" s="1">
         <x:v>50</x:v>
@@ -20825,10 +20825,10 @@
     </x:row>
     <x:row r="779" spans="1:7">
       <x:c r="A779" s="1" t="s">
-        <x:v>833</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>50</x:v>
@@ -20840,18 +20840,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F779" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G779" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="780" spans="1:7">
       <x:c r="A780" s="1" t="s">
-        <x:v>834</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C780" s="1">
         <x:v>50</x:v>
@@ -20863,18 +20863,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F780" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G780" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="781" spans="1:7">
       <x:c r="A781" s="1" t="s">
-        <x:v>835</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C781" s="1">
         <x:v>50</x:v>
@@ -20886,21 +20886,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F781" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
       <x:c r="A782" s="1" t="s">
-        <x:v>836</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C782" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D782" s="1">
         <x:v>0</x:v>
@@ -20909,21 +20909,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F782" s="1">
-        <x:v>37300</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G782" s="1">
-        <x:v>48150</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="783" spans="1:7">
       <x:c r="A783" s="1" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C783" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D783" s="1">
         <x:v>0</x:v>
@@ -20932,21 +20932,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F783" s="1">
-        <x:v>83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G783" s="1">
-        <x:v>83</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="784" spans="1:7">
       <x:c r="A784" s="1" t="s">
-        <x:v>838</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="B784" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C784" s="1">
-        <x:v>50</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D784" s="1">
         <x:v>0</x:v>
@@ -20955,21 +20955,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F784" s="1">
-        <x:v>0</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G784" s="1">
-        <x:v>50</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="785" spans="1:7">
       <x:c r="A785" s="1" t="s">
-        <x:v>839</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="B785" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C785" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D785" s="1">
         <x:v>0</x:v>
@@ -20978,18 +20978,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F785" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G785" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="786" spans="1:7">
       <x:c r="A786" s="1" t="s">
-        <x:v>840</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="B786" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C786" s="1">
         <x:v>50</x:v>
@@ -21009,13 +21009,13 @@
     </x:row>
     <x:row r="787" spans="1:7">
       <x:c r="A787" s="1" t="s">
-        <x:v>841</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="B787" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C787" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D787" s="1">
         <x:v>0</x:v>
@@ -21024,32 +21024,78 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F787" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G787" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="788" spans="1:7">
       <x:c r="A788" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="B788" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C788" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D788" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E788" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F788" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G788" s="1">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="789" spans="1:7">
+      <x:c r="A789" s="1" t="s">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="B789" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C789" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D789" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E789" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F789" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G789" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="790" spans="1:7">
+      <x:c r="A790" s="1" t="s">
         <x:v>842</x:v>
       </x:c>
-      <x:c r="B788" s="1" t="s">
+      <x:c r="B790" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C788" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D788" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E788" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F788" s="1">
+      <x:c r="C790" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D790" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E790" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F790" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G788" s="1">
+      <x:c r="G790" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -9075,13 +9075,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C268" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D268" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E268" s="1">
         <x:v>0</x:v>
@@ -9090,7 +9090,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="269" spans="1:7">
@@ -9098,13 +9098,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B269" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C269" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D269" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E269" s="1">
         <x:v>0</x:v>
@@ -9113,7 +9113,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G269" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="270" spans="1:7">
@@ -19379,22 +19379,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D716" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E716" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19402,22 +19402,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D717" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E717" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3791,7 +3791,7 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>2008868</x:v>
+        <x:v>2032568</x:v>
       </x:c>
       <x:c r="E38" s="1">
         <x:v>0</x:v>
@@ -3800,7 +3800,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G38" s="1">
-        <x:v>2011368</x:v>
+        <x:v>2035068</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -4961,7 +4961,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C89" s="1">
-        <x:v>12000</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="D89" s="1">
         <x:v>0</x:v>
@@ -4973,7 +4973,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G89" s="1">
-        <x:v>13500</x:v>
+        <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
@@ -5217,7 +5217,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D100" s="1">
-        <x:v>1058984</x:v>
+        <x:v>1094084</x:v>
       </x:c>
       <x:c r="E100" s="1">
         <x:v>0</x:v>
@@ -5226,7 +5226,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G100" s="1">
-        <x:v>1058984</x:v>
+        <x:v>1094084</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
@@ -8503,7 +8503,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C243" s="1">
-        <x:v>6550</x:v>
+        <x:v>8050</x:v>
       </x:c>
       <x:c r="D243" s="1">
         <x:v>0</x:v>
@@ -8515,7 +8515,7 @@
         <x:v>13200</x:v>
       </x:c>
       <x:c r="G243" s="1">
-        <x:v>19750</x:v>
+        <x:v>21250</x:v>
       </x:c>
     </x:row>
     <x:row r="244" spans="1:7">
@@ -9012,7 +9012,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D265" s="1">
-        <x:v>150000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="E265" s="1">
         <x:v>0</x:v>
@@ -9021,7 +9021,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="G265" s="1">
-        <x:v>157000</x:v>
+        <x:v>307000</x:v>
       </x:c>
     </x:row>
     <x:row r="266" spans="1:7">
@@ -9075,13 +9075,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C268" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D268" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E268" s="1">
         <x:v>0</x:v>
@@ -9090,7 +9090,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="269" spans="1:7">
@@ -9098,13 +9098,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B269" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C269" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D269" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E269" s="1">
         <x:v>0</x:v>
@@ -9113,7 +9113,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G269" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="270" spans="1:7">
@@ -10136,7 +10136,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C314" s="1">
-        <x:v>3550</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D314" s="1">
         <x:v>0</x:v>
@@ -10148,7 +10148,7 @@
         <x:v>5800</x:v>
       </x:c>
       <x:c r="G314" s="1">
-        <x:v>9350</x:v>
+        <x:v>11850</x:v>
       </x:c>
     </x:row>
     <x:row r="315" spans="1:7">
@@ -10711,7 +10711,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="C339" s="1">
-        <x:v>2500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D339" s="1">
         <x:v>0</x:v>
@@ -10723,7 +10723,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G339" s="1">
-        <x:v>2500</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="340" spans="1:7">
@@ -12781,7 +12781,7 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="C429" s="1">
-        <x:v>1050</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D429" s="1">
         <x:v>0</x:v>
@@ -12793,7 +12793,7 @@
         <x:v>22650</x:v>
       </x:c>
       <x:c r="G429" s="1">
-        <x:v>23700</x:v>
+        <x:v>28700</x:v>
       </x:c>
     </x:row>
     <x:row r="430" spans="1:7">
@@ -13448,7 +13448,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C458" s="1">
-        <x:v>2500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D458" s="1">
         <x:v>0</x:v>
@@ -13460,7 +13460,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G458" s="1">
-        <x:v>4000</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:7">
@@ -19379,22 +19379,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D716" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E716" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19402,22 +19402,22 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D717" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E717" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
@@ -20391,10 +20391,10 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C760" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D760" s="1">
         <x:v>0</x:v>
@@ -20403,10 +20403,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F760" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
@@ -20414,10 +20414,10 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C761" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D761" s="1">
         <x:v>0</x:v>
@@ -20426,10 +20426,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F761" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -20391,10 +20391,10 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C760" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D760" s="1">
         <x:v>0</x:v>
@@ -20403,10 +20403,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F760" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
@@ -20414,10 +20414,10 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C761" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D761" s="1">
         <x:v>0</x:v>
@@ -20426,10 +20426,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F761" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -18551,7 +18551,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C680" s="1">
         <x:v>0</x:v>
@@ -18574,7 +18574,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C681" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4622,7 +4622,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E74" s="1">
-        <x:v>34386390</x:v>
+        <x:v>43296984</x:v>
       </x:c>
       <x:c r="F74" s="1">
         <x:v>26600</x:v>
@@ -5427,7 +5427,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E109" s="1">
-        <x:v>5731065</x:v>
+        <x:v>7216164</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>0</x:v>
@@ -10530,7 +10530,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D331" s="1">
-        <x:v>11461082</x:v>
+        <x:v>14431280</x:v>
       </x:c>
       <x:c r="E331" s="1">
         <x:v>0</x:v>
@@ -10539,7 +10539,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G331" s="1">
-        <x:v>11487082</x:v>
+        <x:v>14457280</x:v>
       </x:c>
     </x:row>
     <x:row r="332" spans="1:7">
@@ -18551,7 +18551,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C680" s="1">
         <x:v>0</x:v>
@@ -18560,7 +18560,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E680" s="1">
-        <x:v>5731065</x:v>
+        <x:v>7216164</x:v>
       </x:c>
       <x:c r="F680" s="1">
         <x:v>0</x:v>
@@ -18574,7 +18574,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C681" s="1">
         <x:v>0</x:v>
@@ -18583,7 +18583,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E681" s="1">
-        <x:v>5731065</x:v>
+        <x:v>7216164</x:v>
       </x:c>
       <x:c r="F681" s="1">
         <x:v>0</x:v>
@@ -20699,7 +20699,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E773" s="1">
-        <x:v>5731065</x:v>
+        <x:v>7216164</x:v>
       </x:c>
       <x:c r="F773" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -2375,6 +2375,9 @@
   </x:si>
   <x:si>
     <x:t>TUBERVILLE, THOMAS H</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUREK, JOSHUA</x:t>
   </x:si>
   <x:si>
     <x:t>TURNER, MICHAEL R REP.</x:t>
@@ -2613,8 +2616,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G790" totalsRowShown="0">
-  <x:autoFilter ref="A1:G790"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G791" totalsRowShown="0">
+  <x:autoFilter ref="A1:G791"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2916,7 +2919,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G790"/>
+  <x:dimension ref="A1:G791"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -16849,7 +16852,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16872,7 +16875,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -19793,22 +19796,22 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C734" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D734" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E734" s="1">
-        <x:v>0</x:v>
+        <x:v>348625</x:v>
       </x:c>
       <x:c r="F734" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
@@ -19816,10 +19819,10 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19828,10 +19831,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>5200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19839,10 +19842,10 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19851,10 +19854,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
@@ -19862,7 +19865,7 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C737" s="1">
         <x:v>50</x:v>
@@ -19885,7 +19888,7 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C738" s="1">
         <x:v>50</x:v>
@@ -19897,10 +19900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F738" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
@@ -19908,22 +19911,22 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C739" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D739" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E739" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F739" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>3920589</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
@@ -19931,13 +19934,13 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D740" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E740" s="1">
         <x:v>0</x:v>
@@ -19946,7 +19949,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>50</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
@@ -19954,10 +19957,10 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C741" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D741" s="1">
         <x:v>0</x:v>
@@ -19969,7 +19972,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
@@ -19977,10 +19980,10 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C742" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D742" s="1">
         <x:v>0</x:v>
@@ -19992,7 +19995,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
@@ -20000,7 +20003,7 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C743" s="1">
         <x:v>50</x:v>
@@ -20023,10 +20026,10 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C744" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D744" s="1">
         <x:v>0</x:v>
@@ -20035,10 +20038,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F744" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>9334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">
@@ -20046,10 +20049,10 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C745" s="1">
-        <x:v>1050</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D745" s="1">
         <x:v>0</x:v>
@@ -20058,10 +20061,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F745" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G745" s="1">
-        <x:v>1050</x:v>
+        <x:v>9334</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:7">
@@ -20072,7 +20075,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D746" s="1">
         <x:v>0</x:v>
@@ -20084,7 +20087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20092,7 +20095,7 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C747" s="1">
         <x:v>50</x:v>
@@ -20115,13 +20118,13 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D748" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E748" s="1">
         <x:v>0</x:v>
@@ -20130,7 +20133,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
@@ -20138,13 +20141,13 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C749" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D749" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E749" s="1">
         <x:v>0</x:v>
@@ -20153,7 +20156,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>50</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
@@ -20161,10 +20164,10 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>19600</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20173,10 +20176,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>36600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
@@ -20184,10 +20187,10 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>50</x:v>
+        <x:v>19600</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20196,10 +20199,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F751" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>50</x:v>
+        <x:v>36600</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
@@ -20207,7 +20210,7 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C752" s="1">
         <x:v>50</x:v>
@@ -20230,7 +20233,7 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C753" s="1">
         <x:v>50</x:v>
@@ -20253,13 +20256,13 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C754" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D754" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E754" s="1">
         <x:v>0</x:v>
@@ -20268,7 +20271,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
@@ -20276,13 +20279,13 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D755" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E755" s="1">
         <x:v>0</x:v>
@@ -20291,7 +20294,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>50</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -20299,10 +20302,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D756" s="1">
         <x:v>0</x:v>
@@ -20311,10 +20314,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F756" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>30000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
@@ -20322,10 +20325,10 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20334,10 +20337,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>0</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>50</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20345,22 +20348,22 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>19050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D758" s="1">
-        <x:v>2700000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E758" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>2721550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
@@ -20368,22 +20371,22 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C759" s="1">
-        <x:v>3500</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D759" s="1">
-        <x:v>0</x:v>
+        <x:v>2700000</x:v>
       </x:c>
       <x:c r="E759" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>3500</x:v>
+        <x:v>2721550</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
@@ -20391,10 +20394,10 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C760" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D760" s="1">
         <x:v>0</x:v>
@@ -20406,18 +20409,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
       <x:c r="A761" s="1" t="s">
-        <x:v>813</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C761" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D761" s="1">
         <x:v>0</x:v>
@@ -20426,10 +20429,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F761" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
@@ -20437,10 +20440,10 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D762" s="1">
         <x:v>0</x:v>
@@ -20449,10 +20452,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F762" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
@@ -20460,10 +20463,10 @@
         <x:v>815</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C763" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D763" s="1">
         <x:v>0</x:v>
@@ -20475,7 +20478,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G763" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="764" spans="1:7">
@@ -20483,10 +20486,10 @@
         <x:v>816</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C764" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D764" s="1">
         <x:v>0</x:v>
@@ -20498,7 +20501,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G764" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:7">
@@ -20506,10 +20509,10 @@
         <x:v>817</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C765" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D765" s="1">
         <x:v>0</x:v>
@@ -20518,10 +20521,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F765" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G765" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:7">
@@ -20529,10 +20532,10 @@
         <x:v>818</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C766" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D766" s="1">
         <x:v>0</x:v>
@@ -20541,10 +20544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>5000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>5050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
@@ -20552,7 +20555,7 @@
         <x:v>819</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C767" s="1">
         <x:v>50</x:v>
@@ -20564,10 +20567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F767" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G767" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:7">
@@ -20575,10 +20578,10 @@
         <x:v>820</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C768" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D768" s="1">
         <x:v>0</x:v>
@@ -20587,10 +20590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
@@ -20598,10 +20601,10 @@
         <x:v>821</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C769" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D769" s="1">
         <x:v>0</x:v>
@@ -20610,10 +20613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F769" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
@@ -20621,7 +20624,7 @@
         <x:v>822</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C770" s="1">
         <x:v>50</x:v>
@@ -20644,13 +20647,13 @@
         <x:v>823</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C771" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D771" s="1">
-        <x:v>943006</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E771" s="1">
         <x:v>0</x:v>
@@ -20659,7 +20662,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G771" s="1">
-        <x:v>943056</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="772" spans="1:7">
@@ -20667,13 +20670,13 @@
         <x:v>824</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C772" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D772" s="1">
-        <x:v>0</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="E772" s="1">
         <x:v>0</x:v>
@@ -20682,7 +20685,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G772" s="1">
-        <x:v>50</x:v>
+        <x:v>943056</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:7">
@@ -20690,7 +20693,7 @@
         <x:v>825</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C773" s="1">
         <x:v>50</x:v>
@@ -20699,7 +20702,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E773" s="1">
-        <x:v>7216164</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F773" s="1">
         <x:v>0</x:v>
@@ -20713,22 +20716,22 @@
         <x:v>826</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C774" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D774" s="1">
-        <x:v>487174</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E774" s="1">
-        <x:v>0</x:v>
+        <x:v>7216164</x:v>
       </x:c>
       <x:c r="F774" s="1">
-        <x:v>8500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>496674</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
@@ -20736,22 +20739,22 @@
         <x:v>827</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C775" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D775" s="1">
-        <x:v>0</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="E775" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>0</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>50</x:v>
+        <x:v>496674</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
@@ -20759,7 +20762,7 @@
         <x:v>828</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C776" s="1">
         <x:v>50</x:v>
@@ -20771,10 +20774,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>4999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>5049</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
@@ -20782,10 +20785,10 @@
         <x:v>829</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C777" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D777" s="1">
         <x:v>0</x:v>
@@ -20794,10 +20797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F777" s="1">
-        <x:v>16500</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G777" s="1">
-        <x:v>16500</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:7">
@@ -20805,10 +20808,10 @@
         <x:v>830</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C778" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D778" s="1">
         <x:v>0</x:v>
@@ -20817,10 +20820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F778" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
@@ -20828,7 +20831,7 @@
         <x:v>831</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>50</x:v>
@@ -20851,7 +20854,7 @@
         <x:v>832</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C780" s="1">
         <x:v>50</x:v>
@@ -20874,7 +20877,7 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C781" s="1">
         <x:v>50</x:v>
@@ -20886,10 +20889,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F781" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
@@ -20897,7 +20900,7 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C782" s="1">
         <x:v>50</x:v>
@@ -20909,10 +20912,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F782" s="1">
-        <x:v>1500</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G782" s="1">
-        <x:v>1550</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="783" spans="1:7">
@@ -20920,7 +20923,7 @@
         <x:v>835</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C783" s="1">
         <x:v>50</x:v>
@@ -20932,10 +20935,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F783" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G783" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="784" spans="1:7">
@@ -20943,10 +20946,10 @@
         <x:v>836</x:v>
       </x:c>
       <x:c r="B784" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C784" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D784" s="1">
         <x:v>0</x:v>
@@ -20955,10 +20958,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F784" s="1">
-        <x:v>37300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G784" s="1">
-        <x:v>48150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="785" spans="1:7">
@@ -20966,10 +20969,10 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B785" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C785" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D785" s="1">
         <x:v>0</x:v>
@@ -20978,10 +20981,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F785" s="1">
-        <x:v>83</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G785" s="1">
-        <x:v>83</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="786" spans="1:7">
@@ -20989,10 +20992,10 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="B786" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C786" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D786" s="1">
         <x:v>0</x:v>
@@ -21001,10 +21004,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F786" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G786" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="787" spans="1:7">
@@ -21012,7 +21015,7 @@
         <x:v>839</x:v>
       </x:c>
       <x:c r="B787" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C787" s="1">
         <x:v>50</x:v>
@@ -21035,7 +21038,7 @@
         <x:v>840</x:v>
       </x:c>
       <x:c r="B788" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C788" s="1">
         <x:v>50</x:v>
@@ -21058,10 +21061,10 @@
         <x:v>841</x:v>
       </x:c>
       <x:c r="B789" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C789" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D789" s="1">
         <x:v>0</x:v>
@@ -21070,10 +21073,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F789" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G789" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="790" spans="1:7">
@@ -21081,21 +21084,44 @@
         <x:v>842</x:v>
       </x:c>
       <x:c r="B790" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C790" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D790" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E790" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F790" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G790" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="791" spans="1:7">
+      <x:c r="A791" s="1" t="s">
+        <x:v>843</x:v>
+      </x:c>
+      <x:c r="B791" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C790" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D790" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E790" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F790" s="1">
+      <x:c r="C791" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D791" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E791" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F791" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G790" s="1">
+      <x:c r="G791" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -10533,7 +10533,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D331" s="1">
-        <x:v>14431280</x:v>
+        <x:v>38673708</x:v>
       </x:c>
       <x:c r="E331" s="1">
         <x:v>0</x:v>
@@ -10542,7 +10542,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G331" s="1">
-        <x:v>14457280</x:v>
+        <x:v>38699708</x:v>
       </x:c>
     </x:row>
     <x:row r="332" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -9078,13 +9078,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C268" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D268" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E268" s="1">
         <x:v>0</x:v>
@@ -9093,7 +9093,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="269" spans="1:7">
@@ -9101,13 +9101,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B269" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C269" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D269" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E269" s="1">
         <x:v>0</x:v>
@@ -9116,7 +9116,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G269" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="270" spans="1:7">
@@ -16852,7 +16852,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16875,7 +16875,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -18531,22 +18531,22 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C679" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D679" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E679" s="1">
-        <x:v>0</x:v>
+        <x:v>7216164</x:v>
       </x:c>
       <x:c r="F679" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18577,22 +18577,22 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D681" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E681" s="1">
-        <x:v>7216164</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -20417,10 +20417,10 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C761" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D761" s="1">
         <x:v>0</x:v>
@@ -20429,10 +20429,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F761" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
@@ -20440,10 +20440,10 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D762" s="1">
         <x:v>0</x:v>
@@ -20452,10 +20452,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F762" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3285,7 +3285,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>1000</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>0</x:v>
@@ -3297,7 +3297,7 @@
         <x:v>31668</x:v>
       </x:c>
       <x:c r="G16" s="1">
-        <x:v>32668</x:v>
+        <x:v>34168</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
@@ -9078,13 +9078,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C268" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D268" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E268" s="1">
         <x:v>0</x:v>
@@ -9093,7 +9093,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="269" spans="1:7">
@@ -9101,13 +9101,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B269" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C269" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D269" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E269" s="1">
         <x:v>0</x:v>
@@ -9116,7 +9116,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G269" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="270" spans="1:7">
@@ -16852,7 +16852,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16875,7 +16875,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -18531,22 +18531,22 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C679" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D679" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E679" s="1">
-        <x:v>7216164</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F679" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18577,22 +18577,22 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D681" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E681" s="1">
-        <x:v>0</x:v>
+        <x:v>7216164</x:v>
       </x:c>
       <x:c r="F681" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -20417,10 +20417,10 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C761" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D761" s="1">
         <x:v>0</x:v>
@@ -20429,10 +20429,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F761" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
@@ -20440,10 +20440,10 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D762" s="1">
         <x:v>0</x:v>
@@ -20452,10 +20452,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F762" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16852,7 +16852,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16875,7 +16875,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -18117,13 +18117,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18132,7 +18132,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18140,13 +18140,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18155,7 +18155,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18554,7 +18554,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C680" s="1">
         <x:v>0</x:v>
@@ -18577,7 +18577,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C681" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -10533,7 +10533,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D331" s="1">
-        <x:v>38673708</x:v>
+        <x:v>39090956</x:v>
       </x:c>
       <x:c r="E331" s="1">
         <x:v>0</x:v>
@@ -10542,7 +10542,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G331" s="1">
-        <x:v>38699708</x:v>
+        <x:v>39116956</x:v>
       </x:c>
     </x:row>
     <x:row r="332" spans="1:7">
@@ -18117,13 +18117,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18132,7 +18132,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18140,13 +18140,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18155,7 +18155,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18554,7 +18554,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C680" s="1">
         <x:v>0</x:v>
@@ -18577,7 +18577,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C681" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16852,7 +16852,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16875,7 +16875,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4967,7 +4967,7 @@
         <x:v>14500</x:v>
       </x:c>
       <x:c r="D89" s="1">
-        <x:v>0</x:v>
+        <x:v>1020173</x:v>
       </x:c>
       <x:c r="E89" s="1">
         <x:v>0</x:v>
@@ -4976,7 +4976,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G89" s="1">
-        <x:v>16000</x:v>
+        <x:v>1036173</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
@@ -10119,7 +10119,7 @@
         <x:v>11050</x:v>
       </x:c>
       <x:c r="D313" s="1">
-        <x:v>943006</x:v>
+        <x:v>1962970</x:v>
       </x:c>
       <x:c r="E313" s="1">
         <x:v>0</x:v>
@@ -10128,7 +10128,7 @@
         <x:v>42250</x:v>
       </x:c>
       <x:c r="G313" s="1">
-        <x:v>996306</x:v>
+        <x:v>2016270</x:v>
       </x:c>
     </x:row>
     <x:row r="314" spans="1:7">
@@ -10303,7 +10303,7 @@
         <x:v>11850</x:v>
       </x:c>
       <x:c r="D321" s="1">
-        <x:v>3672392</x:v>
+        <x:v>5702430</x:v>
       </x:c>
       <x:c r="E321" s="1">
         <x:v>0</x:v>
@@ -10312,7 +10312,7 @@
         <x:v>47733</x:v>
       </x:c>
       <x:c r="G321" s="1">
-        <x:v>3731975</x:v>
+        <x:v>5762013</x:v>
       </x:c>
     </x:row>
     <x:row r="322" spans="1:7">
@@ -10441,7 +10441,7 @@
         <x:v>12850</x:v>
       </x:c>
       <x:c r="D327" s="1">
-        <x:v>3394035</x:v>
+        <x:v>6451536</x:v>
       </x:c>
       <x:c r="E327" s="1">
         <x:v>0</x:v>
@@ -10450,7 +10450,7 @@
         <x:v>35533</x:v>
       </x:c>
       <x:c r="G327" s="1">
-        <x:v>3442418</x:v>
+        <x:v>6499919</x:v>
       </x:c>
     </x:row>
     <x:row r="328" spans="1:7">
@@ -10533,7 +10533,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D331" s="1">
-        <x:v>39090956</x:v>
+        <x:v>61129130</x:v>
       </x:c>
       <x:c r="E331" s="1">
         <x:v>0</x:v>
@@ -10542,7 +10542,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G331" s="1">
-        <x:v>39116956</x:v>
+        <x:v>61155130</x:v>
       </x:c>
     </x:row>
     <x:row r="332" spans="1:7">
@@ -16852,7 +16852,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16875,7 +16875,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -18721,7 +18721,7 @@
         <x:v>28050</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>764206</x:v>
+        <x:v>1789991</x:v>
       </x:c>
       <x:c r="E687" s="1">
         <x:v>0</x:v>
@@ -18730,7 +18730,7 @@
         <x:v>20501</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>812757</x:v>
+        <x:v>1838542</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -18859,7 +18859,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D693" s="1">
-        <x:v>1131345</x:v>
+        <x:v>2150512</x:v>
       </x:c>
       <x:c r="E693" s="1">
         <x:v>0</x:v>
@@ -18868,7 +18868,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>1131395</x:v>
+        <x:v>2150562</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
@@ -19710,7 +19710,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="D730" s="1">
-        <x:v>0</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="E730" s="1">
         <x:v>0</x:v>
@@ -19719,7 +19719,7 @@
         <x:v>11500</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>13500</x:v>
+        <x:v>1029258</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
@@ -20676,7 +20676,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D772" s="1">
-        <x:v>943006</x:v>
+        <x:v>1962970</x:v>
       </x:c>
       <x:c r="E772" s="1">
         <x:v>0</x:v>
@@ -20685,7 +20685,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G772" s="1">
-        <x:v>943056</x:v>
+        <x:v>1963020</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4634,7 +4634,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E74" s="1">
-        <x:v>43296984</x:v>
+        <x:v>55177776</x:v>
       </x:c>
       <x:c r="F74" s="1">
         <x:v>26600</x:v>
@@ -5439,7 +5439,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E109" s="1">
-        <x:v>7216164</x:v>
+        <x:v>9196296</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>0</x:v>
@@ -10588,7 +10588,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D333" s="1">
-        <x:v>61129130</x:v>
+        <x:v>63109262</x:v>
       </x:c>
       <x:c r="E333" s="1">
         <x:v>0</x:v>
@@ -10597,7 +10597,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G333" s="1">
-        <x:v>61155130</x:v>
+        <x:v>63135262</x:v>
       </x:c>
     </x:row>
     <x:row r="334" spans="1:7">
@@ -12586,7 +12586,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C420" s="1">
-        <x:v>18750</x:v>
+        <x:v>23750</x:v>
       </x:c>
       <x:c r="D420" s="1">
         <x:v>0</x:v>
@@ -12598,7 +12598,7 @@
         <x:v>25450</x:v>
       </x:c>
       <x:c r="G420" s="1">
-        <x:v>44200</x:v>
+        <x:v>49200</x:v>
       </x:c>
     </x:row>
     <x:row r="421" spans="1:7">
@@ -13483,7 +13483,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C459" s="1">
-        <x:v>8300</x:v>
+        <x:v>13300</x:v>
       </x:c>
       <x:c r="D459" s="1">
         <x:v>104910</x:v>
@@ -13495,7 +13495,7 @@
         <x:v>20050</x:v>
       </x:c>
       <x:c r="G459" s="1">
-        <x:v>133260</x:v>
+        <x:v>138260</x:v>
       </x:c>
     </x:row>
     <x:row r="460" spans="1:7">
@@ -17413,10 +17413,10 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C630" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D630" s="1">
         <x:v>0</x:v>
@@ -17425,10 +17425,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F630" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G630" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:7">
@@ -17436,10 +17436,10 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17448,10 +17448,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17873,22 +17873,22 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C650" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D650" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E650" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F650" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
@@ -17896,22 +17896,22 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C651" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D651" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E651" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F651" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
@@ -18687,7 +18687,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E685" s="1">
-        <x:v>7216164</x:v>
+        <x:v>9196296</x:v>
       </x:c>
       <x:c r="F685" s="1">
         <x:v>0</x:v>
@@ -18710,7 +18710,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E686" s="1">
-        <x:v>7216164</x:v>
+        <x:v>9196296</x:v>
       </x:c>
       <x:c r="F686" s="1">
         <x:v>0</x:v>
@@ -18842,7 +18842,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>28050</x:v>
+        <x:v>33050</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>1789991</x:v>
@@ -18854,7 +18854,7 @@
         <x:v>20501</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>1838542</x:v>
+        <x:v>1843542</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -20872,7 +20872,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E780" s="1">
-        <x:v>7216164</x:v>
+        <x:v>9196296</x:v>
       </x:c>
       <x:c r="F780" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -307,10 +307,10 @@
     <x:t>BOOKER, CORY A.</x:t>
   </x:si>
   <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
     <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
   </x:si>
   <x:si>
     <x:t>BOOZMAN, SEN. JOHN</x:t>
@@ -4260,7 +4260,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C58" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>0</x:v>
@@ -4269,10 +4269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>2800</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G58" s="1">
-        <x:v>2800</x:v>
+        <x:v>18250</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
@@ -4283,7 +4283,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C59" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>0</x:v>
@@ -4292,10 +4292,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>18200</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G59" s="1">
-        <x:v>18250</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
@@ -4947,7 +4947,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C88" s="1">
         <x:v>0</x:v>
@@ -5890,7 +5890,7 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C129" s="1">
         <x:v>0</x:v>
@@ -6005,7 +6005,7 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C134" s="1">
         <x:v>50</x:v>
@@ -6120,7 +6120,7 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C139" s="1">
         <x:v>0</x:v>
@@ -7201,7 +7201,7 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C186" s="1">
         <x:v>0</x:v>
@@ -9110,7 +9110,7 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="B269" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C269" s="1">
         <x:v>4550</x:v>
@@ -9616,7 +9616,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="B291" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C291" s="1">
         <x:v>0</x:v>
@@ -9754,7 +9754,7 @@
         <x:v>351</x:v>
       </x:c>
       <x:c r="B297" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C297" s="1">
         <x:v>0</x:v>
@@ -10536,7 +10536,7 @@
         <x:v>385</x:v>
       </x:c>
       <x:c r="B331" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C331" s="1">
         <x:v>0</x:v>
@@ -11226,7 +11226,7 @@
         <x:v>416</x:v>
       </x:c>
       <x:c r="B361" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C361" s="1">
         <x:v>0</x:v>
@@ -11272,7 +11272,7 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B363" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C363" s="1">
         <x:v>0</x:v>
@@ -11479,7 +11479,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="B372" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C372" s="1">
         <x:v>0</x:v>
@@ -11525,7 +11525,7 @@
         <x:v>429</x:v>
       </x:c>
       <x:c r="B374" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C374" s="1">
         <x:v>0</x:v>
@@ -11617,7 +11617,7 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="B378" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C378" s="1">
         <x:v>50</x:v>
@@ -12951,7 +12951,7 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B436" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C436" s="1">
         <x:v>50</x:v>
@@ -13319,7 +13319,7 @@
         <x:v>507</x:v>
       </x:c>
       <x:c r="B452" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C452" s="1">
         <x:v>0</x:v>
@@ -13894,7 +13894,7 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C477" s="1">
         <x:v>1550</x:v>
@@ -14998,7 +14998,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C525" s="1">
         <x:v>50</x:v>
@@ -15159,7 +15159,7 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C532" s="1">
         <x:v>0</x:v>
@@ -15228,7 +15228,7 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C535" s="1">
         <x:v>0</x:v>
@@ -15412,7 +15412,7 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C543" s="1">
         <x:v>50</x:v>
@@ -15481,7 +15481,7 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C546" s="1">
         <x:v>50</x:v>
@@ -15573,7 +15573,7 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C550" s="1">
         <x:v>50</x:v>
@@ -15734,7 +15734,7 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C557" s="1">
         <x:v>0</x:v>
@@ -16125,7 +16125,7 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C574" s="1">
         <x:v>1000</x:v>
@@ -16217,7 +16217,7 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C578" s="1">
         <x:v>0</x:v>
@@ -16769,7 +16769,7 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C602" s="1">
         <x:v>0</x:v>
@@ -17413,10 +17413,10 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C630" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D630" s="1">
         <x:v>0</x:v>
@@ -17425,10 +17425,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F630" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G630" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:7">
@@ -17436,10 +17436,10 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17448,10 +17448,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -18149,7 +18149,7 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C662" s="1">
         <x:v>1050</x:v>
@@ -18287,7 +18287,7 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C668" s="1">
         <x:v>50</x:v>
@@ -18356,7 +18356,7 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C671" s="1">
         <x:v>50</x:v>
@@ -18862,7 +18862,7 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C693" s="1">
         <x:v>0</x:v>
@@ -19805,7 +19805,7 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C734" s="1">
         <x:v>0</x:v>
@@ -19897,7 +19897,7 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C738" s="1">
         <x:v>0</x:v>
@@ -19952,7 +19952,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E740" s="1">
-        <x:v>348625</x:v>
+        <x:v>424596</x:v>
       </x:c>
       <x:c r="F740" s="1">
         <x:v>0</x:v>
@@ -20104,7 +20104,7 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C747" s="1">
         <x:v>50</x:v>
@@ -20587,7 +20587,7 @@
         <x:v>817</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C768" s="1">
         <x:v>0</x:v>
@@ -21139,7 +21139,7 @@
         <x:v>841</x:v>
       </x:c>
       <x:c r="B792" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C792" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16953,7 +16953,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C610" s="1">
         <x:v>0</x:v>
@@ -16976,7 +16976,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C611" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16953,7 +16953,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C610" s="1">
         <x:v>0</x:v>
@@ -16976,7 +16976,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C611" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -307,12 +307,12 @@
     <x:t>BOOKER, CORY A.</x:t>
   </x:si>
   <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
     <x:t>BOOZMAN, SEN. JOHN</x:t>
   </x:si>
   <x:si>
@@ -1802,6 +1802,9 @@
   </x:si>
   <x:si>
     <x:t>ONDER JR, ROBERT FRANK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSBORN, DAN</x:t>
   </x:si>
   <x:si>
     <x:t>OSSOFF, T. JONATHAN</x:t>
@@ -2625,8 +2628,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G798" totalsRowShown="0">
-  <x:autoFilter ref="A1:G798"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G799" totalsRowShown="0">
+  <x:autoFilter ref="A1:G799"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2928,7 +2931,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G798"/>
+  <x:dimension ref="A1:G799"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4260,7 +4263,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C58" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>0</x:v>
@@ -4269,10 +4272,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>18200</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G58" s="1">
-        <x:v>18250</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
@@ -4283,7 +4286,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C59" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>0</x:v>
@@ -4292,10 +4295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>2800</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G59" s="1">
-        <x:v>2800</x:v>
+        <x:v>18250</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
@@ -4634,7 +4637,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E74" s="1">
-        <x:v>55177776</x:v>
+        <x:v>98155764</x:v>
       </x:c>
       <x:c r="F74" s="1">
         <x:v>26600</x:v>
@@ -4947,7 +4950,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C88" s="1">
         <x:v>0</x:v>
@@ -5439,7 +5442,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E109" s="1">
-        <x:v>9196296</x:v>
+        <x:v>16359294</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>0</x:v>
@@ -5890,7 +5893,7 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C129" s="1">
         <x:v>0</x:v>
@@ -6005,7 +6008,7 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C134" s="1">
         <x:v>50</x:v>
@@ -6120,7 +6123,7 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C139" s="1">
         <x:v>0</x:v>
@@ -7201,7 +7204,7 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C186" s="1">
         <x:v>0</x:v>
@@ -9110,7 +9113,7 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="B269" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C269" s="1">
         <x:v>4550</x:v>
@@ -9616,7 +9619,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="B291" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C291" s="1">
         <x:v>0</x:v>
@@ -9754,7 +9757,7 @@
         <x:v>351</x:v>
       </x:c>
       <x:c r="B297" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C297" s="1">
         <x:v>0</x:v>
@@ -10536,7 +10539,7 @@
         <x:v>385</x:v>
       </x:c>
       <x:c r="B331" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C331" s="1">
         <x:v>0</x:v>
@@ -10588,7 +10591,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D333" s="1">
-        <x:v>63109262</x:v>
+        <x:v>72506796</x:v>
       </x:c>
       <x:c r="E333" s="1">
         <x:v>0</x:v>
@@ -10597,7 +10600,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G333" s="1">
-        <x:v>63135262</x:v>
+        <x:v>72532796</x:v>
       </x:c>
     </x:row>
     <x:row r="334" spans="1:7">
@@ -11226,7 +11229,7 @@
         <x:v>416</x:v>
       </x:c>
       <x:c r="B361" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C361" s="1">
         <x:v>0</x:v>
@@ -11272,7 +11275,7 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B363" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C363" s="1">
         <x:v>0</x:v>
@@ -11479,7 +11482,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="B372" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C372" s="1">
         <x:v>0</x:v>
@@ -11525,7 +11528,7 @@
         <x:v>429</x:v>
       </x:c>
       <x:c r="B374" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C374" s="1">
         <x:v>0</x:v>
@@ -11617,7 +11620,7 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="B378" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C378" s="1">
         <x:v>50</x:v>
@@ -12790,22 +12793,22 @@
         <x:v>485</x:v>
       </x:c>
       <x:c r="B429" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C429" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D429" s="1">
-        <x:v>149204</x:v>
+        <x:v>74602</x:v>
       </x:c>
       <x:c r="E429" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F429" s="1">
-        <x:v>33600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G429" s="1">
-        <x:v>182854</x:v>
+        <x:v>74602</x:v>
       </x:c>
     </x:row>
     <x:row r="430" spans="1:7">
@@ -12813,22 +12816,22 @@
         <x:v>485</x:v>
       </x:c>
       <x:c r="B430" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C430" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D430" s="1">
-        <x:v>74602</x:v>
+        <x:v>149204</x:v>
       </x:c>
       <x:c r="E430" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F430" s="1">
-        <x:v>0</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G430" s="1">
-        <x:v>74602</x:v>
+        <x:v>182854</x:v>
       </x:c>
     </x:row>
     <x:row r="431" spans="1:7">
@@ -12951,7 +12954,7 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B436" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C436" s="1">
         <x:v>50</x:v>
@@ -13319,7 +13322,7 @@
         <x:v>507</x:v>
       </x:c>
       <x:c r="B452" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C452" s="1">
         <x:v>0</x:v>
@@ -13894,7 +13897,7 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C477" s="1">
         <x:v>1550</x:v>
@@ -14998,7 +15001,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C525" s="1">
         <x:v>50</x:v>
@@ -15159,7 +15162,7 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C532" s="1">
         <x:v>0</x:v>
@@ -15228,7 +15231,7 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C535" s="1">
         <x:v>0</x:v>
@@ -15343,7 +15346,7 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C540" s="1">
         <x:v>0</x:v>
@@ -15352,13 +15355,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E540" s="1">
-        <x:v>0</x:v>
+        <x:v>20171730</x:v>
       </x:c>
       <x:c r="F540" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -15366,10 +15369,10 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C541" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D541" s="1">
         <x:v>0</x:v>
@@ -15378,10 +15381,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F541" s="1">
-        <x:v>29800</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>34800</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -15389,10 +15392,10 @@
         <x:v>598</x:v>
       </x:c>
       <x:c r="B542" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C542" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D542" s="1">
         <x:v>0</x:v>
@@ -15401,10 +15404,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F542" s="1">
-        <x:v>0</x:v>
+        <x:v>29800</x:v>
       </x:c>
       <x:c r="G542" s="1">
-        <x:v>50</x:v>
+        <x:v>34800</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:7">
@@ -15412,7 +15415,7 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C543" s="1">
         <x:v>50</x:v>
@@ -15424,10 +15427,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>5650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15435,22 +15438,22 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C544" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D544" s="1">
-        <x:v>74692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E544" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>0</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>76742</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -15458,22 +15461,22 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="B545" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C545" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D545" s="1">
-        <x:v>0</x:v>
+        <x:v>74692</x:v>
       </x:c>
       <x:c r="E545" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F545" s="1">
-        <x:v>6834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G545" s="1">
-        <x:v>6884</x:v>
+        <x:v>76742</x:v>
       </x:c>
     </x:row>
     <x:row r="546" spans="1:7">
@@ -15481,7 +15484,7 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C546" s="1">
         <x:v>50</x:v>
@@ -15493,10 +15496,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F546" s="1">
-        <x:v>0</x:v>
+        <x:v>6834</x:v>
       </x:c>
       <x:c r="G546" s="1">
-        <x:v>50</x:v>
+        <x:v>6884</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:7">
@@ -15504,22 +15507,22 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C547" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D547" s="1">
-        <x:v>558813</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E547" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F547" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G547" s="1">
-        <x:v>559813</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="548" spans="1:7">
@@ -15527,22 +15530,22 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C548" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D548" s="1">
-        <x:v>0</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E548" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F548" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G548" s="1">
-        <x:v>6650</x:v>
+        <x:v>559813</x:v>
       </x:c>
     </x:row>
     <x:row r="549" spans="1:7">
@@ -15550,22 +15553,22 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C549" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D549" s="1">
-        <x:v>8250000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E549" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F549" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G549" s="1">
-        <x:v>8250000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:7">
@@ -15573,13 +15576,13 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C550" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D550" s="1">
-        <x:v>0</x:v>
+        <x:v>8250000</x:v>
       </x:c>
       <x:c r="E550" s="1">
         <x:v>0</x:v>
@@ -15588,7 +15591,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G550" s="1">
-        <x:v>50</x:v>
+        <x:v>8250000</x:v>
       </x:c>
     </x:row>
     <x:row r="551" spans="1:7">
@@ -15596,22 +15599,22 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C551" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D551" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E551" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F551" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -15619,22 +15622,22 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C552" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D552" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E552" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F552" s="1">
-        <x:v>1089100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G552" s="1">
-        <x:v>1089150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="553" spans="1:7">
@@ -15642,22 +15645,22 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B553" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C553" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D553" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E553" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F553" s="1">
-        <x:v>0</x:v>
+        <x:v>1089100</x:v>
       </x:c>
       <x:c r="G553" s="1">
-        <x:v>1927706</x:v>
+        <x:v>1089150</x:v>
       </x:c>
     </x:row>
     <x:row r="554" spans="1:7">
@@ -15665,13 +15668,13 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C554" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D554" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E554" s="1">
         <x:v>0</x:v>
@@ -15680,7 +15683,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G554" s="1">
-        <x:v>50</x:v>
+        <x:v>1927706</x:v>
       </x:c>
     </x:row>
     <x:row r="555" spans="1:7">
@@ -15688,7 +15691,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C555" s="1">
         <x:v>50</x:v>
@@ -15700,10 +15703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F555" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G555" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="556" spans="1:7">
@@ -15711,7 +15714,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>50</x:v>
@@ -15723,10 +15726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -15734,10 +15737,10 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C557" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D557" s="1">
         <x:v>0</x:v>
@@ -15746,10 +15749,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F557" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G557" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:7">
@@ -15757,10 +15760,10 @@
         <x:v>614</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C558" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D558" s="1">
         <x:v>0</x:v>
@@ -15769,10 +15772,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F558" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G558" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:7">
@@ -15780,7 +15783,7 @@
         <x:v>615</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C559" s="1">
         <x:v>50</x:v>
@@ -15792,10 +15795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -15803,22 +15806,22 @@
         <x:v>616</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C560" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D560" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E560" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F560" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G560" s="1">
-        <x:v>0</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:7">
@@ -15826,22 +15829,22 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C561" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D561" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E561" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F561" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G561" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:7">
@@ -15849,7 +15852,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B562" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C562" s="1">
         <x:v>50</x:v>
@@ -15872,22 +15875,22 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="B563" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C563" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D563" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E563" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F563" s="1">
-        <x:v>14866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G563" s="1">
-        <x:v>117122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="564" spans="1:7">
@@ -15895,22 +15898,22 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C564" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D564" s="1">
-        <x:v>75000</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E564" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F564" s="1">
-        <x:v>0</x:v>
+        <x:v>14866</x:v>
       </x:c>
       <x:c r="G564" s="1">
-        <x:v>75000</x:v>
+        <x:v>117122</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:7">
@@ -15918,13 +15921,13 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C565" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D565" s="1">
-        <x:v>0</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="E565" s="1">
         <x:v>0</x:v>
@@ -15933,7 +15936,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>50</x:v>
+        <x:v>75000</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -15941,7 +15944,7 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>50</x:v>
@@ -15964,7 +15967,7 @@
         <x:v>623</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>624</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C567" s="1">
         <x:v>50</x:v>
@@ -15984,10 +15987,10 @@
     </x:row>
     <x:row r="568" spans="1:7">
       <x:c r="A568" s="1" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="B568" s="1" t="s">
         <x:v>625</x:v>
-      </x:c>
-      <x:c r="B568" s="1" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="C568" s="1">
         <x:v>50</x:v>
@@ -16010,10 +16013,10 @@
         <x:v>626</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C569" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D569" s="1">
         <x:v>0</x:v>
@@ -16022,10 +16025,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F569" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G569" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="570" spans="1:7">
@@ -16033,7 +16036,7 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>0</x:v>
@@ -16045,10 +16048,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F570" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G570" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="571" spans="1:7">
@@ -16059,19 +16062,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C571" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D571" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E571" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F571" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G571" s="1">
-        <x:v>50</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:7">
@@ -16079,7 +16082,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B572" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C572" s="1">
         <x:v>50</x:v>
@@ -16088,13 +16091,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E572" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F572" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -16102,7 +16105,7 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C573" s="1">
         <x:v>50</x:v>
@@ -16114,10 +16117,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F573" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G573" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:7">
@@ -16125,10 +16128,10 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C574" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D574" s="1">
         <x:v>0</x:v>
@@ -16137,10 +16140,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F574" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G574" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:7">
@@ -16148,10 +16151,10 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C575" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D575" s="1">
         <x:v>0</x:v>
@@ -16160,10 +16163,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F575" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G575" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="576" spans="1:7">
@@ -16171,7 +16174,7 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C576" s="1">
         <x:v>50</x:v>
@@ -16194,7 +16197,7 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C577" s="1">
         <x:v>50</x:v>
@@ -16217,10 +16220,10 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C578" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D578" s="1">
         <x:v>0</x:v>
@@ -16229,10 +16232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F578" s="1">
-        <x:v>-19405</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G578" s="1">
-        <x:v>-19405</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="579" spans="1:7">
@@ -16240,22 +16243,22 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C579" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D579" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E579" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F579" s="1">
-        <x:v>0</x:v>
+        <x:v>-19405</x:v>
       </x:c>
       <x:c r="G579" s="1">
-        <x:v>1491280</x:v>
+        <x:v>-19405</x:v>
       </x:c>
     </x:row>
     <x:row r="580" spans="1:7">
@@ -16263,22 +16266,22 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C580" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D580" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E580" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F580" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G580" s="1">
-        <x:v>500</x:v>
+        <x:v>1491280</x:v>
       </x:c>
     </x:row>
     <x:row r="581" spans="1:7">
@@ -16286,10 +16289,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C581" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D581" s="1">
         <x:v>0</x:v>
@@ -16298,10 +16301,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F581" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G581" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="582" spans="1:7">
@@ -16309,7 +16312,7 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C582" s="1">
         <x:v>50</x:v>
@@ -16321,10 +16324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F582" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G582" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="583" spans="1:7">
@@ -16332,7 +16335,7 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C583" s="1">
         <x:v>50</x:v>
@@ -16344,10 +16347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F583" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G583" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="584" spans="1:7">
@@ -16355,7 +16358,7 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C584" s="1">
         <x:v>50</x:v>
@@ -16367,10 +16370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F584" s="1">
-        <x:v>1287</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>1337</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -16378,10 +16381,10 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -16390,10 +16393,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>6697</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>6697</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -16401,22 +16404,22 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D586" s="1">
-        <x:v>75844</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E586" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>0</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>75894</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -16424,22 +16427,22 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C587" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D587" s="1">
-        <x:v>0</x:v>
+        <x:v>75844</x:v>
       </x:c>
       <x:c r="E587" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F587" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G587" s="1">
-        <x:v>4000</x:v>
+        <x:v>75894</x:v>
       </x:c>
     </x:row>
     <x:row r="588" spans="1:7">
@@ -16447,7 +16450,7 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C588" s="1">
         <x:v>0</x:v>
@@ -16459,10 +16462,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F588" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -16470,10 +16473,10 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C589" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D589" s="1">
         <x:v>0</x:v>
@@ -16482,10 +16485,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F589" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">
@@ -16493,7 +16496,7 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C590" s="1">
         <x:v>50</x:v>
@@ -16516,7 +16519,7 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C591" s="1">
         <x:v>50</x:v>
@@ -16539,22 +16542,22 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C592" s="1">
-        <x:v>7500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D592" s="1">
-        <x:v>1400000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E592" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F592" s="1">
-        <x:v>10500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G592" s="1">
-        <x:v>1418000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="593" spans="1:7">
@@ -16562,22 +16565,22 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C593" s="1">
-        <x:v>50</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D593" s="1">
-        <x:v>0</x:v>
+        <x:v>1400000</x:v>
       </x:c>
       <x:c r="E593" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F593" s="1">
-        <x:v>0</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G593" s="1">
-        <x:v>50</x:v>
+        <x:v>1418000</x:v>
       </x:c>
     </x:row>
     <x:row r="594" spans="1:7">
@@ -16585,10 +16588,10 @@
         <x:v>651</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C594" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D594" s="1">
         <x:v>0</x:v>
@@ -16597,10 +16600,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F594" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G594" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="595" spans="1:7">
@@ -16608,10 +16611,10 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C595" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D595" s="1">
         <x:v>0</x:v>
@@ -16623,7 +16626,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G595" s="1">
-        <x:v>1550</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="596" spans="1:7">
@@ -16631,7 +16634,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C596" s="1">
         <x:v>50</x:v>
@@ -16643,10 +16646,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F596" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G596" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="597" spans="1:7">
@@ -16654,7 +16657,7 @@
         <x:v>654</x:v>
       </x:c>
       <x:c r="B597" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C597" s="1">
         <x:v>50</x:v>
@@ -16677,7 +16680,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>50</x:v>
@@ -16700,7 +16703,7 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C599" s="1">
         <x:v>50</x:v>
@@ -16723,7 +16726,7 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C600" s="1">
         <x:v>50</x:v>
@@ -16746,13 +16749,13 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C601" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D601" s="1">
-        <x:v>2707641</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E601" s="1">
         <x:v>0</x:v>
@@ -16761,7 +16764,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>2707641</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -16769,22 +16772,22 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C602" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D602" s="1">
-        <x:v>0</x:v>
+        <x:v>2707641</x:v>
       </x:c>
       <x:c r="E602" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>81050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>81050</x:v>
+        <x:v>2707641</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -16792,10 +16795,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C603" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D603" s="1">
         <x:v>0</x:v>
@@ -16804,10 +16807,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F603" s="1">
-        <x:v>0</x:v>
+        <x:v>81050</x:v>
       </x:c>
       <x:c r="G603" s="1">
-        <x:v>50</x:v>
+        <x:v>81050</x:v>
       </x:c>
     </x:row>
     <x:row r="604" spans="1:7">
@@ -16815,7 +16818,7 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C604" s="1">
         <x:v>50</x:v>
@@ -16838,10 +16841,10 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16853,7 +16856,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16861,10 +16864,10 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16876,7 +16879,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -16884,7 +16887,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>50</x:v>
@@ -16896,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F607" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G607" s="1">
-        <x:v>14050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:7">
@@ -16907,10 +16910,10 @@
         <x:v>665</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C608" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D608" s="1">
         <x:v>0</x:v>
@@ -16919,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F608" s="1">
-        <x:v>2700</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G608" s="1">
-        <x:v>2700</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="609" spans="1:7">
@@ -16930,7 +16933,7 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C609" s="1">
         <x:v>0</x:v>
@@ -16942,10 +16945,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F609" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G609" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="610" spans="1:7">
@@ -16953,30 +16956,30 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C610" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D610" s="1">
-        <x:v>14446984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E610" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F610" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G610" s="1">
-        <x:v>14446984</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="611" spans="1:7">
       <x:c r="A611" s="1" t="s">
-        <x:v>667</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C611" s="1">
         <x:v>0</x:v>
@@ -16999,13 +17002,13 @@
         <x:v>668</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C612" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D612" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E612" s="1">
         <x:v>0</x:v>
@@ -17014,7 +17017,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G612" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="613" spans="1:7">
@@ -17022,22 +17025,22 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C613" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D613" s="1">
-        <x:v>2470488</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E613" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F613" s="1">
-        <x:v>11834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>2494372</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
@@ -17045,22 +17048,22 @@
         <x:v>670</x:v>
       </x:c>
       <x:c r="B614" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C614" s="1">
-        <x:v>100</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="D614" s="1">
-        <x:v>150640</x:v>
+        <x:v>2470488</x:v>
       </x:c>
       <x:c r="E614" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F614" s="1">
-        <x:v>0</x:v>
+        <x:v>11834</x:v>
       </x:c>
       <x:c r="G614" s="1">
-        <x:v>150740</x:v>
+        <x:v>2494372</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:7">
@@ -17068,13 +17071,13 @@
         <x:v>671</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D615" s="1">
-        <x:v>0</x:v>
+        <x:v>150640</x:v>
       </x:c>
       <x:c r="E615" s="1">
         <x:v>0</x:v>
@@ -17083,7 +17086,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>50</x:v>
+        <x:v>150740</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17091,7 +17094,7 @@
         <x:v>672</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C616" s="1">
         <x:v>50</x:v>
@@ -17117,7 +17120,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C617" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D617" s="1">
         <x:v>0</x:v>
@@ -17126,10 +17129,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F617" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G617" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="618" spans="1:7">
@@ -17137,10 +17140,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B618" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C618" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D618" s="1">
         <x:v>0</x:v>
@@ -17149,10 +17152,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F618" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G618" s="1">
-        <x:v>2550</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:7">
@@ -17160,7 +17163,7 @@
         <x:v>675</x:v>
       </x:c>
       <x:c r="B619" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C619" s="1">
         <x:v>50</x:v>
@@ -17172,10 +17175,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F619" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G619" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="620" spans="1:7">
@@ -17183,7 +17186,7 @@
         <x:v>676</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C620" s="1">
         <x:v>50</x:v>
@@ -17206,7 +17209,7 @@
         <x:v>677</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C621" s="1">
         <x:v>50</x:v>
@@ -17229,7 +17232,7 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C622" s="1">
         <x:v>50</x:v>
@@ -17252,22 +17255,22 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C623" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D623" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E623" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F623" s="1">
-        <x:v>6634</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G623" s="1">
-        <x:v>3982954</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:7">
@@ -17275,22 +17278,22 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C624" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D624" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E624" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F624" s="1">
-        <x:v>22000</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G624" s="1">
-        <x:v>22000</x:v>
+        <x:v>3982954</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:7">
@@ -17298,10 +17301,10 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D625" s="1">
         <x:v>0</x:v>
@@ -17310,10 +17313,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>5800</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>5850</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17321,7 +17324,7 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>683</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C626" s="1">
         <x:v>50</x:v>
@@ -17333,21 +17336,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
       <x:c r="A627" s="1" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="B627" s="1" t="s">
         <x:v>684</x:v>
       </x:c>
-      <x:c r="B627" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C627" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17356,10 +17359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17367,10 +17370,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>686</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C628" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D628" s="1">
         <x:v>0</x:v>
@@ -17379,18 +17382,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F628" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">
       <x:c r="A629" s="1" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="B629" s="1" t="s">
         <x:v>687</x:v>
-      </x:c>
-      <x:c r="B629" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C629" s="1">
         <x:v>50</x:v>
@@ -17413,7 +17416,7 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C630" s="1">
         <x:v>50</x:v>
@@ -17433,13 +17436,13 @@
     </x:row>
     <x:row r="631" spans="1:7">
       <x:c r="A631" s="1" t="s">
-        <x:v>688</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17448,10 +17451,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17459,10 +17462,10 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17471,10 +17474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17482,7 +17485,7 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C633" s="1">
         <x:v>50</x:v>
@@ -17505,10 +17508,10 @@
         <x:v>691</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C634" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D634" s="1">
         <x:v>0</x:v>
@@ -17517,10 +17520,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F634" s="1">
-        <x:v>68600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G634" s="1">
-        <x:v>71150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="635" spans="1:7">
@@ -17528,10 +17531,10 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C635" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D635" s="1">
         <x:v>0</x:v>
@@ -17540,10 +17543,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F635" s="1">
-        <x:v>0</x:v>
+        <x:v>68600</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>50</x:v>
+        <x:v>71150</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">
@@ -17551,7 +17554,7 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C636" s="1">
         <x:v>50</x:v>
@@ -17574,10 +17577,10 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C637" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D637" s="1">
         <x:v>0</x:v>
@@ -17586,10 +17589,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F637" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G637" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="638" spans="1:7">
@@ -17597,10 +17600,10 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B638" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C638" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D638" s="1">
         <x:v>0</x:v>
@@ -17609,10 +17612,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F638" s="1">
-        <x:v>58000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G638" s="1">
-        <x:v>58050</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="639" spans="1:7">
@@ -17620,10 +17623,10 @@
         <x:v>696</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C639" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D639" s="1">
         <x:v>0</x:v>
@@ -17632,10 +17635,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F639" s="1">
-        <x:v>1666</x:v>
+        <x:v>58000</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>3716</x:v>
+        <x:v>58050</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17643,30 +17646,30 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C640" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D640" s="1">
-        <x:v>74382</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E640" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F640" s="1">
-        <x:v>11668</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>86050</x:v>
+        <x:v>3716</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">
       <x:c r="A641" s="1" t="s">
-        <x:v>697</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C641" s="1">
         <x:v>0</x:v>
@@ -17678,10 +17681,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F641" s="1">
-        <x:v>0</x:v>
+        <x:v>11668</x:v>
       </x:c>
       <x:c r="G641" s="1">
-        <x:v>74382</x:v>
+        <x:v>86050</x:v>
       </x:c>
     </x:row>
     <x:row r="642" spans="1:7">
@@ -17692,10 +17695,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C642" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D642" s="1">
-        <x:v>0</x:v>
+        <x:v>74382</x:v>
       </x:c>
       <x:c r="E642" s="1">
         <x:v>0</x:v>
@@ -17704,7 +17707,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>50</x:v>
+        <x:v>74382</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
@@ -17712,13 +17715,13 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C643" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D643" s="1">
-        <x:v>105040</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E643" s="1">
         <x:v>0</x:v>
@@ -17727,7 +17730,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G643" s="1">
-        <x:v>105090</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:7">
@@ -17735,22 +17738,22 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>0</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>30600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>33550</x:v>
+        <x:v>105090</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17758,10 +17761,10 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D645" s="1">
         <x:v>0</x:v>
@@ -17770,10 +17773,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>0</x:v>
+        <x:v>30600</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>2550</x:v>
+        <x:v>33550</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17781,22 +17784,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D646" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E646" s="1">
-        <x:v>56045</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -17810,16 +17813,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D647" s="1">
-        <x:v>150562</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E647" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F647" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G647" s="1">
-        <x:v>150612</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="648" spans="1:7">
@@ -17827,13 +17830,13 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="B648" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C648" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D648" s="1">
-        <x:v>0</x:v>
+        <x:v>150562</x:v>
       </x:c>
       <x:c r="E648" s="1">
         <x:v>0</x:v>
@@ -17842,7 +17845,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G648" s="1">
-        <x:v>2550</x:v>
+        <x:v>150612</x:v>
       </x:c>
     </x:row>
     <x:row r="649" spans="1:7">
@@ -17850,10 +17853,10 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C649" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D649" s="1">
         <x:v>0</x:v>
@@ -17865,7 +17868,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -17873,10 +17876,10 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C650" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D650" s="1">
         <x:v>0</x:v>
@@ -17885,33 +17888,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F650" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
       <x:c r="A651" s="1" t="s">
-        <x:v>706</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C651" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D651" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E651" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F651" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
@@ -17925,7 +17928,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D652" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E652" s="1">
         <x:v>0</x:v>
@@ -17934,7 +17937,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17942,13 +17945,13 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D653" s="1">
-        <x:v>0</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="E653" s="1">
         <x:v>0</x:v>
@@ -17957,7 +17960,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>50</x:v>
+        <x:v>852561</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -17965,7 +17968,7 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C654" s="1">
         <x:v>50</x:v>
@@ -17988,13 +17991,13 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C655" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D655" s="1">
-        <x:v>2200000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E655" s="1">
         <x:v>0</x:v>
@@ -18003,7 +18006,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G655" s="1">
-        <x:v>2200000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:7">
@@ -18011,13 +18014,13 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C656" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>74852</x:v>
+        <x:v>2200000</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
@@ -18026,7 +18029,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>74902</x:v>
+        <x:v>2200000</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -18034,13 +18037,13 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C657" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D657" s="1">
-        <x:v>0</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="E657" s="1">
         <x:v>0</x:v>
@@ -18049,7 +18052,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>50</x:v>
+        <x:v>74902</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">
@@ -18057,7 +18060,7 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C658" s="1">
         <x:v>50</x:v>
@@ -18080,10 +18083,10 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C659" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D659" s="1">
         <x:v>0</x:v>
@@ -18095,7 +18098,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
@@ -18103,10 +18106,10 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D660" s="1">
         <x:v>0</x:v>
@@ -18118,7 +18121,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18126,10 +18129,10 @@
         <x:v>716</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
         <x:v>0</x:v>
@@ -18141,7 +18144,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18149,10 +18152,10 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>1050</x:v>
+        <x:v>10050</x:v>
       </x:c>
       <x:c r="D662" s="1">
         <x:v>0</x:v>
@@ -18161,10 +18164,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F662" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>2717</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18172,10 +18175,10 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C663" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D663" s="1">
         <x:v>0</x:v>
@@ -18184,10 +18187,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F663" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>50</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
@@ -18195,22 +18198,22 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C664" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D664" s="1">
-        <x:v>111599</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E664" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F664" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G664" s="1">
-        <x:v>114899</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:7">
@@ -18218,22 +18221,22 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C665" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D665" s="1">
-        <x:v>0</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="E665" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F665" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G665" s="1">
-        <x:v>50</x:v>
+        <x:v>114899</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:7">
@@ -18241,7 +18244,7 @@
         <x:v>721</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C666" s="1">
         <x:v>50</x:v>
@@ -18261,16 +18264,16 @@
     </x:row>
     <x:row r="667" spans="1:7">
       <x:c r="A667" s="1" t="s">
-        <x:v>721</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C667" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D667" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E667" s="1">
         <x:v>0</x:v>
@@ -18279,7 +18282,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
@@ -18287,13 +18290,13 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D668" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E668" s="1">
         <x:v>0</x:v>
@@ -18302,7 +18305,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18310,22 +18313,22 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C669" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D669" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E669" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F669" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
@@ -18333,22 +18336,22 @@
         <x:v>724</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C670" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D670" s="1">
-        <x:v>2263800</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E670" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F670" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G670" s="1">
-        <x:v>2263850</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="671" spans="1:7">
@@ -18356,13 +18359,13 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C671" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D671" s="1">
-        <x:v>0</x:v>
+        <x:v>2263800</x:v>
       </x:c>
       <x:c r="E671" s="1">
         <x:v>0</x:v>
@@ -18371,7 +18374,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>50</x:v>
+        <x:v>2263850</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
@@ -18379,7 +18382,7 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="B672" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C672" s="1">
         <x:v>50</x:v>
@@ -18391,10 +18394,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F672" s="1">
-        <x:v>19500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G672" s="1">
-        <x:v>19550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="673" spans="1:7">
@@ -18402,22 +18405,22 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C673" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D673" s="1">
-        <x:v>151234</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E673" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F673" s="1">
-        <x:v>55833</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="G673" s="1">
-        <x:v>213117</x:v>
+        <x:v>19550</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:7">
@@ -18425,22 +18428,22 @@
         <x:v>728</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C674" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D674" s="1">
-        <x:v>0</x:v>
+        <x:v>151234</x:v>
       </x:c>
       <x:c r="E674" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F674" s="1">
-        <x:v>0</x:v>
+        <x:v>55833</x:v>
       </x:c>
       <x:c r="G674" s="1">
-        <x:v>50</x:v>
+        <x:v>213117</x:v>
       </x:c>
     </x:row>
     <x:row r="675" spans="1:7">
@@ -18448,7 +18451,7 @@
         <x:v>729</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C675" s="1">
         <x:v>50</x:v>
@@ -18471,10 +18474,10 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C676" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D676" s="1">
         <x:v>0</x:v>
@@ -18483,10 +18486,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F676" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G676" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:7">
@@ -18494,22 +18497,22 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C677" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D677" s="1">
-        <x:v>380377</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E677" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F677" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>380377</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -18517,22 +18520,22 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C678" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D678" s="1">
-        <x:v>817169</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="E678" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F678" s="1">
-        <x:v>1668</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G678" s="1">
-        <x:v>820837</x:v>
+        <x:v>380377</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:7">
@@ -18540,22 +18543,22 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C679" s="1">
-        <x:v>11050</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D679" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E679" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F679" s="1">
-        <x:v>6242</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>17292</x:v>
+        <x:v>820837</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18563,10 +18566,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D680" s="1">
         <x:v>0</x:v>
@@ -18575,10 +18578,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>0</x:v>
+        <x:v>6242</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>50</x:v>
+        <x:v>17292</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -18586,7 +18589,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C681" s="1">
         <x:v>50</x:v>
@@ -18609,10 +18612,10 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -18621,10 +18624,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -18632,10 +18635,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -18644,10 +18647,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>25000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>25050</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -18655,7 +18658,7 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C684" s="1">
         <x:v>50</x:v>
@@ -18667,38 +18670,38 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>50</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
       <x:c r="A685" s="1" t="s">
-        <x:v>738</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E685" s="1">
-        <x:v>9196296</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
       <x:c r="A686" s="1" t="s">
-        <x:v>738</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
         <x:v>48</x:v>
@@ -18710,7 +18713,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E686" s="1">
-        <x:v>9196296</x:v>
+        <x:v>16359294</x:v>
       </x:c>
       <x:c r="F686" s="1">
         <x:v>0</x:v>
@@ -18724,7 +18727,7 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -18733,7 +18736,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E687" s="1">
-        <x:v>1531015</x:v>
+        <x:v>16359294</x:v>
       </x:c>
       <x:c r="F687" s="1">
         <x:v>0</x:v>
@@ -18747,22 +18750,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D688" s="1">
-        <x:v>157560</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E688" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>157610</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -18770,13 +18773,13 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C689" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D689" s="1">
-        <x:v>0</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="E689" s="1">
         <x:v>0</x:v>
@@ -18785,7 +18788,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G689" s="1">
-        <x:v>50</x:v>
+        <x:v>157610</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:7">
@@ -18793,13 +18796,13 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D690" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E690" s="1">
         <x:v>0</x:v>
@@ -18808,7 +18811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>5584432</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -18816,13 +18819,13 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D691" s="1">
-        <x:v>0</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E691" s="1">
         <x:v>0</x:v>
@@ -18831,7 +18834,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>50</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -18839,22 +18842,22 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>33050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D692" s="1">
-        <x:v>1789991</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E692" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>20501</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>1843542</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -18862,22 +18865,22 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C693" s="1">
-        <x:v>0</x:v>
+        <x:v>33050</x:v>
       </x:c>
       <x:c r="D693" s="1">
-        <x:v>0</x:v>
+        <x:v>1789991</x:v>
       </x:c>
       <x:c r="E693" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F693" s="1">
-        <x:v>2700</x:v>
+        <x:v>20501</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>2700</x:v>
+        <x:v>1843542</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
@@ -18885,22 +18888,22 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C694" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D694" s="1">
-        <x:v>1543316</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E694" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F694" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -18908,22 +18911,22 @@
         <x:v>747</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C695" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D695" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E695" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F695" s="1">
-        <x:v>14500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>14550</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
@@ -18931,7 +18934,7 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C696" s="1">
         <x:v>50</x:v>
@@ -18943,10 +18946,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18954,7 +18957,7 @@
         <x:v>749</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C697" s="1">
         <x:v>50</x:v>
@@ -18977,13 +18980,13 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C698" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D698" s="1">
-        <x:v>2150512</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E698" s="1">
         <x:v>0</x:v>
@@ -18992,7 +18995,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>2150562</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
@@ -19000,22 +19003,22 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C699" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D699" s="1">
-        <x:v>0</x:v>
+        <x:v>2150512</x:v>
       </x:c>
       <x:c r="E699" s="1">
-        <x:v>10135449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F699" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>0</x:v>
+        <x:v>2150562</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
@@ -19023,22 +19026,22 @@
         <x:v>752</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C700" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D700" s="1">
-        <x:v>103020</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E700" s="1">
-        <x:v>0</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="F700" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>106354</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -19046,36 +19049,36 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C701" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D701" s="1">
-        <x:v>75281</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="E701" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>75281</x:v>
+        <x:v>106354</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
       <x:c r="A702" s="1" t="s">
-        <x:v>753</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C702" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>0</x:v>
+        <x:v>75281</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
@@ -19084,7 +19087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>2500</x:v>
+        <x:v>75281</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -19092,13 +19095,13 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C703" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D703" s="1">
-        <x:v>182279</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E703" s="1">
         <x:v>0</x:v>
@@ -19107,7 +19110,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>182279</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
@@ -19115,22 +19118,22 @@
         <x:v>755</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C704" s="1">
-        <x:v>2050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D704" s="1">
-        <x:v>0</x:v>
+        <x:v>182279</x:v>
       </x:c>
       <x:c r="E704" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>27050</x:v>
+        <x:v>182279</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
@@ -19138,22 +19141,22 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>1050</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>902176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>7000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>910226</x:v>
+        <x:v>27050</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19161,22 +19164,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D706" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E706" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>25500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>25550</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -19196,10 +19199,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>0</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>50</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
@@ -19207,10 +19210,10 @@
         <x:v>759</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D708" s="1">
         <x:v>0</x:v>
@@ -19219,10 +19222,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -19230,7 +19233,7 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C709" s="1">
         <x:v>0</x:v>
@@ -19242,10 +19245,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>6200</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>6200</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -19253,10 +19256,10 @@
         <x:v>761</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C710" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D710" s="1">
         <x:v>0</x:v>
@@ -19265,10 +19268,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>50</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
@@ -19276,10 +19279,10 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C711" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D711" s="1">
         <x:v>0</x:v>
@@ -19291,7 +19294,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
@@ -19299,10 +19302,10 @@
         <x:v>763</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
@@ -19311,10 +19314,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>6650</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19322,22 +19325,22 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D713" s="1">
-        <x:v>2771797</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E713" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>2771797</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19345,22 +19348,22 @@
         <x:v>765</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C714" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D714" s="1">
-        <x:v>0</x:v>
+        <x:v>2771797</x:v>
       </x:c>
       <x:c r="E714" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>5000</x:v>
+        <x:v>2771797</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19368,10 +19371,10 @@
         <x:v>766</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D715" s="1">
         <x:v>0</x:v>
@@ -19380,10 +19383,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
@@ -19391,22 +19394,22 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>6550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D716" s="1">
-        <x:v>73673</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E716" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>83523</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19414,22 +19417,22 @@
         <x:v>768</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D717" s="1">
-        <x:v>0</x:v>
+        <x:v>73673</x:v>
       </x:c>
       <x:c r="E717" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>50</x:v>
+        <x:v>83523</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
@@ -19437,7 +19440,7 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C718" s="1">
         <x:v>50</x:v>
@@ -19460,10 +19463,10 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C719" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D719" s="1">
         <x:v>0</x:v>
@@ -19472,10 +19475,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F719" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G719" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="720" spans="1:7">
@@ -19483,10 +19486,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D720" s="1">
         <x:v>0</x:v>
@@ -19495,10 +19498,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>2700</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>2700</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
@@ -19506,10 +19509,10 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D721" s="1">
         <x:v>0</x:v>
@@ -19518,10 +19521,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F721" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
@@ -19529,10 +19532,10 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D722" s="1">
         <x:v>0</x:v>
@@ -19541,15 +19544,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F722" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>9350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
       <x:c r="A723" s="1" t="s">
-        <x:v>773</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
         <x:v>59</x:v>
@@ -19575,22 +19578,22 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D724" s="1">
-        <x:v>2835078</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E724" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>5500</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>2840628</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
@@ -19598,22 +19601,22 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C725" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D725" s="1">
-        <x:v>0</x:v>
+        <x:v>2835078</x:v>
       </x:c>
       <x:c r="E725" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F725" s="1">
-        <x:v>0</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>50</x:v>
+        <x:v>2840628</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
@@ -19621,7 +19624,7 @@
         <x:v>776</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C726" s="1">
         <x:v>50</x:v>
@@ -19633,10 +19636,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
@@ -19644,7 +19647,7 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C727" s="1">
         <x:v>50</x:v>
@@ -19656,10 +19659,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F727" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
@@ -19667,10 +19670,10 @@
         <x:v>778</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C728" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D728" s="1">
         <x:v>0</x:v>
@@ -19679,10 +19682,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>3300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
@@ -19693,7 +19696,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C729" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D729" s="1">
         <x:v>0</x:v>
@@ -19702,10 +19705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F729" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>50</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
@@ -19713,7 +19716,7 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C730" s="1">
         <x:v>50</x:v>
@@ -19725,10 +19728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F730" s="1">
-        <x:v>5700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
@@ -19736,7 +19739,7 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C731" s="1">
         <x:v>50</x:v>
@@ -19748,10 +19751,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F731" s="1">
-        <x:v>0</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
@@ -19759,7 +19762,7 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C732" s="1">
         <x:v>50</x:v>
@@ -19782,22 +19785,22 @@
         <x:v>783</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C733" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D733" s="1">
-        <x:v>2192272</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E733" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F733" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G733" s="1">
-        <x:v>2209772</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:7">
@@ -19805,13 +19808,13 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C734" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D734" s="1">
-        <x:v>0</x:v>
+        <x:v>2192272</x:v>
       </x:c>
       <x:c r="E734" s="1">
         <x:v>0</x:v>
@@ -19820,7 +19823,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>1000</x:v>
+        <x:v>2209772</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
@@ -19828,10 +19831,10 @@
         <x:v>785</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19840,10 +19843,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19851,22 +19854,22 @@
         <x:v>786</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D736" s="1">
-        <x:v>1015758</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E736" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>11500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>1029258</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
@@ -19874,22 +19877,22 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C737" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D737" s="1">
-        <x:v>0</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="E737" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F737" s="1">
-        <x:v>0</x:v>
+        <x:v>11500</x:v>
       </x:c>
       <x:c r="G737" s="1">
-        <x:v>50</x:v>
+        <x:v>1029258</x:v>
       </x:c>
     </x:row>
     <x:row r="738" spans="1:7">
@@ -19897,13 +19900,13 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D738" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E738" s="1">
         <x:v>0</x:v>
@@ -19912,7 +19915,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>40000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
@@ -19920,13 +19923,13 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C739" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D739" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E739" s="1">
         <x:v>0</x:v>
@@ -19935,7 +19938,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>1000</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
@@ -19943,22 +19946,22 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D740" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E740" s="1">
-        <x:v>424596</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F740" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
@@ -19966,22 +19969,22 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C741" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D741" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E741" s="1">
-        <x:v>0</x:v>
+        <x:v>424596</x:v>
       </x:c>
       <x:c r="F741" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
@@ -19989,10 +19992,10 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C742" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D742" s="1">
         <x:v>0</x:v>
@@ -20001,10 +20004,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F742" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>5200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
@@ -20012,10 +20015,10 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C743" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D743" s="1">
         <x:v>0</x:v>
@@ -20024,10 +20027,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F743" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G743" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="744" spans="1:7">
@@ -20035,7 +20038,7 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C744" s="1">
         <x:v>50</x:v>
@@ -20058,7 +20061,7 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C745" s="1">
         <x:v>50</x:v>
@@ -20070,10 +20073,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F745" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G745" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:7">
@@ -20081,22 +20084,22 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D746" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E746" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>3920589</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20104,13 +20107,13 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D747" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E747" s="1">
         <x:v>0</x:v>
@@ -20119,7 +20122,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>50</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
@@ -20127,10 +20130,10 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D748" s="1">
         <x:v>0</x:v>
@@ -20142,7 +20145,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
@@ -20150,10 +20153,10 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C749" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D749" s="1">
         <x:v>0</x:v>
@@ -20165,7 +20168,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
@@ -20173,7 +20176,7 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C750" s="1">
         <x:v>50</x:v>
@@ -20196,10 +20199,10 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20208,10 +20211,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F751" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>9334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
@@ -20219,10 +20222,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>1050</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20231,10 +20234,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>1050</x:v>
+        <x:v>9334</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20245,7 +20248,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20257,7 +20260,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
@@ -20265,7 +20268,7 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C754" s="1">
         <x:v>50</x:v>
@@ -20288,13 +20291,13 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D755" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E755" s="1">
         <x:v>0</x:v>
@@ -20303,7 +20306,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -20311,13 +20314,13 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D756" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E756" s="1">
         <x:v>0</x:v>
@@ -20326,7 +20329,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>50</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
@@ -20334,10 +20337,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>19600</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20346,10 +20349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>36600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20357,10 +20360,10 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>19600</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20369,10 +20372,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>50</x:v>
+        <x:v>36600</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
@@ -20380,7 +20383,7 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C759" s="1">
         <x:v>50</x:v>
@@ -20403,7 +20406,7 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C760" s="1">
         <x:v>50</x:v>
@@ -20426,13 +20429,13 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C761" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D761" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E761" s="1">
         <x:v>0</x:v>
@@ -20441,7 +20444,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
@@ -20449,13 +20452,13 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D762" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E762" s="1">
         <x:v>0</x:v>
@@ -20464,7 +20467,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>50</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
@@ -20472,10 +20475,10 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C763" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D763" s="1">
         <x:v>0</x:v>
@@ -20484,10 +20487,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F763" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G763" s="1">
-        <x:v>30000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="764" spans="1:7">
@@ -20495,10 +20498,10 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C764" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D764" s="1">
         <x:v>0</x:v>
@@ -20507,10 +20510,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F764" s="1">
-        <x:v>0</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G764" s="1">
-        <x:v>50</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:7">
@@ -20518,22 +20521,22 @@
         <x:v>815</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C765" s="1">
-        <x:v>19050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D765" s="1">
-        <x:v>2700000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E765" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F765" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G765" s="1">
-        <x:v>2721550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:7">
@@ -20541,22 +20544,22 @@
         <x:v>816</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C766" s="1">
-        <x:v>3500</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D766" s="1">
-        <x:v>0</x:v>
+        <x:v>2700000</x:v>
       </x:c>
       <x:c r="E766" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>3500</x:v>
+        <x:v>2721550</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
@@ -20564,10 +20567,10 @@
         <x:v>817</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C767" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D767" s="1">
         <x:v>0</x:v>
@@ -20579,18 +20582,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G767" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:7">
       <x:c r="A768" s="1" t="s">
-        <x:v>817</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C768" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D768" s="1">
         <x:v>0</x:v>
@@ -20599,10 +20602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
@@ -20610,10 +20613,10 @@
         <x:v>818</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C769" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D769" s="1">
         <x:v>0</x:v>
@@ -20622,10 +20625,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F769" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
@@ -20633,10 +20636,10 @@
         <x:v>819</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C770" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D770" s="1">
         <x:v>0</x:v>
@@ -20648,7 +20651,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G770" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="771" spans="1:7">
@@ -20656,10 +20659,10 @@
         <x:v>820</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C771" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D771" s="1">
         <x:v>0</x:v>
@@ -20671,7 +20674,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G771" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="772" spans="1:7">
@@ -20679,10 +20682,10 @@
         <x:v>821</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C772" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D772" s="1">
         <x:v>0</x:v>
@@ -20691,10 +20694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F772" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G772" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:7">
@@ -20702,10 +20705,10 @@
         <x:v>822</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C773" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D773" s="1">
         <x:v>0</x:v>
@@ -20714,10 +20717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F773" s="1">
-        <x:v>5000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G773" s="1">
-        <x:v>5050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="774" spans="1:7">
@@ -20725,7 +20728,7 @@
         <x:v>823</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C774" s="1">
         <x:v>50</x:v>
@@ -20737,10 +20740,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F774" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
@@ -20748,10 +20751,10 @@
         <x:v>824</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C775" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D775" s="1">
         <x:v>0</x:v>
@@ -20760,10 +20763,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
@@ -20771,10 +20774,10 @@
         <x:v>825</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C776" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D776" s="1">
         <x:v>0</x:v>
@@ -20783,10 +20786,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
@@ -20794,7 +20797,7 @@
         <x:v>826</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C777" s="1">
         <x:v>50</x:v>
@@ -20817,13 +20820,13 @@
         <x:v>827</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C778" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D778" s="1">
-        <x:v>1962970</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E778" s="1">
         <x:v>0</x:v>
@@ -20832,7 +20835,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>1963020</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
@@ -20840,13 +20843,13 @@
         <x:v>828</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D779" s="1">
-        <x:v>0</x:v>
+        <x:v>1962970</x:v>
       </x:c>
       <x:c r="E779" s="1">
         <x:v>0</x:v>
@@ -20855,7 +20858,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G779" s="1">
-        <x:v>50</x:v>
+        <x:v>1963020</x:v>
       </x:c>
     </x:row>
     <x:row r="780" spans="1:7">
@@ -20863,7 +20866,7 @@
         <x:v>829</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C780" s="1">
         <x:v>50</x:v>
@@ -20872,7 +20875,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E780" s="1">
-        <x:v>9196296</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F780" s="1">
         <x:v>0</x:v>
@@ -20886,22 +20889,22 @@
         <x:v>830</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C781" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D781" s="1">
-        <x:v>487174</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E781" s="1">
-        <x:v>0</x:v>
+        <x:v>16359294</x:v>
       </x:c>
       <x:c r="F781" s="1">
-        <x:v>8500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>496674</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
@@ -20909,22 +20912,22 @@
         <x:v>831</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C782" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D782" s="1">
-        <x:v>0</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="E782" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F782" s="1">
-        <x:v>0</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G782" s="1">
-        <x:v>50</x:v>
+        <x:v>496674</x:v>
       </x:c>
     </x:row>
     <x:row r="783" spans="1:7">
@@ -20932,7 +20935,7 @@
         <x:v>832</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C783" s="1">
         <x:v>50</x:v>
@@ -20944,10 +20947,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F783" s="1">
-        <x:v>4999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G783" s="1">
-        <x:v>5049</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="784" spans="1:7">
@@ -20955,10 +20958,10 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B784" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C784" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D784" s="1">
         <x:v>0</x:v>
@@ -20967,10 +20970,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F784" s="1">
-        <x:v>16500</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G784" s="1">
-        <x:v>16500</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="785" spans="1:7">
@@ -20978,10 +20981,10 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="B785" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C785" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D785" s="1">
         <x:v>0</x:v>
@@ -20990,10 +20993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F785" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G785" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="786" spans="1:7">
@@ -21001,7 +21004,7 @@
         <x:v>835</x:v>
       </x:c>
       <x:c r="B786" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C786" s="1">
         <x:v>50</x:v>
@@ -21024,7 +21027,7 @@
         <x:v>836</x:v>
       </x:c>
       <x:c r="B787" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C787" s="1">
         <x:v>50</x:v>
@@ -21047,7 +21050,7 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B788" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C788" s="1">
         <x:v>50</x:v>
@@ -21059,10 +21062,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F788" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G788" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="789" spans="1:7">
@@ -21070,7 +21073,7 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="B789" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C789" s="1">
         <x:v>50</x:v>
@@ -21082,10 +21085,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F789" s="1">
-        <x:v>1500</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G789" s="1">
-        <x:v>1550</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="790" spans="1:7">
@@ -21093,7 +21096,7 @@
         <x:v>839</x:v>
       </x:c>
       <x:c r="B790" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C790" s="1">
         <x:v>50</x:v>
@@ -21105,10 +21108,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F790" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G790" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="791" spans="1:7">
@@ -21116,10 +21119,10 @@
         <x:v>840</x:v>
       </x:c>
       <x:c r="B791" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C791" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D791" s="1">
         <x:v>0</x:v>
@@ -21128,10 +21131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F791" s="1">
-        <x:v>37300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G791" s="1">
-        <x:v>48150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="792" spans="1:7">
@@ -21139,10 +21142,10 @@
         <x:v>841</x:v>
       </x:c>
       <x:c r="B792" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C792" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D792" s="1">
         <x:v>0</x:v>
@@ -21151,10 +21154,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F792" s="1">
-        <x:v>83</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G792" s="1">
-        <x:v>83</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="793" spans="1:7">
@@ -21162,36 +21165,36 @@
         <x:v>842</x:v>
       </x:c>
       <x:c r="B793" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C793" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D793" s="1">
-        <x:v>74852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E793" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F793" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G793" s="1">
-        <x:v>74852</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="794" spans="1:7">
       <x:c r="A794" s="1" t="s">
-        <x:v>842</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="B794" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C794" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D794" s="1">
-        <x:v>0</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="E794" s="1">
         <x:v>0</x:v>
@@ -21200,7 +21203,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G794" s="1">
-        <x:v>50</x:v>
+        <x:v>74852</x:v>
       </x:c>
     </x:row>
     <x:row r="795" spans="1:7">
@@ -21208,7 +21211,7 @@
         <x:v>843</x:v>
       </x:c>
       <x:c r="B795" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C795" s="1">
         <x:v>50</x:v>
@@ -21231,7 +21234,7 @@
         <x:v>844</x:v>
       </x:c>
       <x:c r="B796" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C796" s="1">
         <x:v>50</x:v>
@@ -21254,10 +21257,10 @@
         <x:v>845</x:v>
       </x:c>
       <x:c r="B797" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C797" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D797" s="1">
         <x:v>0</x:v>
@@ -21266,10 +21269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F797" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G797" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="798" spans="1:7">
@@ -21277,21 +21280,44 @@
         <x:v>846</x:v>
       </x:c>
       <x:c r="B798" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C798" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D798" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E798" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F798" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G798" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="799" spans="1:7">
+      <x:c r="A799" s="1" t="s">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="B799" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C798" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D798" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E798" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F798" s="1">
+      <x:c r="C799" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D799" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E799" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F799" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G798" s="1">
+      <x:c r="G799" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -12793,22 +12793,22 @@
         <x:v>485</x:v>
       </x:c>
       <x:c r="B429" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C429" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D429" s="1">
-        <x:v>74602</x:v>
+        <x:v>149204</x:v>
       </x:c>
       <x:c r="E429" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F429" s="1">
-        <x:v>0</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G429" s="1">
-        <x:v>74602</x:v>
+        <x:v>182854</x:v>
       </x:c>
     </x:row>
     <x:row r="430" spans="1:7">
@@ -12816,22 +12816,22 @@
         <x:v>485</x:v>
       </x:c>
       <x:c r="B430" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C430" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D430" s="1">
-        <x:v>149204</x:v>
+        <x:v>74602</x:v>
       </x:c>
       <x:c r="E430" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F430" s="1">
-        <x:v>33600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G430" s="1">
-        <x:v>182854</x:v>
+        <x:v>74602</x:v>
       </x:c>
     </x:row>
     <x:row r="431" spans="1:7">
@@ -18267,13 +18267,13 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C667" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D667" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E667" s="1">
         <x:v>0</x:v>
@@ -18282,7 +18282,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
@@ -18290,13 +18290,13 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D668" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E668" s="1">
         <x:v>0</x:v>
@@ -18305,7 +18305,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -19555,22 +19555,22 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D723" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E723" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F723" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
@@ -19578,22 +19578,22 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D724" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E724" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17439,10 +17439,10 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17451,10 +17451,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17462,10 +17462,10 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17474,10 +17474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -18267,13 +18267,13 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C667" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D667" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E667" s="1">
         <x:v>0</x:v>
@@ -18282,7 +18282,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
@@ -18290,13 +18290,13 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D668" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E668" s="1">
         <x:v>0</x:v>
@@ -18305,7 +18305,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18704,7 +18704,7 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>0</x:v>
@@ -18727,7 +18727,7 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -1501,6 +1501,9 @@
     <x:t>MANCHIN, JOE III</x:t>
   </x:si>
   <x:si>
+    <x:t>MANN, TRACEY ROBERT</x:t>
+  </x:si>
+  <x:si>
     <x:t>MANSHARAMANI, VIKRAM</x:t>
   </x:si>
   <x:si>
@@ -2441,6 +2444,9 @@
   </x:si>
   <x:si>
     <x:t>WAGNER, ANN L.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
   </x:si>
   <x:si>
     <x:t>WALBERG, TIMOTHY L REP</x:t>
@@ -2628,8 +2634,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G799" totalsRowShown="0">
-  <x:autoFilter ref="A1:G799"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G801" totalsRowShown="0">
+  <x:autoFilter ref="A1:G801"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2931,7 +2937,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G799"/>
+  <x:dimension ref="A1:G801"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3527,7 +3533,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1050</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>3009467</x:v>
@@ -3539,7 +3545,7 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="G26" s="1">
-        <x:v>3025517</x:v>
+        <x:v>3030517</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
@@ -3757,7 +3763,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>0</x:v>
@@ -3769,7 +3775,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G36" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
@@ -4769,7 +4775,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="C80" s="1">
-        <x:v>3000</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="D80" s="1">
         <x:v>666234</x:v>
@@ -4781,7 +4787,7 @@
         <x:v>15668</x:v>
       </x:c>
       <x:c r="G80" s="1">
-        <x:v>684902</x:v>
+        <x:v>687402</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
@@ -7621,7 +7627,7 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="C204" s="1">
-        <x:v>24250</x:v>
+        <x:v>29250</x:v>
       </x:c>
       <x:c r="D204" s="1">
         <x:v>388752</x:v>
@@ -7633,7 +7639,7 @@
         <x:v>75973</x:v>
       </x:c>
       <x:c r="G204" s="1">
-        <x:v>488975</x:v>
+        <x:v>493975</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:7">
@@ -9116,7 +9122,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C269" s="1">
-        <x:v>4550</x:v>
+        <x:v>9550</x:v>
       </x:c>
       <x:c r="D269" s="1">
         <x:v>755176</x:v>
@@ -9128,7 +9134,7 @@
         <x:v>127300</x:v>
       </x:c>
       <x:c r="G269" s="1">
-        <x:v>887026</x:v>
+        <x:v>892026</x:v>
       </x:c>
     </x:row>
     <x:row r="270" spans="1:7">
@@ -9136,13 +9142,13 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B270" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C270" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D270" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E270" s="1">
         <x:v>0</x:v>
@@ -9151,7 +9157,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G270" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="271" spans="1:7">
@@ -9159,13 +9165,13 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B271" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C271" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D271" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E271" s="1">
         <x:v>0</x:v>
@@ -9174,7 +9180,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G271" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="272" spans="1:7">
@@ -9691,7 +9697,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="C294" s="1">
-        <x:v>1500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D294" s="1">
         <x:v>74932</x:v>
@@ -9703,7 +9709,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G294" s="1">
-        <x:v>76432</x:v>
+        <x:v>78932</x:v>
       </x:c>
     </x:row>
     <x:row r="295" spans="1:7">
@@ -12244,7 +12250,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C405" s="1">
-        <x:v>10500</x:v>
+        <x:v>13500</x:v>
       </x:c>
       <x:c r="D405" s="1">
         <x:v>0</x:v>
@@ -12256,7 +12262,7 @@
         <x:v>6666</x:v>
       </x:c>
       <x:c r="G405" s="1">
-        <x:v>17166</x:v>
+        <x:v>20166</x:v>
       </x:c>
     </x:row>
     <x:row r="406" spans="1:7">
@@ -13046,10 +13052,10 @@
         <x:v>495</x:v>
       </x:c>
       <x:c r="B440" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C440" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D440" s="1">
         <x:v>0</x:v>
@@ -13058,10 +13064,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F440" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G440" s="1">
-        <x:v>1000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="441" spans="1:7">
@@ -13069,10 +13075,10 @@
         <x:v>496</x:v>
       </x:c>
       <x:c r="B441" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C441" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D441" s="1">
         <x:v>0</x:v>
@@ -13081,10 +13087,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F441" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G441" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="442" spans="1:7">
@@ -13092,7 +13098,7 @@
         <x:v>497</x:v>
       </x:c>
       <x:c r="B442" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C442" s="1">
         <x:v>50</x:v>
@@ -13104,10 +13110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F442" s="1">
-        <x:v>1715</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G442" s="1">
-        <x:v>1765</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="443" spans="1:7">
@@ -13115,10 +13121,10 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="B443" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C443" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D443" s="1">
         <x:v>0</x:v>
@@ -13127,10 +13133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F443" s="1">
-        <x:v>14000</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="G443" s="1">
-        <x:v>15050</x:v>
+        <x:v>1765</x:v>
       </x:c>
     </x:row>
     <x:row r="444" spans="1:7">
@@ -13138,10 +13144,10 @@
         <x:v>499</x:v>
       </x:c>
       <x:c r="B444" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C444" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D444" s="1">
         <x:v>0</x:v>
@@ -13150,10 +13156,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F444" s="1">
-        <x:v>6600</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G444" s="1">
-        <x:v>6650</x:v>
+        <x:v>15050</x:v>
       </x:c>
     </x:row>
     <x:row r="445" spans="1:7">
@@ -13161,7 +13167,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="B445" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C445" s="1">
         <x:v>50</x:v>
@@ -13173,10 +13179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F445" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G445" s="1">
-        <x:v>50</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="446" spans="1:7">
@@ -13184,22 +13190,22 @@
         <x:v>501</x:v>
       </x:c>
       <x:c r="B446" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C446" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D446" s="1">
-        <x:v>582915</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E446" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F446" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G446" s="1">
-        <x:v>591215</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="447" spans="1:7">
@@ -13207,22 +13213,22 @@
         <x:v>502</x:v>
       </x:c>
       <x:c r="B447" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C447" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D447" s="1">
-        <x:v>0</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="E447" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F447" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G447" s="1">
-        <x:v>50</x:v>
+        <x:v>591215</x:v>
       </x:c>
     </x:row>
     <x:row r="448" spans="1:7">
@@ -13230,7 +13236,7 @@
         <x:v>503</x:v>
       </x:c>
       <x:c r="B448" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C448" s="1">
         <x:v>50</x:v>
@@ -13253,13 +13259,13 @@
         <x:v>504</x:v>
       </x:c>
       <x:c r="B449" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C449" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D449" s="1">
-        <x:v>76114</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E449" s="1">
         <x:v>0</x:v>
@@ -13268,7 +13274,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G449" s="1">
-        <x:v>77164</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="450" spans="1:7">
@@ -13276,22 +13282,22 @@
         <x:v>505</x:v>
       </x:c>
       <x:c r="B450" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C450" s="1">
-        <x:v>0</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D450" s="1">
-        <x:v>112913</x:v>
+        <x:v>76114</x:v>
       </x:c>
       <x:c r="E450" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F450" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G450" s="1">
-        <x:v>117913</x:v>
+        <x:v>77164</x:v>
       </x:c>
     </x:row>
     <x:row r="451" spans="1:7">
@@ -13299,22 +13305,22 @@
         <x:v>506</x:v>
       </x:c>
       <x:c r="B451" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C451" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D451" s="1">
-        <x:v>0</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="E451" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F451" s="1">
-        <x:v>250</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G451" s="1">
-        <x:v>250</x:v>
+        <x:v>117913</x:v>
       </x:c>
     </x:row>
     <x:row r="452" spans="1:7">
@@ -13322,7 +13328,7 @@
         <x:v>507</x:v>
       </x:c>
       <x:c r="B452" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C452" s="1">
         <x:v>0</x:v>
@@ -13334,10 +13340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F452" s="1">
-        <x:v>2000</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G452" s="1">
-        <x:v>2000</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="453" spans="1:7">
@@ -13345,10 +13351,10 @@
         <x:v>508</x:v>
       </x:c>
       <x:c r="B453" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C453" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D453" s="1">
         <x:v>0</x:v>
@@ -13357,10 +13363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F453" s="1">
-        <x:v>46300</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G453" s="1">
-        <x:v>46350</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="454" spans="1:7">
@@ -13368,7 +13374,7 @@
         <x:v>509</x:v>
       </x:c>
       <x:c r="B454" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C454" s="1">
         <x:v>50</x:v>
@@ -13380,10 +13386,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F454" s="1">
-        <x:v>500</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="G454" s="1">
-        <x:v>550</x:v>
+        <x:v>46350</x:v>
       </x:c>
     </x:row>
     <x:row r="455" spans="1:7">
@@ -13391,22 +13397,22 @@
         <x:v>510</x:v>
       </x:c>
       <x:c r="B455" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C455" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D455" s="1">
-        <x:v>75226</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E455" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F455" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G455" s="1">
-        <x:v>76726</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="456" spans="1:7">
@@ -13414,22 +13420,22 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="B456" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C456" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D456" s="1">
-        <x:v>0</x:v>
+        <x:v>75226</x:v>
       </x:c>
       <x:c r="E456" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F456" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G456" s="1">
-        <x:v>300</x:v>
+        <x:v>79226</x:v>
       </x:c>
     </x:row>
     <x:row r="457" spans="1:7">
@@ -13437,7 +13443,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="B457" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C457" s="1">
         <x:v>50</x:v>
@@ -13449,10 +13455,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F457" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G457" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="458" spans="1:7">
@@ -13460,7 +13466,7 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B458" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C458" s="1">
         <x:v>50</x:v>
@@ -13472,10 +13478,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F458" s="1">
-        <x:v>7900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G458" s="1">
-        <x:v>7950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:7">
@@ -13483,22 +13489,22 @@
         <x:v>514</x:v>
       </x:c>
       <x:c r="B459" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C459" s="1">
-        <x:v>13300</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D459" s="1">
-        <x:v>104910</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E459" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F459" s="1">
-        <x:v>20050</x:v>
+        <x:v>7900</x:v>
       </x:c>
       <x:c r="G459" s="1">
-        <x:v>138260</x:v>
+        <x:v>7950</x:v>
       </x:c>
     </x:row>
     <x:row r="460" spans="1:7">
@@ -13506,22 +13512,22 @@
         <x:v>515</x:v>
       </x:c>
       <x:c r="B460" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C460" s="1">
-        <x:v>0</x:v>
+        <x:v>13300</x:v>
       </x:c>
       <x:c r="D460" s="1">
-        <x:v>0</x:v>
+        <x:v>104910</x:v>
       </x:c>
       <x:c r="E460" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F460" s="1">
-        <x:v>250</x:v>
+        <x:v>20050</x:v>
       </x:c>
       <x:c r="G460" s="1">
-        <x:v>250</x:v>
+        <x:v>138260</x:v>
       </x:c>
     </x:row>
     <x:row r="461" spans="1:7">
@@ -13529,10 +13535,10 @@
         <x:v>516</x:v>
       </x:c>
       <x:c r="B461" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C461" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D461" s="1">
         <x:v>0</x:v>
@@ -13541,10 +13547,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F461" s="1">
-        <x:v>1500</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G461" s="1">
-        <x:v>6500</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="462" spans="1:7">
@@ -13552,10 +13558,10 @@
         <x:v>517</x:v>
       </x:c>
       <x:c r="B462" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C462" s="1">
-        <x:v>1000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D462" s="1">
         <x:v>0</x:v>
@@ -13564,10 +13570,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F462" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G462" s="1">
-        <x:v>1000</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="463" spans="1:7">
@@ -13575,10 +13581,10 @@
         <x:v>518</x:v>
       </x:c>
       <x:c r="B463" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C463" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D463" s="1">
         <x:v>0</x:v>
@@ -13590,7 +13596,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G463" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="464" spans="1:7">
@@ -13598,7 +13604,7 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B464" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C464" s="1">
         <x:v>50</x:v>
@@ -13621,13 +13627,13 @@
         <x:v>520</x:v>
       </x:c>
       <x:c r="B465" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C465" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D465" s="1">
-        <x:v>382680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E465" s="1">
         <x:v>0</x:v>
@@ -13636,7 +13642,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G465" s="1">
-        <x:v>382680</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="466" spans="1:7">
@@ -13644,22 +13650,22 @@
         <x:v>521</x:v>
       </x:c>
       <x:c r="B466" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C466" s="1">
-        <x:v>8670</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D466" s="1">
-        <x:v>126626</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="E466" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F466" s="1">
-        <x:v>8000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G466" s="1">
-        <x:v>143296</x:v>
+        <x:v>382680</x:v>
       </x:c>
     </x:row>
     <x:row r="467" spans="1:7">
@@ -13667,22 +13673,22 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B467" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C467" s="1">
-        <x:v>50</x:v>
+        <x:v>8670</x:v>
       </x:c>
       <x:c r="D467" s="1">
-        <x:v>0</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="E467" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F467" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G467" s="1">
-        <x:v>50</x:v>
+        <x:v>143296</x:v>
       </x:c>
     </x:row>
     <x:row r="468" spans="1:7">
@@ -13690,13 +13696,13 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B468" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C468" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D468" s="1">
-        <x:v>1013834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E468" s="1">
         <x:v>0</x:v>
@@ -13705,7 +13711,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G468" s="1">
-        <x:v>1013834</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="469" spans="1:7">
@@ -13713,22 +13719,22 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C469" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
-        <x:v>0</x:v>
+        <x:v>1013834</x:v>
       </x:c>
       <x:c r="E469" s="1">
-        <x:v>268690</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>0</x:v>
+        <x:v>1013834</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -13736,22 +13742,22 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E470" s="1">
-        <x:v>0</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="F470" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -13759,10 +13765,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -13771,10 +13777,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -13782,10 +13788,10 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -13794,10 +13800,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -13805,7 +13811,7 @@
         <x:v>528</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C473" s="1">
         <x:v>50</x:v>
@@ -13817,10 +13823,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -13828,22 +13834,22 @@
         <x:v>529</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C474" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D474" s="1">
-        <x:v>923885</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E474" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F474" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G474" s="1">
-        <x:v>923885</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="475" spans="1:7">
@@ -13851,13 +13857,13 @@
         <x:v>530</x:v>
       </x:c>
       <x:c r="B475" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C475" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D475" s="1">
-        <x:v>92320</x:v>
+        <x:v>923885</x:v>
       </x:c>
       <x:c r="E475" s="1">
         <x:v>0</x:v>
@@ -13866,7 +13872,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G475" s="1">
-        <x:v>95870</x:v>
+        <x:v>923885</x:v>
       </x:c>
     </x:row>
     <x:row r="476" spans="1:7">
@@ -13874,22 +13880,22 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B476" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C476" s="1">
-        <x:v>0</x:v>
+        <x:v>8550</x:v>
       </x:c>
       <x:c r="D476" s="1">
-        <x:v>6471279</x:v>
+        <x:v>92320</x:v>
       </x:c>
       <x:c r="E476" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F476" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G476" s="1">
-        <x:v>6474779</x:v>
+        <x:v>100870</x:v>
       </x:c>
     </x:row>
     <x:row r="477" spans="1:7">
@@ -13897,22 +13903,22 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>1550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D477" s="1">
-        <x:v>512918</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="E477" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>514468</x:v>
+        <x:v>6474779</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -13920,13 +13926,13 @@
         <x:v>533</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C478" s="1">
         <x:v>1550</x:v>
       </x:c>
       <x:c r="D478" s="1">
-        <x:v>0</x:v>
+        <x:v>512918</x:v>
       </x:c>
       <x:c r="E478" s="1">
         <x:v>0</x:v>
@@ -13935,7 +13941,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>1550</x:v>
+        <x:v>514468</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -13943,10 +13949,10 @@
         <x:v>534</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -13958,7 +13964,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -13966,13 +13972,13 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B480" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C480" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D480" s="1">
-        <x:v>504020</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E480" s="1">
         <x:v>0</x:v>
@@ -13981,7 +13987,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G480" s="1">
-        <x:v>504020</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="481" spans="1:7">
@@ -13989,13 +13995,13 @@
         <x:v>536</x:v>
       </x:c>
       <x:c r="B481" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C481" s="1">
-        <x:v>4050</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D481" s="1">
-        <x:v>0</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="E481" s="1">
         <x:v>0</x:v>
@@ -14004,7 +14010,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G481" s="1">
-        <x:v>4050</x:v>
+        <x:v>506520</x:v>
       </x:c>
     </x:row>
     <x:row r="482" spans="1:7">
@@ -14012,10 +14018,10 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="B482" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C482" s="1">
-        <x:v>50</x:v>
+        <x:v>4050</x:v>
       </x:c>
       <x:c r="D482" s="1">
         <x:v>0</x:v>
@@ -14027,7 +14033,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G482" s="1">
-        <x:v>50</x:v>
+        <x:v>4050</x:v>
       </x:c>
     </x:row>
     <x:row r="483" spans="1:7">
@@ -14035,7 +14041,7 @@
         <x:v>538</x:v>
       </x:c>
       <x:c r="B483" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C483" s="1">
         <x:v>50</x:v>
@@ -14058,10 +14064,10 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="B484" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C484" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D484" s="1">
         <x:v>0</x:v>
@@ -14070,10 +14076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F484" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G484" s="1">
-        <x:v>3667</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="485" spans="1:7">
@@ -14081,10 +14087,10 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="B485" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C485" s="1">
-        <x:v>1000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D485" s="1">
         <x:v>0</x:v>
@@ -14093,10 +14099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F485" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G485" s="1">
-        <x:v>1000</x:v>
+        <x:v>3667</x:v>
       </x:c>
     </x:row>
     <x:row r="486" spans="1:7">
@@ -14104,22 +14110,22 @@
         <x:v>541</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C486" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D486" s="1">
-        <x:v>107940</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E486" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F486" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G486" s="1">
-        <x:v>109940</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="487" spans="1:7">
@@ -14127,22 +14133,22 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="B487" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C487" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D487" s="1">
-        <x:v>0</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="E487" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F487" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G487" s="1">
-        <x:v>50</x:v>
+        <x:v>109940</x:v>
       </x:c>
     </x:row>
     <x:row r="488" spans="1:7">
@@ -14150,10 +14156,10 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B488" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C488" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D488" s="1">
         <x:v>0</x:v>
@@ -14162,10 +14168,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F488" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G488" s="1">
-        <x:v>7200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="489" spans="1:7">
@@ -14173,10 +14179,10 @@
         <x:v>544</x:v>
       </x:c>
       <x:c r="B489" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C489" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D489" s="1">
         <x:v>0</x:v>
@@ -14185,10 +14191,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F489" s="1">
-        <x:v>2000</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G489" s="1">
-        <x:v>2000</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="490" spans="1:7">
@@ -14196,10 +14202,10 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="B490" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C490" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D490" s="1">
         <x:v>0</x:v>
@@ -14208,10 +14214,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F490" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G490" s="1">
-        <x:v>2500</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="491" spans="1:7">
@@ -14219,10 +14225,10 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="B491" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C491" s="1">
-        <x:v>5050</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D491" s="1">
         <x:v>0</x:v>
@@ -14231,10 +14237,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F491" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G491" s="1">
-        <x:v>6050</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="492" spans="1:7">
@@ -14242,10 +14248,10 @@
         <x:v>547</x:v>
       </x:c>
       <x:c r="B492" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C492" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D492" s="1">
         <x:v>0</x:v>
@@ -14254,10 +14260,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F492" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G492" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
     </x:row>
     <x:row r="493" spans="1:7">
@@ -14265,13 +14271,13 @@
         <x:v>548</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C493" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D493" s="1">
-        <x:v>800044</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E493" s="1">
         <x:v>0</x:v>
@@ -14280,7 +14286,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G493" s="1">
-        <x:v>801044</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="494" spans="1:7">
@@ -14288,22 +14294,22 @@
         <x:v>549</x:v>
       </x:c>
       <x:c r="B494" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C494" s="1">
-        <x:v>3500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D494" s="1">
-        <x:v>50315254</x:v>
+        <x:v>800044</x:v>
       </x:c>
       <x:c r="E494" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F494" s="1">
-        <x:v>8000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G494" s="1">
-        <x:v>50326754</x:v>
+        <x:v>801044</x:v>
       </x:c>
     </x:row>
     <x:row r="495" spans="1:7">
@@ -14311,22 +14317,22 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="B495" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C495" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D495" s="1">
-        <x:v>0</x:v>
+        <x:v>50315254</x:v>
       </x:c>
       <x:c r="E495" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F495" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G495" s="1">
-        <x:v>50</x:v>
+        <x:v>50326754</x:v>
       </x:c>
     </x:row>
     <x:row r="496" spans="1:7">
@@ -14334,13 +14340,13 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C496" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D496" s="1">
-        <x:v>726377</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E496" s="1">
         <x:v>0</x:v>
@@ -14349,7 +14355,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G496" s="1">
-        <x:v>726377</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="497" spans="1:7">
@@ -14357,22 +14363,22 @@
         <x:v>552</x:v>
       </x:c>
       <x:c r="B497" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C497" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D497" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="E497" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F497" s="1">
-        <x:v>14600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G497" s="1">
-        <x:v>685549</x:v>
+        <x:v>726377</x:v>
       </x:c>
     </x:row>
     <x:row r="498" spans="1:7">
@@ -14380,22 +14386,22 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B498" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C498" s="1">
-        <x:v>1000</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D498" s="1">
-        <x:v>0</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="E498" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F498" s="1">
-        <x:v>0</x:v>
+        <x:v>14600</x:v>
       </x:c>
       <x:c r="G498" s="1">
-        <x:v>1000</x:v>
+        <x:v>685549</x:v>
       </x:c>
     </x:row>
     <x:row r="499" spans="1:7">
@@ -14403,10 +14409,10 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B499" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C499" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D499" s="1">
         <x:v>0</x:v>
@@ -14415,10 +14421,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F499" s="1">
-        <x:v>1250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G499" s="1">
-        <x:v>1300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="500" spans="1:7">
@@ -14426,7 +14432,7 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B500" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C500" s="1">
         <x:v>50</x:v>
@@ -14438,10 +14444,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F500" s="1">
-        <x:v>0</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="G500" s="1">
-        <x:v>50</x:v>
+        <x:v>1300</x:v>
       </x:c>
     </x:row>
     <x:row r="501" spans="1:7">
@@ -14449,13 +14455,13 @@
         <x:v>556</x:v>
       </x:c>
       <x:c r="B501" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C501" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D501" s="1">
-        <x:v>120404787</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E501" s="1">
         <x:v>0</x:v>
@@ -14464,7 +14470,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G501" s="1">
-        <x:v>120406787</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="502" spans="1:7">
@@ -14472,13 +14478,13 @@
         <x:v>557</x:v>
       </x:c>
       <x:c r="B502" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C502" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D502" s="1">
-        <x:v>442806</x:v>
+        <x:v>120404787</x:v>
       </x:c>
       <x:c r="E502" s="1">
         <x:v>0</x:v>
@@ -14487,7 +14493,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G502" s="1">
-        <x:v>442806</x:v>
+        <x:v>120406787</x:v>
       </x:c>
     </x:row>
     <x:row r="503" spans="1:7">
@@ -14495,22 +14501,22 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="B503" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C503" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D503" s="1">
-        <x:v>0</x:v>
+        <x:v>442806</x:v>
       </x:c>
       <x:c r="E503" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F503" s="1">
-        <x:v>3333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G503" s="1">
-        <x:v>4333</x:v>
+        <x:v>442806</x:v>
       </x:c>
     </x:row>
     <x:row r="504" spans="1:7">
@@ -14518,10 +14524,10 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C504" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D504" s="1">
         <x:v>0</x:v>
@@ -14530,10 +14536,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F504" s="1">
-        <x:v>14000</x:v>
+        <x:v>3333</x:v>
       </x:c>
       <x:c r="G504" s="1">
-        <x:v>14050</x:v>
+        <x:v>4333</x:v>
       </x:c>
     </x:row>
     <x:row r="505" spans="1:7">
@@ -14541,7 +14547,7 @@
         <x:v>560</x:v>
       </x:c>
       <x:c r="B505" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C505" s="1">
         <x:v>50</x:v>
@@ -14553,10 +14559,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F505" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G505" s="1">
-        <x:v>50</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="506" spans="1:7">
@@ -14564,10 +14570,10 @@
         <x:v>561</x:v>
       </x:c>
       <x:c r="B506" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C506" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D506" s="1">
         <x:v>0</x:v>
@@ -14579,7 +14585,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G506" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="507" spans="1:7">
@@ -14587,10 +14593,10 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C507" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D507" s="1">
         <x:v>0</x:v>
@@ -14599,10 +14605,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F507" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G507" s="1">
-        <x:v>1050</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="508" spans="1:7">
@@ -14610,10 +14616,10 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C508" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D508" s="1">
         <x:v>0</x:v>
@@ -14622,10 +14628,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F508" s="1">
-        <x:v>2700</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G508" s="1">
-        <x:v>5400</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="509" spans="1:7">
@@ -14633,10 +14639,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C509" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D509" s="1">
         <x:v>0</x:v>
@@ -14645,10 +14651,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F509" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G509" s="1">
-        <x:v>50</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="510" spans="1:7">
@@ -14656,7 +14662,7 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C510" s="1">
         <x:v>50</x:v>
@@ -14668,10 +14674,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F510" s="1">
-        <x:v>12000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G510" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="511" spans="1:7">
@@ -14679,7 +14685,7 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C511" s="1">
         <x:v>50</x:v>
@@ -14691,10 +14697,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F511" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G511" s="1">
-        <x:v>50</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="512" spans="1:7">
@@ -14702,13 +14708,13 @@
         <x:v>567</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C512" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D512" s="1">
-        <x:v>151713</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E512" s="1">
         <x:v>0</x:v>
@@ -14717,7 +14723,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G512" s="1">
-        <x:v>151713</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="513" spans="1:7">
@@ -14725,22 +14731,22 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C513" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D513" s="1">
-        <x:v>0</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="E513" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F513" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G513" s="1">
-        <x:v>250</x:v>
+        <x:v>151713</x:v>
       </x:c>
     </x:row>
     <x:row r="514" spans="1:7">
@@ -14748,10 +14754,10 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B514" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C514" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D514" s="1">
         <x:v>0</x:v>
@@ -14760,10 +14766,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F514" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G514" s="1">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="515" spans="1:7">
@@ -14771,7 +14777,7 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="B515" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C515" s="1">
         <x:v>50</x:v>
@@ -14783,10 +14789,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F515" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G515" s="1">
-        <x:v>2750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="516" spans="1:7">
@@ -14794,10 +14800,10 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="B516" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C516" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D516" s="1">
         <x:v>0</x:v>
@@ -14806,10 +14812,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F516" s="1">
-        <x:v>4600</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G516" s="1">
-        <x:v>4600</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="517" spans="1:7">
@@ -14817,10 +14823,10 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="B517" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C517" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D517" s="1">
         <x:v>0</x:v>
@@ -14829,10 +14835,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>0</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>50</x:v>
+        <x:v>4600</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -14840,7 +14846,7 @@
         <x:v>573</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C518" s="1">
         <x:v>50</x:v>
@@ -14863,7 +14869,7 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="B519" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C519" s="1">
         <x:v>50</x:v>
@@ -14886,7 +14892,7 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C520" s="1">
         <x:v>50</x:v>
@@ -14909,13 +14915,13 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B521" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C521" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D521" s="1">
-        <x:v>282526</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E521" s="1">
         <x:v>0</x:v>
@@ -14924,7 +14930,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G521" s="1">
-        <x:v>282526</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="522" spans="1:7">
@@ -14932,22 +14938,22 @@
         <x:v>577</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C522" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D522" s="1">
-        <x:v>0</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E522" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F522" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G522" s="1">
-        <x:v>1000</x:v>
+        <x:v>282526</x:v>
       </x:c>
     </x:row>
     <x:row r="523" spans="1:7">
@@ -14955,10 +14961,10 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C523" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D523" s="1">
         <x:v>0</x:v>
@@ -14967,10 +14973,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F523" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G523" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="524" spans="1:7">
@@ -14978,22 +14984,22 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C524" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D524" s="1">
-        <x:v>116161</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E524" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F524" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>124661</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -15001,22 +15007,22 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C525" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D525" s="1">
-        <x:v>0</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="E525" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F525" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>50</x:v>
+        <x:v>124661</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -15024,7 +15030,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C526" s="1">
         <x:v>50</x:v>
@@ -15047,7 +15053,7 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B527" s="1" t="s">
-        <x:v>583</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C527" s="1">
         <x:v>50</x:v>
@@ -15067,10 +15073,10 @@
     </x:row>
     <x:row r="528" spans="1:7">
       <x:c r="A528" s="1" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B528" s="1" t="s">
         <x:v>584</x:v>
-      </x:c>
-      <x:c r="B528" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C528" s="1">
         <x:v>50</x:v>
@@ -15093,22 +15099,22 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C529" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D529" s="1">
-        <x:v>2997852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E529" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F529" s="1">
-        <x:v>6800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G529" s="1">
-        <x:v>3007652</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="530" spans="1:7">
@@ -15116,22 +15122,22 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="B530" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C530" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D530" s="1">
-        <x:v>14446984</x:v>
+        <x:v>2997852</x:v>
       </x:c>
       <x:c r="E530" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F530" s="1">
-        <x:v>0</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G530" s="1">
-        <x:v>14446984</x:v>
+        <x:v>3012652</x:v>
       </x:c>
     </x:row>
     <x:row r="531" spans="1:7">
@@ -15139,13 +15145,13 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="B531" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C531" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D531" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E531" s="1">
         <x:v>0</x:v>
@@ -15154,7 +15160,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G531" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="532" spans="1:7">
@@ -15162,10 +15168,10 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C532" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D532" s="1">
         <x:v>0</x:v>
@@ -15174,10 +15180,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F532" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G532" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="533" spans="1:7">
@@ -15185,7 +15191,7 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C533" s="1">
         <x:v>0</x:v>
@@ -15197,10 +15203,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F533" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G533" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="534" spans="1:7">
@@ -15208,10 +15214,10 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="B534" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C534" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D534" s="1">
         <x:v>0</x:v>
@@ -15220,10 +15226,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F534" s="1">
-        <x:v>0</x:v>
+        <x:v>22334</x:v>
       </x:c>
       <x:c r="G534" s="1">
-        <x:v>50</x:v>
+        <x:v>22334</x:v>
       </x:c>
     </x:row>
     <x:row r="535" spans="1:7">
@@ -15231,10 +15237,10 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C535" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D535" s="1">
         <x:v>0</x:v>
@@ -15243,10 +15249,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F535" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G535" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="536" spans="1:7">
@@ -15254,10 +15260,10 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C536" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D536" s="1">
         <x:v>0</x:v>
@@ -15266,10 +15272,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F536" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G536" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="537" spans="1:7">
@@ -15277,13 +15283,13 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C537" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D537" s="1">
-        <x:v>209387</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E537" s="1">
         <x:v>0</x:v>
@@ -15292,7 +15298,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G537" s="1">
-        <x:v>209387</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="538" spans="1:7">
@@ -15300,13 +15306,13 @@
         <x:v>594</x:v>
       </x:c>
       <x:c r="B538" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C538" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D538" s="1">
-        <x:v>0</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="E538" s="1">
         <x:v>0</x:v>
@@ -15315,7 +15321,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G538" s="1">
-        <x:v>50</x:v>
+        <x:v>209387</x:v>
       </x:c>
     </x:row>
     <x:row r="539" spans="1:7">
@@ -15323,13 +15329,13 @@
         <x:v>595</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C539" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D539" s="1">
-        <x:v>257695</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E539" s="1">
         <x:v>0</x:v>
@@ -15338,7 +15344,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G539" s="1">
-        <x:v>257695</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="540" spans="1:7">
@@ -15346,22 +15352,22 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C540" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D540" s="1">
-        <x:v>0</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="E540" s="1">
-        <x:v>20171730</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F540" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>0</x:v>
+        <x:v>257695</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -15369,7 +15375,7 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C541" s="1">
         <x:v>0</x:v>
@@ -15378,13 +15384,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E541" s="1">
-        <x:v>0</x:v>
+        <x:v>20171730</x:v>
       </x:c>
       <x:c r="F541" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -15392,10 +15398,10 @@
         <x:v>598</x:v>
       </x:c>
       <x:c r="B542" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C542" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D542" s="1">
         <x:v>0</x:v>
@@ -15404,10 +15410,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F542" s="1">
-        <x:v>29800</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G542" s="1">
-        <x:v>34800</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:7">
@@ -15415,10 +15421,10 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C543" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D543" s="1">
         <x:v>0</x:v>
@@ -15427,10 +15433,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>0</x:v>
+        <x:v>29800</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>50</x:v>
+        <x:v>34800</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15438,7 +15444,7 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C544" s="1">
         <x:v>50</x:v>
@@ -15450,10 +15456,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>5650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -15461,22 +15467,22 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="B545" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C545" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D545" s="1">
-        <x:v>74692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E545" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F545" s="1">
-        <x:v>0</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G545" s="1">
-        <x:v>76742</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="546" spans="1:7">
@@ -15484,22 +15490,22 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C546" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D546" s="1">
-        <x:v>0</x:v>
+        <x:v>74692</x:v>
       </x:c>
       <x:c r="E546" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F546" s="1">
-        <x:v>6834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G546" s="1">
-        <x:v>6884</x:v>
+        <x:v>76742</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:7">
@@ -15507,7 +15513,7 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C547" s="1">
         <x:v>50</x:v>
@@ -15519,10 +15525,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F547" s="1">
-        <x:v>0</x:v>
+        <x:v>6834</x:v>
       </x:c>
       <x:c r="G547" s="1">
-        <x:v>50</x:v>
+        <x:v>6884</x:v>
       </x:c>
     </x:row>
     <x:row r="548" spans="1:7">
@@ -15530,22 +15536,22 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C548" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D548" s="1">
-        <x:v>558813</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E548" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F548" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G548" s="1">
-        <x:v>559813</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="549" spans="1:7">
@@ -15553,22 +15559,22 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C549" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D549" s="1">
-        <x:v>0</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E549" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F549" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G549" s="1">
-        <x:v>6650</x:v>
+        <x:v>559813</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:7">
@@ -15576,22 +15582,22 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C550" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D550" s="1">
-        <x:v>8250000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E550" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F550" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G550" s="1">
-        <x:v>8250000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="551" spans="1:7">
@@ -15599,13 +15605,13 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C551" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D551" s="1">
-        <x:v>0</x:v>
+        <x:v>8250000</x:v>
       </x:c>
       <x:c r="E551" s="1">
         <x:v>0</x:v>
@@ -15614,7 +15620,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>50</x:v>
+        <x:v>8250000</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -15622,22 +15628,22 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C552" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D552" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E552" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F552" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G552" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="553" spans="1:7">
@@ -15645,22 +15651,22 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B553" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C553" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D553" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E553" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F553" s="1">
-        <x:v>1089100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G553" s="1">
-        <x:v>1089150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="554" spans="1:7">
@@ -15668,22 +15674,22 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C554" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D554" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E554" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F554" s="1">
-        <x:v>0</x:v>
+        <x:v>1089100</x:v>
       </x:c>
       <x:c r="G554" s="1">
-        <x:v>1927706</x:v>
+        <x:v>1089150</x:v>
       </x:c>
     </x:row>
     <x:row r="555" spans="1:7">
@@ -15691,13 +15697,13 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C555" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D555" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E555" s="1">
         <x:v>0</x:v>
@@ -15706,7 +15712,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G555" s="1">
-        <x:v>50</x:v>
+        <x:v>1927706</x:v>
       </x:c>
     </x:row>
     <x:row r="556" spans="1:7">
@@ -15714,7 +15720,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>50</x:v>
@@ -15726,10 +15732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -15737,7 +15743,7 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C557" s="1">
         <x:v>50</x:v>
@@ -15749,10 +15755,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F557" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G557" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:7">
@@ -15760,10 +15766,10 @@
         <x:v>614</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C558" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D558" s="1">
         <x:v>0</x:v>
@@ -15772,10 +15778,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F558" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G558" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:7">
@@ -15783,10 +15789,10 @@
         <x:v>615</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C559" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D559" s="1">
         <x:v>0</x:v>
@@ -15795,10 +15801,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -15806,7 +15812,7 @@
         <x:v>616</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>50</x:v>
@@ -15818,10 +15824,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F560" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G560" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:7">
@@ -15829,22 +15835,22 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C561" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D561" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E561" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F561" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G561" s="1">
-        <x:v>0</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:7">
@@ -15852,22 +15858,22 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B562" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C562" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D562" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E562" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F562" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G562" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="563" spans="1:7">
@@ -15875,7 +15881,7 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="B563" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C563" s="1">
         <x:v>50</x:v>
@@ -15898,22 +15904,22 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C564" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D564" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E564" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F564" s="1">
-        <x:v>14866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G564" s="1">
-        <x:v>117122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:7">
@@ -15921,22 +15927,22 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C565" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D565" s="1">
-        <x:v>75000</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E565" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>0</x:v>
+        <x:v>14866</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>75000</x:v>
+        <x:v>117122</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -15944,13 +15950,13 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C566" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D566" s="1">
-        <x:v>0</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="E566" s="1">
         <x:v>0</x:v>
@@ -15959,7 +15965,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>50</x:v>
+        <x:v>75000</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -15967,7 +15973,7 @@
         <x:v>623</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C567" s="1">
         <x:v>50</x:v>
@@ -15990,7 +15996,7 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B568" s="1" t="s">
-        <x:v>625</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C568" s="1">
         <x:v>50</x:v>
@@ -16010,10 +16016,10 @@
     </x:row>
     <x:row r="569" spans="1:7">
       <x:c r="A569" s="1" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="B569" s="1" t="s">
         <x:v>626</x:v>
-      </x:c>
-      <x:c r="B569" s="1" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>50</x:v>
@@ -16036,10 +16042,10 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C570" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D570" s="1">
         <x:v>0</x:v>
@@ -16048,10 +16054,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F570" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G570" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="571" spans="1:7">
@@ -16059,7 +16065,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B571" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C571" s="1">
         <x:v>0</x:v>
@@ -16071,10 +16077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F571" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G571" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:7">
@@ -16085,19 +16091,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C572" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D572" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E572" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F572" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>50</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -16105,7 +16111,7 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C573" s="1">
         <x:v>50</x:v>
@@ -16114,13 +16120,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E573" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F573" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G573" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:7">
@@ -16128,7 +16134,7 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C574" s="1">
         <x:v>50</x:v>
@@ -16140,10 +16146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F574" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G574" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:7">
@@ -16151,10 +16157,10 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C575" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D575" s="1">
         <x:v>0</x:v>
@@ -16163,10 +16169,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F575" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G575" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="576" spans="1:7">
@@ -16174,10 +16180,10 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C576" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D576" s="1">
         <x:v>0</x:v>
@@ -16186,10 +16192,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F576" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G576" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="577" spans="1:7">
@@ -16197,7 +16203,7 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C577" s="1">
         <x:v>50</x:v>
@@ -16220,7 +16226,7 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C578" s="1">
         <x:v>50</x:v>
@@ -16243,10 +16249,10 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C579" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D579" s="1">
         <x:v>0</x:v>
@@ -16255,10 +16261,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F579" s="1">
-        <x:v>-19405</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G579" s="1">
-        <x:v>-19405</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="580" spans="1:7">
@@ -16266,22 +16272,22 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C580" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D580" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E580" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F580" s="1">
-        <x:v>0</x:v>
+        <x:v>-19405</x:v>
       </x:c>
       <x:c r="G580" s="1">
-        <x:v>1491280</x:v>
+        <x:v>-19405</x:v>
       </x:c>
     </x:row>
     <x:row r="581" spans="1:7">
@@ -16289,22 +16295,22 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C581" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D581" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E581" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F581" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G581" s="1">
-        <x:v>500</x:v>
+        <x:v>1491280</x:v>
       </x:c>
     </x:row>
     <x:row r="582" spans="1:7">
@@ -16312,10 +16318,10 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C582" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D582" s="1">
         <x:v>0</x:v>
@@ -16324,10 +16330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F582" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G582" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="583" spans="1:7">
@@ -16335,7 +16341,7 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C583" s="1">
         <x:v>50</x:v>
@@ -16347,10 +16353,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F583" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G583" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="584" spans="1:7">
@@ -16358,7 +16364,7 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C584" s="1">
         <x:v>50</x:v>
@@ -16370,10 +16376,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F584" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -16381,7 +16387,7 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C585" s="1">
         <x:v>50</x:v>
@@ -16393,10 +16399,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>1287</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>1337</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -16404,10 +16410,10 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -16416,10 +16422,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>6697</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>6697</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -16427,22 +16433,22 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C587" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D587" s="1">
-        <x:v>75844</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E587" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F587" s="1">
-        <x:v>0</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G587" s="1">
-        <x:v>75894</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="588" spans="1:7">
@@ -16450,22 +16456,22 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C588" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D588" s="1">
-        <x:v>0</x:v>
+        <x:v>75844</x:v>
       </x:c>
       <x:c r="E588" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F588" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>4000</x:v>
+        <x:v>75894</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -16473,7 +16479,7 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>0</x:v>
@@ -16485,10 +16491,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F589" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">
@@ -16496,10 +16502,10 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C590" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D590" s="1">
         <x:v>0</x:v>
@@ -16508,10 +16514,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F590" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G590" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="591" spans="1:7">
@@ -16519,7 +16525,7 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C591" s="1">
         <x:v>50</x:v>
@@ -16542,7 +16548,7 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C592" s="1">
         <x:v>50</x:v>
@@ -16565,22 +16571,22 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C593" s="1">
-        <x:v>7500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D593" s="1">
-        <x:v>1400000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E593" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F593" s="1">
-        <x:v>10500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G593" s="1">
-        <x:v>1418000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="594" spans="1:7">
@@ -16588,22 +16594,22 @@
         <x:v>651</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C594" s="1">
-        <x:v>50</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D594" s="1">
-        <x:v>0</x:v>
+        <x:v>1400000</x:v>
       </x:c>
       <x:c r="E594" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F594" s="1">
-        <x:v>0</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G594" s="1">
-        <x:v>50</x:v>
+        <x:v>1418000</x:v>
       </x:c>
     </x:row>
     <x:row r="595" spans="1:7">
@@ -16611,10 +16617,10 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C595" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D595" s="1">
         <x:v>0</x:v>
@@ -16623,10 +16629,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F595" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G595" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="596" spans="1:7">
@@ -16634,10 +16640,10 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C596" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D596" s="1">
         <x:v>0</x:v>
@@ -16649,7 +16655,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G596" s="1">
-        <x:v>1550</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="597" spans="1:7">
@@ -16657,7 +16663,7 @@
         <x:v>654</x:v>
       </x:c>
       <x:c r="B597" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C597" s="1">
         <x:v>50</x:v>
@@ -16669,10 +16675,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F597" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G597" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="598" spans="1:7">
@@ -16680,7 +16686,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>50</x:v>
@@ -16703,7 +16709,7 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C599" s="1">
         <x:v>50</x:v>
@@ -16726,7 +16732,7 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C600" s="1">
         <x:v>50</x:v>
@@ -16749,7 +16755,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>50</x:v>
@@ -16772,13 +16778,13 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C602" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D602" s="1">
-        <x:v>2707641</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E602" s="1">
         <x:v>0</x:v>
@@ -16787,7 +16793,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>2707641</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -16795,22 +16801,22 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C603" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D603" s="1">
-        <x:v>0</x:v>
+        <x:v>2707641</x:v>
       </x:c>
       <x:c r="E603" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F603" s="1">
-        <x:v>81050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G603" s="1">
-        <x:v>81050</x:v>
+        <x:v>2707641</x:v>
       </x:c>
     </x:row>
     <x:row r="604" spans="1:7">
@@ -16818,10 +16824,10 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C604" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D604" s="1">
         <x:v>0</x:v>
@@ -16830,10 +16836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F604" s="1">
-        <x:v>0</x:v>
+        <x:v>81050</x:v>
       </x:c>
       <x:c r="G604" s="1">
-        <x:v>50</x:v>
+        <x:v>81050</x:v>
       </x:c>
     </x:row>
     <x:row r="605" spans="1:7">
@@ -16841,7 +16847,7 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>50</x:v>
@@ -16864,10 +16870,10 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16879,7 +16885,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -16887,10 +16893,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C607" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D607" s="1">
         <x:v>0</x:v>
@@ -16902,7 +16908,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G607" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:7">
@@ -16910,7 +16916,7 @@
         <x:v>665</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C608" s="1">
         <x:v>50</x:v>
@@ -16922,10 +16928,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F608" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G608" s="1">
-        <x:v>14050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="609" spans="1:7">
@@ -16933,10 +16939,10 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C609" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D609" s="1">
         <x:v>0</x:v>
@@ -16945,10 +16951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F609" s="1">
-        <x:v>2700</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G609" s="1">
-        <x:v>2700</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="610" spans="1:7">
@@ -16956,7 +16962,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C610" s="1">
         <x:v>0</x:v>
@@ -16968,10 +16974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F610" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G610" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="611" spans="1:7">
@@ -16979,30 +16985,30 @@
         <x:v>668</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C611" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D611" s="1">
-        <x:v>14446984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E611" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F611" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G611" s="1">
-        <x:v>14446984</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="612" spans="1:7">
       <x:c r="A612" s="1" t="s">
-        <x:v>668</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>0</x:v>
@@ -17025,13 +17031,13 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C613" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D613" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E613" s="1">
         <x:v>0</x:v>
@@ -17040,7 +17046,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
@@ -17048,22 +17054,22 @@
         <x:v>670</x:v>
       </x:c>
       <x:c r="B614" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C614" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D614" s="1">
-        <x:v>2470488</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E614" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F614" s="1">
-        <x:v>11834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G614" s="1">
-        <x:v>2494372</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:7">
@@ -17071,22 +17077,22 @@
         <x:v>671</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>100</x:v>
+        <x:v>17050</x:v>
       </x:c>
       <x:c r="D615" s="1">
-        <x:v>150640</x:v>
+        <x:v>2470488</x:v>
       </x:c>
       <x:c r="E615" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>0</x:v>
+        <x:v>11834</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>150740</x:v>
+        <x:v>2499372</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17094,13 +17100,13 @@
         <x:v>672</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D616" s="1">
-        <x:v>0</x:v>
+        <x:v>150640</x:v>
       </x:c>
       <x:c r="E616" s="1">
         <x:v>0</x:v>
@@ -17109,7 +17115,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>50</x:v>
+        <x:v>150740</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -17117,7 +17123,7 @@
         <x:v>673</x:v>
       </x:c>
       <x:c r="B617" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C617" s="1">
         <x:v>50</x:v>
@@ -17143,7 +17149,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C618" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D618" s="1">
         <x:v>0</x:v>
@@ -17152,10 +17158,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F618" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G618" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:7">
@@ -17163,10 +17169,10 @@
         <x:v>675</x:v>
       </x:c>
       <x:c r="B619" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C619" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D619" s="1">
         <x:v>0</x:v>
@@ -17175,10 +17181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F619" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G619" s="1">
-        <x:v>2550</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="620" spans="1:7">
@@ -17186,7 +17192,7 @@
         <x:v>676</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C620" s="1">
         <x:v>50</x:v>
@@ -17198,10 +17204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F620" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G620" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="621" spans="1:7">
@@ -17209,7 +17215,7 @@
         <x:v>677</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C621" s="1">
         <x:v>50</x:v>
@@ -17232,7 +17238,7 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C622" s="1">
         <x:v>50</x:v>
@@ -17255,7 +17261,7 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C623" s="1">
         <x:v>50</x:v>
@@ -17278,22 +17284,22 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C624" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D624" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E624" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F624" s="1">
-        <x:v>6634</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G624" s="1">
-        <x:v>3982954</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:7">
@@ -17301,22 +17307,22 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D625" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E625" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>22000</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>22000</x:v>
+        <x:v>3982954</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17324,10 +17330,10 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17336,10 +17342,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>5800</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>5850</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17347,7 +17353,7 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>684</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C627" s="1">
         <x:v>50</x:v>
@@ -17359,21 +17365,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
       <x:c r="A628" s="1" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="B628" s="1" t="s">
         <x:v>685</x:v>
       </x:c>
-      <x:c r="B628" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C628" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D628" s="1">
         <x:v>0</x:v>
@@ -17382,10 +17388,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F628" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">
@@ -17393,10 +17399,10 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>687</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C629" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D629" s="1">
         <x:v>0</x:v>
@@ -17405,18 +17411,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F629" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G629" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:7">
       <x:c r="A630" s="1" t="s">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="B630" s="1" t="s">
         <x:v>688</x:v>
-      </x:c>
-      <x:c r="B630" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C630" s="1">
         <x:v>50</x:v>
@@ -17439,10 +17445,10 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17451,21 +17457,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
       <x:c r="A632" s="1" t="s">
-        <x:v>689</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17474,10 +17480,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17485,7 +17491,7 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C633" s="1">
         <x:v>50</x:v>
@@ -17508,7 +17514,7 @@
         <x:v>691</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C634" s="1">
         <x:v>50</x:v>
@@ -17531,10 +17537,10 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C635" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D635" s="1">
         <x:v>0</x:v>
@@ -17543,10 +17549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F635" s="1">
-        <x:v>68600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>71150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">
@@ -17554,10 +17560,10 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C636" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D636" s="1">
         <x:v>0</x:v>
@@ -17566,10 +17572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F636" s="1">
-        <x:v>0</x:v>
+        <x:v>68600</x:v>
       </x:c>
       <x:c r="G636" s="1">
-        <x:v>50</x:v>
+        <x:v>71150</x:v>
       </x:c>
     </x:row>
     <x:row r="637" spans="1:7">
@@ -17577,7 +17583,7 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C637" s="1">
         <x:v>50</x:v>
@@ -17600,10 +17606,10 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B638" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C638" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D638" s="1">
         <x:v>0</x:v>
@@ -17612,10 +17618,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F638" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G638" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="639" spans="1:7">
@@ -17623,10 +17629,10 @@
         <x:v>696</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C639" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D639" s="1">
         <x:v>0</x:v>
@@ -17635,10 +17641,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F639" s="1">
-        <x:v>58000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>58050</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17646,10 +17652,10 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C640" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D640" s="1">
         <x:v>0</x:v>
@@ -17658,10 +17664,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F640" s="1">
-        <x:v>1666</x:v>
+        <x:v>58000</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>3716</x:v>
+        <x:v>58050</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">
@@ -17669,30 +17675,30 @@
         <x:v>698</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C641" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D641" s="1">
-        <x:v>74382</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E641" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F641" s="1">
-        <x:v>11668</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="G641" s="1">
-        <x:v>86050</x:v>
+        <x:v>3716</x:v>
       </x:c>
     </x:row>
     <x:row r="642" spans="1:7">
       <x:c r="A642" s="1" t="s">
-        <x:v>698</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C642" s="1">
         <x:v>0</x:v>
@@ -17704,10 +17710,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F642" s="1">
-        <x:v>0</x:v>
+        <x:v>11668</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>74382</x:v>
+        <x:v>86050</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
@@ -17718,10 +17724,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C643" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D643" s="1">
-        <x:v>0</x:v>
+        <x:v>74382</x:v>
       </x:c>
       <x:c r="E643" s="1">
         <x:v>0</x:v>
@@ -17730,7 +17736,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G643" s="1">
-        <x:v>50</x:v>
+        <x:v>74382</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:7">
@@ -17738,13 +17744,13 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C644" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>105040</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
@@ -17753,7 +17759,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>105090</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17761,22 +17767,22 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>0</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>30600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>33550</x:v>
+        <x:v>105090</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17784,10 +17790,10 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D646" s="1">
         <x:v>0</x:v>
@@ -17796,10 +17802,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
-        <x:v>0</x:v>
+        <x:v>30600</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>2550</x:v>
+        <x:v>33550</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -17807,22 +17813,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B647" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C647" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D647" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E647" s="1">
-        <x:v>56045</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F647" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G647" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="648" spans="1:7">
@@ -17836,16 +17842,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D648" s="1">
-        <x:v>150562</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E648" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F648" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G648" s="1">
-        <x:v>150612</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="649" spans="1:7">
@@ -17853,13 +17859,13 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C649" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D649" s="1">
-        <x:v>0</x:v>
+        <x:v>150562</x:v>
       </x:c>
       <x:c r="E649" s="1">
         <x:v>0</x:v>
@@ -17868,7 +17874,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>2550</x:v>
+        <x:v>150612</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -17876,10 +17882,10 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C650" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D650" s="1">
         <x:v>0</x:v>
@@ -17891,7 +17897,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
@@ -17899,10 +17905,10 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C651" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D651" s="1">
         <x:v>0</x:v>
@@ -17911,33 +17917,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F651" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
       <x:c r="A652" s="1" t="s">
-        <x:v>707</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D652" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E652" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F652" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17951,7 +17957,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D653" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E653" s="1">
         <x:v>0</x:v>
@@ -17960,7 +17966,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -17968,13 +17974,13 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C654" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D654" s="1">
-        <x:v>0</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="E654" s="1">
         <x:v>0</x:v>
@@ -17983,7 +17989,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G654" s="1">
-        <x:v>50</x:v>
+        <x:v>852561</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:7">
@@ -17991,7 +17997,7 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C655" s="1">
         <x:v>50</x:v>
@@ -18014,13 +18020,13 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C656" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>2200000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
@@ -18029,7 +18035,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>2200000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -18037,13 +18043,13 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C657" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D657" s="1">
-        <x:v>74852</x:v>
+        <x:v>2200000</x:v>
       </x:c>
       <x:c r="E657" s="1">
         <x:v>0</x:v>
@@ -18052,7 +18058,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>74902</x:v>
+        <x:v>2200000</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">
@@ -18060,13 +18066,13 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C658" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D658" s="1">
-        <x:v>0</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="E658" s="1">
         <x:v>0</x:v>
@@ -18075,7 +18081,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>50</x:v>
+        <x:v>74902</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
@@ -18083,7 +18089,7 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C659" s="1">
         <x:v>50</x:v>
@@ -18106,10 +18112,10 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D660" s="1">
         <x:v>0</x:v>
@@ -18121,7 +18127,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18129,10 +18135,10 @@
         <x:v>716</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D661" s="1">
         <x:v>0</x:v>
@@ -18144,7 +18150,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18152,10 +18158,10 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D662" s="1">
         <x:v>0</x:v>
@@ -18167,7 +18173,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18175,10 +18181,10 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C663" s="1">
-        <x:v>1050</x:v>
+        <x:v>10050</x:v>
       </x:c>
       <x:c r="D663" s="1">
         <x:v>0</x:v>
@@ -18187,10 +18193,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F663" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>2717</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
@@ -18198,10 +18204,10 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C664" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D664" s="1">
         <x:v>0</x:v>
@@ -18210,10 +18216,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F664" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G664" s="1">
-        <x:v>50</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:7">
@@ -18221,22 +18227,22 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C665" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D665" s="1">
-        <x:v>111599</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E665" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F665" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G665" s="1">
-        <x:v>114899</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:7">
@@ -18244,22 +18250,22 @@
         <x:v>721</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C666" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D666" s="1">
-        <x:v>0</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="E666" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F666" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G666" s="1">
-        <x:v>50</x:v>
+        <x:v>114899</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:7">
@@ -18267,7 +18273,7 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C667" s="1">
         <x:v>50</x:v>
@@ -18287,16 +18293,16 @@
     </x:row>
     <x:row r="668" spans="1:7">
       <x:c r="A668" s="1" t="s">
-        <x:v>722</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D668" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E668" s="1">
         <x:v>0</x:v>
@@ -18305,7 +18311,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18313,13 +18319,13 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C669" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D669" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E669" s="1">
         <x:v>0</x:v>
@@ -18328,7 +18334,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
@@ -18336,22 +18342,22 @@
         <x:v>724</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C670" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D670" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E670" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F670" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G670" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="671" spans="1:7">
@@ -18359,22 +18365,22 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C671" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D671" s="1">
-        <x:v>2263800</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E671" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F671" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>2263850</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
@@ -18382,13 +18388,13 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="B672" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C672" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D672" s="1">
-        <x:v>0</x:v>
+        <x:v>2263800</x:v>
       </x:c>
       <x:c r="E672" s="1">
         <x:v>0</x:v>
@@ -18397,7 +18403,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G672" s="1">
-        <x:v>50</x:v>
+        <x:v>2263850</x:v>
       </x:c>
     </x:row>
     <x:row r="673" spans="1:7">
@@ -18405,7 +18411,7 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C673" s="1">
         <x:v>50</x:v>
@@ -18417,10 +18423,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F673" s="1">
-        <x:v>19500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G673" s="1">
-        <x:v>19550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:7">
@@ -18428,22 +18434,22 @@
         <x:v>728</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C674" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D674" s="1">
-        <x:v>151234</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E674" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F674" s="1">
-        <x:v>55833</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="G674" s="1">
-        <x:v>213117</x:v>
+        <x:v>19550</x:v>
       </x:c>
     </x:row>
     <x:row r="675" spans="1:7">
@@ -18451,22 +18457,22 @@
         <x:v>729</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C675" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D675" s="1">
-        <x:v>0</x:v>
+        <x:v>151234</x:v>
       </x:c>
       <x:c r="E675" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F675" s="1">
-        <x:v>0</x:v>
+        <x:v>55833</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>50</x:v>
+        <x:v>213117</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
@@ -18474,7 +18480,7 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C676" s="1">
         <x:v>50</x:v>
@@ -18497,10 +18503,10 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C677" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D677" s="1">
         <x:v>0</x:v>
@@ -18509,10 +18515,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F677" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -18520,22 +18526,22 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C678" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D678" s="1">
-        <x:v>380377</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E678" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F678" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G678" s="1">
-        <x:v>380377</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:7">
@@ -18543,22 +18549,22 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C679" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D679" s="1">
-        <x:v>817169</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="E679" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F679" s="1">
-        <x:v>1668</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>820837</x:v>
+        <x:v>380377</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18566,22 +18572,22 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>11050</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D680" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E680" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>6242</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>17292</x:v>
+        <x:v>820837</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -18589,10 +18595,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D681" s="1">
         <x:v>0</x:v>
@@ -18601,10 +18607,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>0</x:v>
+        <x:v>6242</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>50</x:v>
+        <x:v>17292</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -18612,7 +18618,7 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C682" s="1">
         <x:v>50</x:v>
@@ -18635,10 +18641,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -18647,10 +18653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -18658,10 +18664,10 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D684" s="1">
         <x:v>0</x:v>
@@ -18670,10 +18676,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>25000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>25050</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -18681,7 +18687,7 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C685" s="1">
         <x:v>50</x:v>
@@ -18693,41 +18699,41 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>50</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
       <x:c r="A686" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E686" s="1">
-        <x:v>16359294</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
       <x:c r="A687" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -18750,7 +18756,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C688" s="1">
         <x:v>0</x:v>
@@ -18759,7 +18765,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E688" s="1">
-        <x:v>1531015</x:v>
+        <x:v>16359294</x:v>
       </x:c>
       <x:c r="F688" s="1">
         <x:v>0</x:v>
@@ -18773,22 +18779,22 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C689" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D689" s="1">
-        <x:v>157560</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E689" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F689" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G689" s="1">
-        <x:v>157610</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:7">
@@ -18796,13 +18802,13 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C690" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D690" s="1">
-        <x:v>0</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="E690" s="1">
         <x:v>0</x:v>
@@ -18811,7 +18817,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>50</x:v>
+        <x:v>157610</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -18819,13 +18825,13 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D691" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E691" s="1">
         <x:v>0</x:v>
@@ -18834,7 +18840,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5584432</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -18842,13 +18848,13 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D692" s="1">
-        <x:v>0</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E692" s="1">
         <x:v>0</x:v>
@@ -18857,7 +18863,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>50</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -18865,22 +18871,22 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C693" s="1">
-        <x:v>33050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D693" s="1">
-        <x:v>1789991</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E693" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F693" s="1">
-        <x:v>20501</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>1843542</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
@@ -18888,22 +18894,22 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C694" s="1">
-        <x:v>0</x:v>
+        <x:v>33050</x:v>
       </x:c>
       <x:c r="D694" s="1">
-        <x:v>0</x:v>
+        <x:v>1789991</x:v>
       </x:c>
       <x:c r="E694" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F694" s="1">
-        <x:v>2700</x:v>
+        <x:v>20501</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>2700</x:v>
+        <x:v>1843542</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -18911,22 +18917,22 @@
         <x:v>747</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C695" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D695" s="1">
-        <x:v>1543316</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E695" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F695" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
@@ -18934,22 +18940,22 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D696" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E696" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>14500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>14550</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18957,7 +18963,7 @@
         <x:v>749</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C697" s="1">
         <x:v>50</x:v>
@@ -18969,10 +18975,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
@@ -18980,7 +18986,7 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C698" s="1">
         <x:v>50</x:v>
@@ -19003,13 +19009,13 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C699" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D699" s="1">
-        <x:v>2150512</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E699" s="1">
         <x:v>0</x:v>
@@ -19018,7 +19024,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>2150562</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
@@ -19026,22 +19032,22 @@
         <x:v>752</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C700" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D700" s="1">
-        <x:v>0</x:v>
+        <x:v>2150512</x:v>
       </x:c>
       <x:c r="E700" s="1">
-        <x:v>10135449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F700" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>0</x:v>
+        <x:v>2150562</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -19049,22 +19055,22 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C701" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D701" s="1">
-        <x:v>103020</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E701" s="1">
-        <x:v>0</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>106354</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
@@ -19072,36 +19078,36 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C702" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>75281</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>75281</x:v>
+        <x:v>106354</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
       <x:c r="A703" s="1" t="s">
-        <x:v>754</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C703" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D703" s="1">
-        <x:v>0</x:v>
+        <x:v>75281</x:v>
       </x:c>
       <x:c r="E703" s="1">
         <x:v>0</x:v>
@@ -19110,7 +19116,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>2500</x:v>
+        <x:v>75281</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
@@ -19118,13 +19124,13 @@
         <x:v>755</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C704" s="1">
-        <x:v>0</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D704" s="1">
-        <x:v>182279</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E704" s="1">
         <x:v>0</x:v>
@@ -19133,7 +19139,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>182279</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
@@ -19141,22 +19147,22 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>2050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>0</x:v>
+        <x:v>182279</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>27050</x:v>
+        <x:v>182279</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19164,22 +19170,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>1050</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D706" s="1">
-        <x:v>902176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E706" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>7000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>910226</x:v>
+        <x:v>27050</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -19187,22 +19193,22 @@
         <x:v>758</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D707" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E707" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>25500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>25550</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
@@ -19222,10 +19228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>0</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>50</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -19233,10 +19239,10 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D709" s="1">
         <x:v>0</x:v>
@@ -19245,10 +19251,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -19256,7 +19262,7 @@
         <x:v>761</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C710" s="1">
         <x:v>0</x:v>
@@ -19268,10 +19274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>6200</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>6200</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
@@ -19279,10 +19285,10 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C711" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D711" s="1">
         <x:v>0</x:v>
@@ -19291,10 +19297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>50</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
@@ -19302,10 +19308,10 @@
         <x:v>763</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
@@ -19317,7 +19323,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19325,10 +19331,10 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19337,10 +19343,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>6650</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19348,22 +19354,22 @@
         <x:v>765</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D714" s="1">
-        <x:v>2771797</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E714" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>2771797</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19371,22 +19377,22 @@
         <x:v>766</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C715" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>0</x:v>
+        <x:v>2771797</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>5000</x:v>
+        <x:v>2771797</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
@@ -19394,10 +19400,10 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D716" s="1">
         <x:v>0</x:v>
@@ -19406,10 +19412,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19417,22 +19423,22 @@
         <x:v>768</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>6550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D717" s="1">
-        <x:v>73673</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E717" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>83523</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
@@ -19440,22 +19446,22 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C718" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D718" s="1">
-        <x:v>0</x:v>
+        <x:v>73673</x:v>
       </x:c>
       <x:c r="E718" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F718" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>50</x:v>
+        <x:v>83523</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
@@ -19463,7 +19469,7 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C719" s="1">
         <x:v>50</x:v>
@@ -19486,10 +19492,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D720" s="1">
         <x:v>0</x:v>
@@ -19498,10 +19504,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
@@ -19509,10 +19515,10 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D721" s="1">
         <x:v>0</x:v>
@@ -19521,10 +19527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F721" s="1">
-        <x:v>2700</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>2700</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
@@ -19532,10 +19538,10 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D722" s="1">
         <x:v>0</x:v>
@@ -19544,10 +19550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F722" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
@@ -19555,10 +19561,10 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D723" s="1">
         <x:v>0</x:v>
@@ -19567,33 +19573,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F723" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>9350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
       <x:c r="A724" s="1" t="s">
-        <x:v>774</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D724" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E724" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
@@ -19601,22 +19607,22 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D725" s="1">
-        <x:v>2835078</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E725" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F725" s="1">
-        <x:v>5500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>2840628</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
@@ -19624,22 +19630,22 @@
         <x:v>776</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C726" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D726" s="1">
-        <x:v>0</x:v>
+        <x:v>2835078</x:v>
       </x:c>
       <x:c r="E726" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>0</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>50</x:v>
+        <x:v>2840628</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
@@ -19647,7 +19653,7 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C727" s="1">
         <x:v>50</x:v>
@@ -19659,10 +19665,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F727" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
@@ -19670,7 +19676,7 @@
         <x:v>778</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C728" s="1">
         <x:v>50</x:v>
@@ -19682,10 +19688,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
@@ -19693,10 +19699,10 @@
         <x:v>779</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C729" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D729" s="1">
         <x:v>0</x:v>
@@ -19705,10 +19711,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F729" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>3300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
@@ -19719,7 +19725,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C730" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D730" s="1">
         <x:v>0</x:v>
@@ -19728,10 +19734,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F730" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>50</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
@@ -19739,7 +19745,7 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C731" s="1">
         <x:v>50</x:v>
@@ -19751,10 +19757,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F731" s="1">
-        <x:v>5700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
@@ -19762,7 +19768,7 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C732" s="1">
         <x:v>50</x:v>
@@ -19774,10 +19780,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F732" s="1">
-        <x:v>0</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
@@ -19785,7 +19791,7 @@
         <x:v>783</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C733" s="1">
         <x:v>50</x:v>
@@ -19808,22 +19814,22 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C734" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D734" s="1">
-        <x:v>2192272</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E734" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F734" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>2209772</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
@@ -19831,13 +19837,13 @@
         <x:v>785</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D735" s="1">
-        <x:v>0</x:v>
+        <x:v>2192272</x:v>
       </x:c>
       <x:c r="E735" s="1">
         <x:v>0</x:v>
@@ -19846,7 +19852,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>1000</x:v>
+        <x:v>2209772</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19854,10 +19860,10 @@
         <x:v>786</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19866,10 +19872,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
@@ -19877,22 +19883,22 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C737" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D737" s="1">
-        <x:v>1015758</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E737" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F737" s="1">
-        <x:v>11500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G737" s="1">
-        <x:v>1029258</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="738" spans="1:7">
@@ -19900,22 +19906,22 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D738" s="1">
-        <x:v>0</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="E738" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F738" s="1">
-        <x:v>0</x:v>
+        <x:v>11500</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>50</x:v>
+        <x:v>1029258</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
@@ -19923,13 +19929,13 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C739" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D739" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E739" s="1">
         <x:v>0</x:v>
@@ -19938,7 +19944,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>40000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
@@ -19946,13 +19952,13 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D740" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E740" s="1">
         <x:v>0</x:v>
@@ -19961,7 +19967,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>1000</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
@@ -19969,22 +19975,22 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C741" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D741" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E741" s="1">
-        <x:v>424596</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F741" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
@@ -19992,22 +19998,22 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C742" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D742" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E742" s="1">
-        <x:v>0</x:v>
+        <x:v>424596</x:v>
       </x:c>
       <x:c r="F742" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
@@ -20015,10 +20021,10 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C743" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D743" s="1">
         <x:v>0</x:v>
@@ -20027,10 +20033,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F743" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G743" s="1">
-        <x:v>5200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="744" spans="1:7">
@@ -20038,10 +20044,10 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C744" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D744" s="1">
         <x:v>0</x:v>
@@ -20050,10 +20056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F744" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">
@@ -20061,7 +20067,7 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C745" s="1">
         <x:v>50</x:v>
@@ -20084,7 +20090,7 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C746" s="1">
         <x:v>50</x:v>
@@ -20096,10 +20102,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20107,22 +20113,22 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D747" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E747" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F747" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>3920589</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
@@ -20130,13 +20136,13 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D748" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E748" s="1">
         <x:v>0</x:v>
@@ -20145,7 +20151,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>50</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
@@ -20153,10 +20159,10 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C749" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D749" s="1">
         <x:v>0</x:v>
@@ -20168,7 +20174,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
@@ -20176,10 +20182,10 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20191,7 +20197,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
@@ -20199,7 +20205,7 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C751" s="1">
         <x:v>50</x:v>
@@ -20222,10 +20228,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20234,10 +20240,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>9334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20245,10 +20251,10 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>1050</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20257,10 +20263,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>1050</x:v>
+        <x:v>9334</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
@@ -20271,7 +20277,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C754" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D754" s="1">
         <x:v>0</x:v>
@@ -20283,7 +20289,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
@@ -20291,7 +20297,7 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C755" s="1">
         <x:v>50</x:v>
@@ -20314,13 +20320,13 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D756" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E756" s="1">
         <x:v>0</x:v>
@@ -20329,7 +20335,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
@@ -20337,13 +20343,13 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D757" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E757" s="1">
         <x:v>0</x:v>
@@ -20352,7 +20358,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>50</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20360,10 +20366,10 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>19600</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20372,10 +20378,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>36600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
@@ -20383,10 +20389,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C759" s="1">
-        <x:v>50</x:v>
+        <x:v>19600</x:v>
       </x:c>
       <x:c r="D759" s="1">
         <x:v>0</x:v>
@@ -20395,10 +20401,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>50</x:v>
+        <x:v>36600</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
@@ -20406,13 +20412,13 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C760" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D760" s="1">
-        <x:v>0</x:v>
+        <x:v>362000</x:v>
       </x:c>
       <x:c r="E760" s="1">
         <x:v>0</x:v>
@@ -20421,7 +20427,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>50</x:v>
+        <x:v>362000</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
@@ -20429,7 +20435,7 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C761" s="1">
         <x:v>50</x:v>
@@ -20452,13 +20458,13 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D762" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E762" s="1">
         <x:v>0</x:v>
@@ -20467,7 +20473,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
@@ -20475,7 +20481,7 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C763" s="1">
         <x:v>50</x:v>
@@ -20498,22 +20504,22 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C764" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D764" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E764" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F764" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G764" s="1">
-        <x:v>30000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:7">
@@ -20521,7 +20527,7 @@
         <x:v>815</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C765" s="1">
         <x:v>50</x:v>
@@ -20544,22 +20550,22 @@
         <x:v>816</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C766" s="1">
-        <x:v>19050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D766" s="1">
-        <x:v>2700000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E766" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>2500</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>2721550</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
@@ -20567,10 +20573,10 @@
         <x:v>817</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C767" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D767" s="1">
         <x:v>0</x:v>
@@ -20582,7 +20588,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G767" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:7">
@@ -20590,33 +20596,33 @@
         <x:v>818</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C768" s="1">
-        <x:v>50</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D768" s="1">
-        <x:v>0</x:v>
+        <x:v>2700000</x:v>
       </x:c>
       <x:c r="E768" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>50</x:v>
+        <x:v>2721550</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
       <x:c r="A769" s="1" t="s">
-        <x:v>818</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C769" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D769" s="1">
         <x:v>0</x:v>
@@ -20625,18 +20631,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F769" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>35</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
       <x:c r="A770" s="1" t="s">
-        <x:v>819</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C770" s="1">
         <x:v>50</x:v>
@@ -20659,10 +20665,10 @@
         <x:v>820</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C771" s="1">
-        <x:v>6450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D771" s="1">
         <x:v>0</x:v>
@@ -20671,10 +20677,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F771" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G771" s="1">
-        <x:v>6450</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="772" spans="1:7">
@@ -20682,7 +20688,7 @@
         <x:v>821</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C772" s="1">
         <x:v>50</x:v>
@@ -20705,10 +20711,10 @@
         <x:v>822</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C773" s="1">
-        <x:v>0</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D773" s="1">
         <x:v>0</x:v>
@@ -20717,10 +20723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F773" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G773" s="1">
-        <x:v>1000</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="774" spans="1:7">
@@ -20728,7 +20734,7 @@
         <x:v>823</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C774" s="1">
         <x:v>50</x:v>
@@ -20740,10 +20746,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F774" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
@@ -20751,10 +20757,10 @@
         <x:v>824</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C775" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D775" s="1">
         <x:v>0</x:v>
@@ -20763,10 +20769,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
@@ -20774,10 +20780,10 @@
         <x:v>825</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C776" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D776" s="1">
         <x:v>0</x:v>
@@ -20786,10 +20792,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>13200</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>13200</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
@@ -20797,7 +20803,7 @@
         <x:v>826</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C777" s="1">
         <x:v>50</x:v>
@@ -20820,10 +20826,10 @@
         <x:v>827</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C778" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D778" s="1">
         <x:v>0</x:v>
@@ -20832,10 +20838,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F778" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
@@ -20843,13 +20849,13 @@
         <x:v>828</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D779" s="1">
-        <x:v>1962970</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E779" s="1">
         <x:v>0</x:v>
@@ -20858,7 +20864,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G779" s="1">
-        <x:v>1963020</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="780" spans="1:7">
@@ -20866,7 +20872,7 @@
         <x:v>829</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C780" s="1">
         <x:v>50</x:v>
@@ -20889,22 +20895,22 @@
         <x:v>830</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C781" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D781" s="1">
-        <x:v>0</x:v>
+        <x:v>1962970</x:v>
       </x:c>
       <x:c r="E781" s="1">
-        <x:v>16359294</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F781" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>50</x:v>
+        <x:v>1963020</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
@@ -20912,22 +20918,22 @@
         <x:v>831</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C782" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D782" s="1">
-        <x:v>487174</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E782" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F782" s="1">
-        <x:v>8500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G782" s="1">
-        <x:v>496674</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="783" spans="1:7">
@@ -20935,7 +20941,7 @@
         <x:v>832</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C783" s="1">
         <x:v>50</x:v>
@@ -20944,7 +20950,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E783" s="1">
-        <x:v>0</x:v>
+        <x:v>16359294</x:v>
       </x:c>
       <x:c r="F783" s="1">
         <x:v>0</x:v>
@@ -20958,22 +20964,22 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B784" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C784" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D784" s="1">
-        <x:v>0</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="E784" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F784" s="1">
-        <x:v>4999</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G784" s="1">
-        <x:v>5049</x:v>
+        <x:v>496674</x:v>
       </x:c>
     </x:row>
     <x:row r="785" spans="1:7">
@@ -20981,10 +20987,10 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="B785" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C785" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D785" s="1">
         <x:v>0</x:v>
@@ -20993,10 +20999,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F785" s="1">
-        <x:v>16500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G785" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="786" spans="1:7">
@@ -21004,7 +21010,7 @@
         <x:v>835</x:v>
       </x:c>
       <x:c r="B786" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C786" s="1">
         <x:v>50</x:v>
@@ -21016,10 +21022,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F786" s="1">
-        <x:v>0</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G786" s="1">
-        <x:v>50</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="787" spans="1:7">
@@ -21027,10 +21033,10 @@
         <x:v>836</x:v>
       </x:c>
       <x:c r="B787" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C787" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D787" s="1">
         <x:v>0</x:v>
@@ -21039,10 +21045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F787" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G787" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="788" spans="1:7">
@@ -21050,7 +21056,7 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B788" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C788" s="1">
         <x:v>50</x:v>
@@ -21073,7 +21079,7 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="B789" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C789" s="1">
         <x:v>50</x:v>
@@ -21085,10 +21091,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F789" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G789" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="790" spans="1:7">
@@ -21096,7 +21102,7 @@
         <x:v>839</x:v>
       </x:c>
       <x:c r="B790" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C790" s="1">
         <x:v>50</x:v>
@@ -21108,10 +21114,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F790" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G790" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="791" spans="1:7">
@@ -21119,7 +21125,7 @@
         <x:v>840</x:v>
       </x:c>
       <x:c r="B791" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C791" s="1">
         <x:v>50</x:v>
@@ -21131,10 +21137,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F791" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G791" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="792" spans="1:7">
@@ -21142,10 +21148,10 @@
         <x:v>841</x:v>
       </x:c>
       <x:c r="B792" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C792" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D792" s="1">
         <x:v>0</x:v>
@@ -21154,10 +21160,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F792" s="1">
-        <x:v>37300</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G792" s="1">
-        <x:v>48150</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="793" spans="1:7">
@@ -21165,10 +21171,10 @@
         <x:v>842</x:v>
       </x:c>
       <x:c r="B793" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C793" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D793" s="1">
         <x:v>0</x:v>
@@ -21177,10 +21183,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F793" s="1">
-        <x:v>83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G793" s="1">
-        <x:v>83</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="794" spans="1:7">
@@ -21188,33 +21194,33 @@
         <x:v>843</x:v>
       </x:c>
       <x:c r="B794" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C794" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D794" s="1">
-        <x:v>74852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E794" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F794" s="1">
-        <x:v>0</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G794" s="1">
-        <x:v>74852</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="795" spans="1:7">
       <x:c r="A795" s="1" t="s">
-        <x:v>843</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="B795" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C795" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D795" s="1">
         <x:v>0</x:v>
@@ -21223,24 +21229,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F795" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G795" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="796" spans="1:7">
       <x:c r="A796" s="1" t="s">
-        <x:v>844</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="B796" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C796" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D796" s="1">
-        <x:v>0</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="E796" s="1">
         <x:v>0</x:v>
@@ -21249,7 +21255,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G796" s="1">
-        <x:v>50</x:v>
+        <x:v>74852</x:v>
       </x:c>
     </x:row>
     <x:row r="797" spans="1:7">
@@ -21257,7 +21263,7 @@
         <x:v>845</x:v>
       </x:c>
       <x:c r="B797" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C797" s="1">
         <x:v>50</x:v>
@@ -21280,10 +21286,10 @@
         <x:v>846</x:v>
       </x:c>
       <x:c r="B798" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C798" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D798" s="1">
         <x:v>0</x:v>
@@ -21292,10 +21298,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F798" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G798" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="799" spans="1:7">
@@ -21303,21 +21309,67 @@
         <x:v>847</x:v>
       </x:c>
       <x:c r="B799" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C799" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D799" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E799" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F799" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G799" s="1">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="800" spans="1:7">
+      <x:c r="A800" s="1" t="s">
+        <x:v>848</x:v>
+      </x:c>
+      <x:c r="B800" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C800" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D800" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E800" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F800" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G800" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="801" spans="1:7">
+      <x:c r="A801" s="1" t="s">
+        <x:v>849</x:v>
+      </x:c>
+      <x:c r="B801" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C799" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D799" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E799" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F799" s="1">
+      <x:c r="C801" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D801" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E801" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F801" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G799" s="1">
+      <x:c r="G801" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -9142,13 +9142,13 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B270" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C270" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D270" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E270" s="1">
         <x:v>0</x:v>
@@ -9157,7 +9157,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G270" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="271" spans="1:7">
@@ -9165,13 +9165,13 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B271" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C271" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D271" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E271" s="1">
         <x:v>0</x:v>
@@ -9180,7 +9180,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G271" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="272" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17468,10 +17468,10 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17480,10 +17480,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17491,10 +17491,10 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C633" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D633" s="1">
         <x:v>0</x:v>
@@ -17503,10 +17503,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F633" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G633" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:7">
@@ -17928,22 +17928,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D652" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E652" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F652" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17951,22 +17951,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D653" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E653" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F653" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4643,7 +4643,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E74" s="1">
-        <x:v>98155764</x:v>
+        <x:v>98407482</x:v>
       </x:c>
       <x:c r="F74" s="1">
         <x:v>26600</x:v>
@@ -5448,7 +5448,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E109" s="1">
-        <x:v>16359294</x:v>
+        <x:v>16401247</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>0</x:v>
@@ -10597,7 +10597,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D333" s="1">
-        <x:v>72506796</x:v>
+        <x:v>72511212</x:v>
       </x:c>
       <x:c r="E333" s="1">
         <x:v>0</x:v>
@@ -10606,7 +10606,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G333" s="1">
-        <x:v>72532796</x:v>
+        <x:v>72537212</x:v>
       </x:c>
     </x:row>
     <x:row r="334" spans="1:7">
@@ -15611,7 +15611,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D551" s="1">
-        <x:v>8250000</x:v>
+        <x:v>8262225</x:v>
       </x:c>
       <x:c r="E551" s="1">
         <x:v>0</x:v>
@@ -15620,7 +15620,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>8250000</x:v>
+        <x:v>8262225</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -17008,7 +17008,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>0</x:v>
@@ -17031,7 +17031,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C613" s="1">
         <x:v>0</x:v>
@@ -17928,22 +17928,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D652" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E652" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F652" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17951,22 +17951,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D653" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E653" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F653" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -18742,7 +18742,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E687" s="1">
-        <x:v>16359294</x:v>
+        <x:v>16401247</x:v>
       </x:c>
       <x:c r="F687" s="1">
         <x:v>0</x:v>
@@ -18765,7 +18765,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E688" s="1">
-        <x:v>16359294</x:v>
+        <x:v>16401247</x:v>
       </x:c>
       <x:c r="F688" s="1">
         <x:v>0</x:v>
@@ -19271,7 +19271,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E710" s="1">
-        <x:v>0</x:v>
+        <x:v>77424</x:v>
       </x:c>
       <x:c r="F710" s="1">
         <x:v>14000</x:v>
@@ -20007,7 +20007,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E742" s="1">
-        <x:v>424596</x:v>
+        <x:v>429577</x:v>
       </x:c>
       <x:c r="F742" s="1">
         <x:v>0</x:v>
@@ -20418,7 +20418,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D760" s="1">
-        <x:v>362000</x:v>
+        <x:v>381352</x:v>
       </x:c>
       <x:c r="E760" s="1">
         <x:v>0</x:v>
@@ -20427,7 +20427,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>362000</x:v>
+        <x:v>381352</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
@@ -20950,7 +20950,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E783" s="1">
-        <x:v>16359294</x:v>
+        <x:v>16401247</x:v>
       </x:c>
       <x:c r="F783" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4433,7 +4433,7 @@
         <x:v>1050</x:v>
       </x:c>
       <x:c r="D65" s="1">
-        <x:v>75206</x:v>
+        <x:v>150412</x:v>
       </x:c>
       <x:c r="E65" s="1">
         <x:v>0</x:v>
@@ -4442,7 +4442,7 @@
         <x:v>6634</x:v>
       </x:c>
       <x:c r="G65" s="1">
-        <x:v>82890</x:v>
+        <x:v>158096</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
@@ -4643,7 +4643,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E74" s="1">
-        <x:v>98407482</x:v>
+        <x:v>139280694</x:v>
       </x:c>
       <x:c r="F74" s="1">
         <x:v>26600</x:v>
@@ -5448,7 +5448,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E109" s="1">
-        <x:v>16401247</x:v>
+        <x:v>23213449</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>0</x:v>
@@ -5882,7 +5882,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D128" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="E128" s="1">
         <x:v>0</x:v>
@@ -5891,7 +5891,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G128" s="1">
-        <x:v>75050</x:v>
+        <x:v>150050</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7">
@@ -7423,7 +7423,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="D195" s="1">
-        <x:v>584942</x:v>
+        <x:v>659925</x:v>
       </x:c>
       <x:c r="E195" s="1">
         <x:v>0</x:v>
@@ -7432,7 +7432,7 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="G195" s="1">
-        <x:v>594942</x:v>
+        <x:v>669925</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:7">
@@ -7630,7 +7630,7 @@
         <x:v>29250</x:v>
       </x:c>
       <x:c r="D204" s="1">
-        <x:v>388752</x:v>
+        <x:v>541436</x:v>
       </x:c>
       <x:c r="E204" s="1">
         <x:v>0</x:v>
@@ -7639,7 +7639,7 @@
         <x:v>75973</x:v>
       </x:c>
       <x:c r="G204" s="1">
-        <x:v>493975</x:v>
+        <x:v>646659</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:7">
@@ -7998,7 +7998,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D220" s="1">
-        <x:v>152226</x:v>
+        <x:v>304452</x:v>
       </x:c>
       <x:c r="E220" s="1">
         <x:v>0</x:v>
@@ -8007,7 +8007,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G220" s="1">
-        <x:v>152226</x:v>
+        <x:v>304452</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:7">
@@ -8044,7 +8044,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D222" s="1">
-        <x:v>74753</x:v>
+        <x:v>149506</x:v>
       </x:c>
       <x:c r="E222" s="1">
         <x:v>0</x:v>
@@ -8053,7 +8053,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G222" s="1">
-        <x:v>74753</x:v>
+        <x:v>149506</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:7">
@@ -9700,7 +9700,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="D294" s="1">
-        <x:v>74932</x:v>
+        <x:v>149864</x:v>
       </x:c>
       <x:c r="E294" s="1">
         <x:v>0</x:v>
@@ -9709,7 +9709,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G294" s="1">
-        <x:v>78932</x:v>
+        <x:v>153864</x:v>
       </x:c>
     </x:row>
     <x:row r="295" spans="1:7">
@@ -9723,7 +9723,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D295" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="E295" s="1">
         <x:v>0</x:v>
@@ -9732,7 +9732,7 @@
         <x:v>19900</x:v>
       </x:c>
       <x:c r="G295" s="1">
-        <x:v>94900</x:v>
+        <x:v>169900</x:v>
       </x:c>
     </x:row>
     <x:row r="296" spans="1:7">
@@ -10597,7 +10597,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D333" s="1">
-        <x:v>72511212</x:v>
+        <x:v>77063616</x:v>
       </x:c>
       <x:c r="E333" s="1">
         <x:v>0</x:v>
@@ -10606,7 +10606,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G333" s="1">
-        <x:v>72537212</x:v>
+        <x:v>77089616</x:v>
       </x:c>
     </x:row>
     <x:row r="334" spans="1:7">
@@ -10758,7 +10758,7 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="D340" s="1">
-        <x:v>1383600</x:v>
+        <x:v>1458299</x:v>
       </x:c>
       <x:c r="E340" s="1">
         <x:v>0</x:v>
@@ -10767,7 +10767,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G340" s="1">
-        <x:v>1386100</x:v>
+        <x:v>1460799</x:v>
       </x:c>
     </x:row>
     <x:row r="341" spans="1:7">
@@ -10781,7 +10781,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="D341" s="1">
-        <x:v>75227</x:v>
+        <x:v>150454</x:v>
       </x:c>
       <x:c r="E341" s="1">
         <x:v>0</x:v>
@@ -10790,7 +10790,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G341" s="1">
-        <x:v>80227</x:v>
+        <x:v>155454</x:v>
       </x:c>
     </x:row>
     <x:row r="342" spans="1:7">
@@ -12805,7 +12805,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D429" s="1">
-        <x:v>149204</x:v>
+        <x:v>298408</x:v>
       </x:c>
       <x:c r="E429" s="1">
         <x:v>0</x:v>
@@ -12814,7 +12814,7 @@
         <x:v>33600</x:v>
       </x:c>
       <x:c r="G429" s="1">
-        <x:v>182854</x:v>
+        <x:v>332058</x:v>
       </x:c>
     </x:row>
     <x:row r="430" spans="1:7">
@@ -12828,7 +12828,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D430" s="1">
-        <x:v>74602</x:v>
+        <x:v>149204</x:v>
       </x:c>
       <x:c r="E430" s="1">
         <x:v>0</x:v>
@@ -12837,7 +12837,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G430" s="1">
-        <x:v>74602</x:v>
+        <x:v>149204</x:v>
       </x:c>
     </x:row>
     <x:row r="431" spans="1:7">
@@ -13288,7 +13288,7 @@
         <x:v>1050</x:v>
       </x:c>
       <x:c r="D450" s="1">
-        <x:v>76114</x:v>
+        <x:v>152228</x:v>
       </x:c>
       <x:c r="E450" s="1">
         <x:v>0</x:v>
@@ -13297,7 +13297,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G450" s="1">
-        <x:v>77164</x:v>
+        <x:v>153278</x:v>
       </x:c>
     </x:row>
     <x:row r="451" spans="1:7">
@@ -13426,7 +13426,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="D456" s="1">
-        <x:v>75226</x:v>
+        <x:v>150452</x:v>
       </x:c>
       <x:c r="E456" s="1">
         <x:v>0</x:v>
@@ -13435,7 +13435,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G456" s="1">
-        <x:v>79226</x:v>
+        <x:v>154452</x:v>
       </x:c>
     </x:row>
     <x:row r="457" spans="1:7">
@@ -15384,7 +15384,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E541" s="1">
-        <x:v>20171730</x:v>
+        <x:v>32477826</x:v>
       </x:c>
       <x:c r="F541" s="1">
         <x:v>0</x:v>
@@ -15496,7 +15496,7 @@
         <x:v>2050</x:v>
       </x:c>
       <x:c r="D546" s="1">
-        <x:v>74692</x:v>
+        <x:v>149384</x:v>
       </x:c>
       <x:c r="E546" s="1">
         <x:v>0</x:v>
@@ -15505,7 +15505,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G546" s="1">
-        <x:v>76742</x:v>
+        <x:v>151434</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:7">
@@ -15956,7 +15956,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D566" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="E566" s="1">
         <x:v>0</x:v>
@@ -15965,7 +15965,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -16462,7 +16462,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D588" s="1">
-        <x:v>75844</x:v>
+        <x:v>151688</x:v>
       </x:c>
       <x:c r="E588" s="1">
         <x:v>0</x:v>
@@ -16471,7 +16471,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>75894</x:v>
+        <x:v>151738</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -17008,7 +17008,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>0</x:v>
@@ -17031,7 +17031,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C613" s="1">
         <x:v>0</x:v>
@@ -17106,7 +17106,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="D616" s="1">
-        <x:v>150640</x:v>
+        <x:v>301208</x:v>
       </x:c>
       <x:c r="E616" s="1">
         <x:v>0</x:v>
@@ -17115,7 +17115,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>150740</x:v>
+        <x:v>301308</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -17468,10 +17468,10 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17480,10 +17480,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17491,10 +17491,10 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C633" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D633" s="1">
         <x:v>0</x:v>
@@ -17503,10 +17503,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F633" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G633" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:7">
@@ -17704,7 +17704,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D642" s="1">
-        <x:v>74382</x:v>
+        <x:v>148764</x:v>
       </x:c>
       <x:c r="E642" s="1">
         <x:v>0</x:v>
@@ -17713,7 +17713,7 @@
         <x:v>11668</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>86050</x:v>
+        <x:v>160432</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
@@ -17727,7 +17727,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D643" s="1">
-        <x:v>74382</x:v>
+        <x:v>148764</x:v>
       </x:c>
       <x:c r="E643" s="1">
         <x:v>0</x:v>
@@ -17736,7 +17736,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G643" s="1">
-        <x:v>74382</x:v>
+        <x:v>148764</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:7">
@@ -17865,7 +17865,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D649" s="1">
-        <x:v>150562</x:v>
+        <x:v>301124</x:v>
       </x:c>
       <x:c r="E649" s="1">
         <x:v>0</x:v>
@@ -17874,7 +17874,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>150612</x:v>
+        <x:v>301174</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -18072,7 +18072,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D658" s="1">
-        <x:v>74852</x:v>
+        <x:v>149704</x:v>
       </x:c>
       <x:c r="E658" s="1">
         <x:v>0</x:v>
@@ -18081,7 +18081,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>74902</x:v>
+        <x:v>149754</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
@@ -18463,7 +18463,7 @@
         <x:v>6050</x:v>
       </x:c>
       <x:c r="D675" s="1">
-        <x:v>151234</x:v>
+        <x:v>302468</x:v>
       </x:c>
       <x:c r="E675" s="1">
         <x:v>0</x:v>
@@ -18472,7 +18472,7 @@
         <x:v>55833</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>213117</x:v>
+        <x:v>364351</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
@@ -18733,7 +18733,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -18742,7 +18742,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E687" s="1">
-        <x:v>16401247</x:v>
+        <x:v>23213449</x:v>
       </x:c>
       <x:c r="F687" s="1">
         <x:v>0</x:v>
@@ -18756,7 +18756,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C688" s="1">
         <x:v>0</x:v>
@@ -18765,7 +18765,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E688" s="1">
-        <x:v>16401247</x:v>
+        <x:v>23213449</x:v>
       </x:c>
       <x:c r="F688" s="1">
         <x:v>0</x:v>
@@ -19107,7 +19107,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D703" s="1">
-        <x:v>75281</x:v>
+        <x:v>150562</x:v>
       </x:c>
       <x:c r="E703" s="1">
         <x:v>0</x:v>
@@ -19116,7 +19116,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>75281</x:v>
+        <x:v>150562</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
@@ -19153,7 +19153,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>182279</x:v>
+        <x:v>257611</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
@@ -19162,7 +19162,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>182279</x:v>
+        <x:v>257611</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19452,7 +19452,7 @@
         <x:v>6550</x:v>
       </x:c>
       <x:c r="D718" s="1">
-        <x:v>73673</x:v>
+        <x:v>147346</x:v>
       </x:c>
       <x:c r="E718" s="1">
         <x:v>0</x:v>
@@ -19461,7 +19461,7 @@
         <x:v>3300</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>83523</x:v>
+        <x:v>157196</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
@@ -20950,7 +20950,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E783" s="1">
-        <x:v>16401247</x:v>
+        <x:v>23213449</x:v>
       </x:c>
       <x:c r="F783" s="1">
         <x:v>0</x:v>
@@ -21246,7 +21246,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D796" s="1">
-        <x:v>74852</x:v>
+        <x:v>149704</x:v>
       </x:c>
       <x:c r="E796" s="1">
         <x:v>0</x:v>
@@ -21255,7 +21255,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G796" s="1">
-        <x:v>74852</x:v>
+        <x:v>149704</x:v>
       </x:c>
     </x:row>
     <x:row r="797" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4643,7 +4643,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E74" s="1">
-        <x:v>139280694</x:v>
+        <x:v>142479450</x:v>
       </x:c>
       <x:c r="F74" s="1">
         <x:v>26600</x:v>
@@ -5448,7 +5448,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E109" s="1">
-        <x:v>23213449</x:v>
+        <x:v>23746575</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>0</x:v>
@@ -10597,7 +10597,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D333" s="1">
-        <x:v>77063616</x:v>
+        <x:v>78057692</x:v>
       </x:c>
       <x:c r="E333" s="1">
         <x:v>0</x:v>
@@ -10606,7 +10606,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G333" s="1">
-        <x:v>77089616</x:v>
+        <x:v>78083692</x:v>
       </x:c>
     </x:row>
     <x:row r="334" spans="1:7">
@@ -15611,7 +15611,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D551" s="1">
-        <x:v>8262225</x:v>
+        <x:v>8372112</x:v>
       </x:c>
       <x:c r="E551" s="1">
         <x:v>0</x:v>
@@ -15620,7 +15620,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>8262225</x:v>
+        <x:v>8372112</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -17008,7 +17008,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>0</x:v>
@@ -17031,7 +17031,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C613" s="1">
         <x:v>0</x:v>
@@ -17468,10 +17468,10 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17480,10 +17480,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17491,10 +17491,10 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C633" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D633" s="1">
         <x:v>0</x:v>
@@ -17503,10 +17503,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F633" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G633" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:7">
@@ -17928,22 +17928,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D652" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E652" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F652" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17951,22 +17951,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D653" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E653" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F653" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -18710,22 +18710,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E686" s="1">
-        <x:v>0</x:v>
+        <x:v>23746575</x:v>
       </x:c>
       <x:c r="F686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -18742,7 +18742,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E687" s="1">
-        <x:v>23213449</x:v>
+        <x:v>23746575</x:v>
       </x:c>
       <x:c r="F687" s="1">
         <x:v>0</x:v>
@@ -18756,22 +18756,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E688" s="1">
-        <x:v>23213449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -19271,7 +19271,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E710" s="1">
-        <x:v>77424</x:v>
+        <x:v>114053</x:v>
       </x:c>
       <x:c r="F710" s="1">
         <x:v>14000</x:v>
@@ -20007,7 +20007,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E742" s="1">
-        <x:v>429577</x:v>
+        <x:v>433936</x:v>
       </x:c>
       <x:c r="F742" s="1">
         <x:v>0</x:v>
@@ -20950,7 +20950,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E783" s="1">
-        <x:v>23213449</x:v>
+        <x:v>23746575</x:v>
       </x:c>
       <x:c r="F783" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17008,7 +17008,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>0</x:v>
@@ -17031,7 +17031,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C613" s="1">
         <x:v>0</x:v>
@@ -17928,22 +17928,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D652" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E652" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F652" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17951,22 +17951,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D653" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E653" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F653" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -18296,13 +18296,13 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D668" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E668" s="1">
         <x:v>0</x:v>
@@ -18311,7 +18311,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18319,13 +18319,13 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C669" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D669" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E669" s="1">
         <x:v>0</x:v>
@@ -18334,7 +18334,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
@@ -18710,22 +18710,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E686" s="1">
-        <x:v>23746575</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -18756,22 +18756,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E688" s="1">
-        <x:v>0</x:v>
+        <x:v>23746575</x:v>
       </x:c>
       <x:c r="F688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -20007,7 +20007,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E742" s="1">
-        <x:v>433936</x:v>
+        <x:v>438132</x:v>
       </x:c>
       <x:c r="F742" s="1">
         <x:v>0</x:v>
@@ -20418,7 +20418,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D760" s="1">
-        <x:v>381352</x:v>
+        <x:v>432714</x:v>
       </x:c>
       <x:c r="E760" s="1">
         <x:v>0</x:v>
@@ -20427,7 +20427,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>381352</x:v>
+        <x:v>432714</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4643,7 +4643,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E74" s="1">
-        <x:v>142479450</x:v>
+        <x:v>143614818</x:v>
       </x:c>
       <x:c r="F74" s="1">
         <x:v>26600</x:v>
@@ -5448,7 +5448,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E109" s="1">
-        <x:v>23746575</x:v>
+        <x:v>23935803</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>0</x:v>
@@ -10597,7 +10597,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D333" s="1">
-        <x:v>78057692</x:v>
+        <x:v>78150456</x:v>
       </x:c>
       <x:c r="E333" s="1">
         <x:v>0</x:v>
@@ -10606,7 +10606,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G333" s="1">
-        <x:v>78083692</x:v>
+        <x:v>78176456</x:v>
       </x:c>
     </x:row>
     <x:row r="334" spans="1:7">
@@ -15611,7 +15611,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D551" s="1">
-        <x:v>8372112</x:v>
+        <x:v>8746764</x:v>
       </x:c>
       <x:c r="E551" s="1">
         <x:v>0</x:v>
@@ -15620,7 +15620,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>8372112</x:v>
+        <x:v>8746764</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -17008,7 +17008,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>0</x:v>
@@ -17031,7 +17031,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C613" s="1">
         <x:v>0</x:v>
@@ -18733,7 +18733,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -18742,7 +18742,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E687" s="1">
-        <x:v>23746575</x:v>
+        <x:v>23935803</x:v>
       </x:c>
       <x:c r="F687" s="1">
         <x:v>0</x:v>
@@ -18756,7 +18756,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C688" s="1">
         <x:v>0</x:v>
@@ -18765,7 +18765,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E688" s="1">
-        <x:v>23746575</x:v>
+        <x:v>23935803</x:v>
       </x:c>
       <x:c r="F688" s="1">
         <x:v>0</x:v>
@@ -19271,7 +19271,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E710" s="1">
-        <x:v>114053</x:v>
+        <x:v>392890</x:v>
       </x:c>
       <x:c r="F710" s="1">
         <x:v>14000</x:v>
@@ -20007,7 +20007,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E742" s="1">
-        <x:v>438132</x:v>
+        <x:v>474362</x:v>
       </x:c>
       <x:c r="F742" s="1">
         <x:v>0</x:v>
@@ -20950,7 +20950,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E783" s="1">
-        <x:v>23746575</x:v>
+        <x:v>23935803</x:v>
       </x:c>
       <x:c r="F783" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17008,7 +17008,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>0</x:v>
@@ -17031,7 +17031,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C613" s="1">
         <x:v>0</x:v>
@@ -17468,10 +17468,10 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17480,10 +17480,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17491,10 +17491,10 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C633" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D633" s="1">
         <x:v>0</x:v>
@@ -17503,10 +17503,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F633" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G633" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:7">
@@ -18296,13 +18296,13 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D668" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E668" s="1">
         <x:v>0</x:v>
@@ -18311,7 +18311,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18319,13 +18319,13 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C669" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D669" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E669" s="1">
         <x:v>0</x:v>
@@ -18334,7 +18334,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
@@ -18733,7 +18733,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -18756,7 +18756,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C688" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -18733,7 +18733,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -18756,7 +18756,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C688" s="1">
         <x:v>0</x:v>
@@ -20418,7 +20418,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D760" s="1">
-        <x:v>432714</x:v>
+        <x:v>484076</x:v>
       </x:c>
       <x:c r="E760" s="1">
         <x:v>0</x:v>
@@ -20427,7 +20427,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>432714</x:v>
+        <x:v>484076</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -10597,7 +10597,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="D333" s="1">
-        <x:v>78150456</x:v>
+        <x:v>79789920</x:v>
       </x:c>
       <x:c r="E333" s="1">
         <x:v>0</x:v>
@@ -10606,7 +10606,7 @@
         <x:v>21500</x:v>
       </x:c>
       <x:c r="G333" s="1">
-        <x:v>78176456</x:v>
+        <x:v>79815920</x:v>
       </x:c>
     </x:row>
     <x:row r="334" spans="1:7">
@@ -15384,7 +15384,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E541" s="1">
-        <x:v>32477826</x:v>
+        <x:v>40428834</x:v>
       </x:c>
       <x:c r="F541" s="1">
         <x:v>0</x:v>
@@ -18733,7 +18733,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -18756,7 +18756,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C688" s="1">
         <x:v>0</x:v>
@@ -20418,7 +20418,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D760" s="1">
-        <x:v>484076</x:v>
+        <x:v>535438</x:v>
       </x:c>
       <x:c r="E760" s="1">
         <x:v>0</x:v>
@@ -20427,7 +20427,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>484076</x:v>
+        <x:v>535438</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -1429,6 +1429,9 @@
     <x:t>LEE, SUSIE</x:t>
   </x:si>
   <x:si>
+    <x:t>LEONARD, DON</x:t>
+  </x:si>
+  <x:si>
     <x:t>LESKO, DEBBIE</x:t>
   </x:si>
   <x:si>
@@ -1511,6 +1514,9 @@
   </x:si>
   <x:si>
     <x:t>MARKEY, EDWARD SEN.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARQUES, RHETT</x:t>
   </x:si>
   <x:si>
     <x:t>MARSHALL, ROGER W</x:t>
@@ -2634,8 +2640,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G801" totalsRowShown="0">
-  <x:autoFilter ref="A1:G801"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G803" totalsRowShown="0">
+  <x:autoFilter ref="A1:G803"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2937,7 +2943,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G801"/>
+  <x:dimension ref="A1:G803"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -7932,7 +7938,7 @@
         <x:v>2408433</x:v>
       </x:c>
       <x:c r="E217" s="1">
-        <x:v>0</x:v>
+        <x:v>101595</x:v>
       </x:c>
       <x:c r="F217" s="1">
         <x:v>10000</x:v>
@@ -9142,13 +9148,13 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B270" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C270" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D270" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E270" s="1">
         <x:v>0</x:v>
@@ -9157,7 +9163,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G270" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="271" spans="1:7">
@@ -9165,13 +9171,13 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B271" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C271" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D271" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E271" s="1">
         <x:v>0</x:v>
@@ -9180,7 +9186,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G271" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="272" spans="1:7">
@@ -12477,22 +12483,22 @@
         <x:v>471</x:v>
       </x:c>
       <x:c r="B415" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C415" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D415" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E415" s="1">
-        <x:v>0</x:v>
+        <x:v>80000</x:v>
       </x:c>
       <x:c r="F415" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G415" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="416" spans="1:7">
@@ -12500,22 +12506,22 @@
         <x:v>472</x:v>
       </x:c>
       <x:c r="B416" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C416" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D416" s="1">
-        <x:v>700000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E416" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F416" s="1">
-        <x:v>12000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G416" s="1">
-        <x:v>714500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="417" spans="1:7">
@@ -12523,22 +12529,22 @@
         <x:v>473</x:v>
       </x:c>
       <x:c r="B417" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C417" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D417" s="1">
-        <x:v>0</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="E417" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F417" s="1">
-        <x:v>5400</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G417" s="1">
-        <x:v>5450</x:v>
+        <x:v>714500</x:v>
       </x:c>
     </x:row>
     <x:row r="418" spans="1:7">
@@ -12546,7 +12552,7 @@
         <x:v>474</x:v>
       </x:c>
       <x:c r="B418" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C418" s="1">
         <x:v>50</x:v>
@@ -12558,10 +12564,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F418" s="1">
-        <x:v>0</x:v>
+        <x:v>5400</x:v>
       </x:c>
       <x:c r="G418" s="1">
-        <x:v>50</x:v>
+        <x:v>5450</x:v>
       </x:c>
     </x:row>
     <x:row r="419" spans="1:7">
@@ -12569,7 +12575,7 @@
         <x:v>475</x:v>
       </x:c>
       <x:c r="B419" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C419" s="1">
         <x:v>50</x:v>
@@ -12592,10 +12598,10 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="B420" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C420" s="1">
-        <x:v>23750</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D420" s="1">
         <x:v>0</x:v>
@@ -12604,10 +12610,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F420" s="1">
-        <x:v>25450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G420" s="1">
-        <x:v>49200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="421" spans="1:7">
@@ -12618,19 +12624,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C421" s="1">
-        <x:v>1050</x:v>
+        <x:v>23750</x:v>
       </x:c>
       <x:c r="D421" s="1">
-        <x:v>212696</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E421" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F421" s="1">
-        <x:v>10000</x:v>
+        <x:v>25450</x:v>
       </x:c>
       <x:c r="G421" s="1">
-        <x:v>223746</x:v>
+        <x:v>49200</x:v>
       </x:c>
     </x:row>
     <x:row r="422" spans="1:7">
@@ -12638,22 +12644,22 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B422" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C422" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D422" s="1">
-        <x:v>0</x:v>
+        <x:v>212696</x:v>
       </x:c>
       <x:c r="E422" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F422" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G422" s="1">
-        <x:v>50</x:v>
+        <x:v>223746</x:v>
       </x:c>
     </x:row>
     <x:row r="423" spans="1:7">
@@ -12661,7 +12667,7 @@
         <x:v>479</x:v>
       </x:c>
       <x:c r="B423" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C423" s="1">
         <x:v>50</x:v>
@@ -12684,22 +12690,22 @@
         <x:v>480</x:v>
       </x:c>
       <x:c r="B424" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C424" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D424" s="1">
-        <x:v>218548</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E424" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F424" s="1">
-        <x:v>58600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G424" s="1">
-        <x:v>279198</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="425" spans="1:7">
@@ -12707,22 +12713,22 @@
         <x:v>481</x:v>
       </x:c>
       <x:c r="B425" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C425" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D425" s="1">
-        <x:v>0</x:v>
+        <x:v>218548</x:v>
       </x:c>
       <x:c r="E425" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F425" s="1">
-        <x:v>0</x:v>
+        <x:v>58600</x:v>
       </x:c>
       <x:c r="G425" s="1">
-        <x:v>50</x:v>
+        <x:v>279198</x:v>
       </x:c>
     </x:row>
     <x:row r="426" spans="1:7">
@@ -12730,7 +12736,7 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="B426" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C426" s="1">
         <x:v>50</x:v>
@@ -12742,10 +12748,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F426" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G426" s="1">
-        <x:v>550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="427" spans="1:7">
@@ -12753,7 +12759,7 @@
         <x:v>483</x:v>
       </x:c>
       <x:c r="B427" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C427" s="1">
         <x:v>50</x:v>
@@ -12765,10 +12771,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F427" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G427" s="1">
-        <x:v>50</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="428" spans="1:7">
@@ -12776,7 +12782,7 @@
         <x:v>484</x:v>
       </x:c>
       <x:c r="B428" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C428" s="1">
         <x:v>50</x:v>
@@ -12799,45 +12805,45 @@
         <x:v>485</x:v>
       </x:c>
       <x:c r="B429" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C429" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D429" s="1">
-        <x:v>298408</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E429" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F429" s="1">
-        <x:v>33600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G429" s="1">
-        <x:v>332058</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="430" spans="1:7">
       <x:c r="A430" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B430" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C430" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D430" s="1">
-        <x:v>149204</x:v>
+        <x:v>298408</x:v>
       </x:c>
       <x:c r="E430" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F430" s="1">
-        <x:v>0</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G430" s="1">
-        <x:v>149204</x:v>
+        <x:v>332058</x:v>
       </x:c>
     </x:row>
     <x:row r="431" spans="1:7">
@@ -12845,13 +12851,13 @@
         <x:v>486</x:v>
       </x:c>
       <x:c r="B431" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C431" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D431" s="1">
-        <x:v>0</x:v>
+        <x:v>149204</x:v>
       </x:c>
       <x:c r="E431" s="1">
         <x:v>0</x:v>
@@ -12860,7 +12866,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G431" s="1">
-        <x:v>50</x:v>
+        <x:v>149204</x:v>
       </x:c>
     </x:row>
     <x:row r="432" spans="1:7">
@@ -12868,10 +12874,10 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B432" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C432" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D432" s="1">
         <x:v>0</x:v>
@@ -12880,10 +12886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F432" s="1">
-        <x:v>22650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G432" s="1">
-        <x:v>28700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="433" spans="1:7">
@@ -12891,10 +12897,10 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B433" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C433" s="1">
-        <x:v>19400</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D433" s="1">
         <x:v>0</x:v>
@@ -12903,10 +12909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F433" s="1">
-        <x:v>11600</x:v>
+        <x:v>22650</x:v>
       </x:c>
       <x:c r="G433" s="1">
-        <x:v>31000</x:v>
+        <x:v>28700</x:v>
       </x:c>
     </x:row>
     <x:row r="434" spans="1:7">
@@ -12914,10 +12920,10 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="B434" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C434" s="1">
-        <x:v>50</x:v>
+        <x:v>19400</x:v>
       </x:c>
       <x:c r="D434" s="1">
         <x:v>0</x:v>
@@ -12926,10 +12932,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F434" s="1">
-        <x:v>0</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G434" s="1">
-        <x:v>50</x:v>
+        <x:v>31000</x:v>
       </x:c>
     </x:row>
     <x:row r="435" spans="1:7">
@@ -12937,7 +12943,7 @@
         <x:v>490</x:v>
       </x:c>
       <x:c r="B435" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C435" s="1">
         <x:v>50</x:v>
@@ -12960,7 +12966,7 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B436" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C436" s="1">
         <x:v>50</x:v>
@@ -12983,7 +12989,7 @@
         <x:v>492</x:v>
       </x:c>
       <x:c r="B437" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C437" s="1">
         <x:v>50</x:v>
@@ -13009,7 +13015,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C438" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D438" s="1">
         <x:v>0</x:v>
@@ -13021,7 +13027,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G438" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="439" spans="1:7">
@@ -13029,10 +13035,10 @@
         <x:v>494</x:v>
       </x:c>
       <x:c r="B439" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C439" s="1">
-        <x:v>50</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D439" s="1">
         <x:v>0</x:v>
@@ -13041,10 +13047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F439" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G439" s="1">
-        <x:v>5850</x:v>
+        <x:v>2950</x:v>
       </x:c>
     </x:row>
     <x:row r="440" spans="1:7">
@@ -13052,10 +13058,10 @@
         <x:v>495</x:v>
       </x:c>
       <x:c r="B440" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C440" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D440" s="1">
         <x:v>0</x:v>
@@ -13064,10 +13070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F440" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G440" s="1">
-        <x:v>2500</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="441" spans="1:7">
@@ -13075,10 +13081,10 @@
         <x:v>496</x:v>
       </x:c>
       <x:c r="B441" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C441" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D441" s="1">
         <x:v>0</x:v>
@@ -13087,10 +13093,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F441" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G441" s="1">
-        <x:v>1000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="442" spans="1:7">
@@ -13098,10 +13104,10 @@
         <x:v>497</x:v>
       </x:c>
       <x:c r="B442" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C442" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D442" s="1">
         <x:v>0</x:v>
@@ -13110,10 +13116,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F442" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G442" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="443" spans="1:7">
@@ -13121,7 +13127,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="B443" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C443" s="1">
         <x:v>50</x:v>
@@ -13133,10 +13139,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F443" s="1">
-        <x:v>1715</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G443" s="1">
-        <x:v>1765</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="444" spans="1:7">
@@ -13144,10 +13150,10 @@
         <x:v>499</x:v>
       </x:c>
       <x:c r="B444" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C444" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D444" s="1">
         <x:v>0</x:v>
@@ -13156,10 +13162,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F444" s="1">
-        <x:v>14000</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="G444" s="1">
-        <x:v>15050</x:v>
+        <x:v>1765</x:v>
       </x:c>
     </x:row>
     <x:row r="445" spans="1:7">
@@ -13167,22 +13173,22 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="B445" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C445" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D445" s="1">
-        <x:v>0</x:v>
+        <x:v>101595</x:v>
       </x:c>
       <x:c r="E445" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F445" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G445" s="1">
-        <x:v>6650</x:v>
+        <x:v>101595</x:v>
       </x:c>
     </x:row>
     <x:row r="446" spans="1:7">
@@ -13190,10 +13196,10 @@
         <x:v>501</x:v>
       </x:c>
       <x:c r="B446" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C446" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D446" s="1">
         <x:v>0</x:v>
@@ -13202,10 +13208,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F446" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G446" s="1">
-        <x:v>50</x:v>
+        <x:v>15050</x:v>
       </x:c>
     </x:row>
     <x:row r="447" spans="1:7">
@@ -13213,22 +13219,22 @@
         <x:v>502</x:v>
       </x:c>
       <x:c r="B447" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C447" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D447" s="1">
-        <x:v>582915</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E447" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F447" s="1">
-        <x:v>5800</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G447" s="1">
-        <x:v>591215</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="448" spans="1:7">
@@ -13236,7 +13242,7 @@
         <x:v>503</x:v>
       </x:c>
       <x:c r="B448" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C448" s="1">
         <x:v>50</x:v>
@@ -13259,22 +13265,22 @@
         <x:v>504</x:v>
       </x:c>
       <x:c r="B449" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C449" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D449" s="1">
-        <x:v>0</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="E449" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F449" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G449" s="1">
-        <x:v>50</x:v>
+        <x:v>591215</x:v>
       </x:c>
     </x:row>
     <x:row r="450" spans="1:7">
@@ -13282,13 +13288,13 @@
         <x:v>505</x:v>
       </x:c>
       <x:c r="B450" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C450" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D450" s="1">
-        <x:v>152228</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E450" s="1">
         <x:v>0</x:v>
@@ -13297,7 +13303,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G450" s="1">
-        <x:v>153278</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="451" spans="1:7">
@@ -13305,22 +13311,22 @@
         <x:v>506</x:v>
       </x:c>
       <x:c r="B451" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C451" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D451" s="1">
-        <x:v>112913</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E451" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F451" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G451" s="1">
-        <x:v>117913</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="452" spans="1:7">
@@ -13328,22 +13334,22 @@
         <x:v>507</x:v>
       </x:c>
       <x:c r="B452" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C452" s="1">
-        <x:v>0</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D452" s="1">
-        <x:v>0</x:v>
+        <x:v>152228</x:v>
       </x:c>
       <x:c r="E452" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F452" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G452" s="1">
-        <x:v>250</x:v>
+        <x:v>153278</x:v>
       </x:c>
     </x:row>
     <x:row r="453" spans="1:7">
@@ -13351,22 +13357,22 @@
         <x:v>508</x:v>
       </x:c>
       <x:c r="B453" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C453" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D453" s="1">
-        <x:v>0</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="E453" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F453" s="1">
-        <x:v>2000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G453" s="1">
-        <x:v>2000</x:v>
+        <x:v>117913</x:v>
       </x:c>
     </x:row>
     <x:row r="454" spans="1:7">
@@ -13374,10 +13380,10 @@
         <x:v>509</x:v>
       </x:c>
       <x:c r="B454" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C454" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D454" s="1">
         <x:v>0</x:v>
@@ -13386,10 +13392,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F454" s="1">
-        <x:v>46300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G454" s="1">
-        <x:v>46350</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="455" spans="1:7">
@@ -13397,10 +13403,10 @@
         <x:v>510</x:v>
       </x:c>
       <x:c r="B455" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C455" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D455" s="1">
         <x:v>0</x:v>
@@ -13409,10 +13415,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F455" s="1">
-        <x:v>500</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G455" s="1">
-        <x:v>550</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="456" spans="1:7">
@@ -13420,22 +13426,22 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="B456" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C456" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D456" s="1">
-        <x:v>150452</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E456" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F456" s="1">
-        <x:v>0</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="G456" s="1">
-        <x:v>154452</x:v>
+        <x:v>46350</x:v>
       </x:c>
     </x:row>
     <x:row r="457" spans="1:7">
@@ -13443,7 +13449,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="B457" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C457" s="1">
         <x:v>50</x:v>
@@ -13455,10 +13461,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F457" s="1">
-        <x:v>250</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G457" s="1">
-        <x:v>300</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="458" spans="1:7">
@@ -13466,13 +13472,13 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B458" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C458" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D458" s="1">
-        <x:v>0</x:v>
+        <x:v>150452</x:v>
       </x:c>
       <x:c r="E458" s="1">
         <x:v>0</x:v>
@@ -13481,7 +13487,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G458" s="1">
-        <x:v>50</x:v>
+        <x:v>154452</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:7">
@@ -13489,7 +13495,7 @@
         <x:v>514</x:v>
       </x:c>
       <x:c r="B459" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C459" s="1">
         <x:v>50</x:v>
@@ -13501,10 +13507,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F459" s="1">
-        <x:v>7900</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G459" s="1">
-        <x:v>7950</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="460" spans="1:7">
@@ -13512,22 +13518,22 @@
         <x:v>515</x:v>
       </x:c>
       <x:c r="B460" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C460" s="1">
-        <x:v>13300</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D460" s="1">
-        <x:v>104910</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E460" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F460" s="1">
-        <x:v>20050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G460" s="1">
-        <x:v>138260</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="461" spans="1:7">
@@ -13535,10 +13541,10 @@
         <x:v>516</x:v>
       </x:c>
       <x:c r="B461" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C461" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D461" s="1">
         <x:v>0</x:v>
@@ -13547,10 +13553,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F461" s="1">
-        <x:v>250</x:v>
+        <x:v>7900</x:v>
       </x:c>
       <x:c r="G461" s="1">
-        <x:v>250</x:v>
+        <x:v>7950</x:v>
       </x:c>
     </x:row>
     <x:row r="462" spans="1:7">
@@ -13558,22 +13564,22 @@
         <x:v>517</x:v>
       </x:c>
       <x:c r="B462" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C462" s="1">
-        <x:v>5000</x:v>
+        <x:v>13300</x:v>
       </x:c>
       <x:c r="D462" s="1">
-        <x:v>0</x:v>
+        <x:v>104910</x:v>
       </x:c>
       <x:c r="E462" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F462" s="1">
-        <x:v>1500</x:v>
+        <x:v>20050</x:v>
       </x:c>
       <x:c r="G462" s="1">
-        <x:v>6500</x:v>
+        <x:v>138260</x:v>
       </x:c>
     </x:row>
     <x:row r="463" spans="1:7">
@@ -13584,7 +13590,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C463" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D463" s="1">
         <x:v>0</x:v>
@@ -13593,10 +13599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F463" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G463" s="1">
-        <x:v>1000</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="464" spans="1:7">
@@ -13604,10 +13610,10 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B464" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C464" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D464" s="1">
         <x:v>0</x:v>
@@ -13616,10 +13622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F464" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G464" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="465" spans="1:7">
@@ -13627,10 +13633,10 @@
         <x:v>520</x:v>
       </x:c>
       <x:c r="B465" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C465" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D465" s="1">
         <x:v>0</x:v>
@@ -13642,7 +13648,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G465" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="466" spans="1:7">
@@ -13650,13 +13656,13 @@
         <x:v>521</x:v>
       </x:c>
       <x:c r="B466" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C466" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D466" s="1">
-        <x:v>382680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E466" s="1">
         <x:v>0</x:v>
@@ -13665,7 +13671,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G466" s="1">
-        <x:v>382680</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="467" spans="1:7">
@@ -13673,22 +13679,22 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B467" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C467" s="1">
-        <x:v>8670</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D467" s="1">
-        <x:v>126626</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E467" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F467" s="1">
-        <x:v>8000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G467" s="1">
-        <x:v>143296</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="468" spans="1:7">
@@ -13696,13 +13702,13 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B468" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C468" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D468" s="1">
-        <x:v>0</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="E468" s="1">
         <x:v>0</x:v>
@@ -13711,7 +13717,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G468" s="1">
-        <x:v>50</x:v>
+        <x:v>382680</x:v>
       </x:c>
     </x:row>
     <x:row r="469" spans="1:7">
@@ -13719,22 +13725,22 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>0</x:v>
+        <x:v>8670</x:v>
       </x:c>
       <x:c r="D469" s="1">
-        <x:v>1013834</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="E469" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>1013834</x:v>
+        <x:v>143296</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -13742,22 +13748,22 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E470" s="1">
-        <x:v>268690</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -13768,10 +13774,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D471" s="1">
-        <x:v>0</x:v>
+        <x:v>1013834</x:v>
       </x:c>
       <x:c r="E471" s="1">
         <x:v>0</x:v>
@@ -13780,7 +13786,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>50</x:v>
+        <x:v>1013834</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -13788,7 +13794,7 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C472" s="1">
         <x:v>0</x:v>
@@ -13797,13 +13803,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E472" s="1">
-        <x:v>0</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -13811,7 +13817,7 @@
         <x:v>528</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C473" s="1">
         <x:v>50</x:v>
@@ -13834,10 +13840,10 @@
         <x:v>529</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C474" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D474" s="1">
         <x:v>0</x:v>
@@ -13846,10 +13852,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F474" s="1">
-        <x:v>1000</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G474" s="1">
-        <x:v>1050</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="475" spans="1:7">
@@ -13857,13 +13863,13 @@
         <x:v>530</x:v>
       </x:c>
       <x:c r="B475" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C475" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D475" s="1">
-        <x:v>923885</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E475" s="1">
         <x:v>0</x:v>
@@ -13872,7 +13878,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G475" s="1">
-        <x:v>923885</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="476" spans="1:7">
@@ -13880,22 +13886,22 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B476" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C476" s="1">
-        <x:v>8550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D476" s="1">
-        <x:v>92320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E476" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F476" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G476" s="1">
-        <x:v>100870</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="477" spans="1:7">
@@ -13909,16 +13915,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D477" s="1">
-        <x:v>6471279</x:v>
+        <x:v>923885</x:v>
       </x:c>
       <x:c r="E477" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>6474779</x:v>
+        <x:v>923885</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -13926,13 +13932,13 @@
         <x:v>533</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>1550</x:v>
+        <x:v>8550</x:v>
       </x:c>
       <x:c r="D478" s="1">
-        <x:v>512918</x:v>
+        <x:v>92320</x:v>
       </x:c>
       <x:c r="E478" s="1">
         <x:v>0</x:v>
@@ -13941,7 +13947,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>514468</x:v>
+        <x:v>100870</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -13949,22 +13955,22 @@
         <x:v>534</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>1550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D479" s="1">
-        <x:v>0</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="E479" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>1550</x:v>
+        <x:v>6474779</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -13972,13 +13978,13 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B480" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C480" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D480" s="1">
-        <x:v>0</x:v>
+        <x:v>512918</x:v>
       </x:c>
       <x:c r="E480" s="1">
         <x:v>0</x:v>
@@ -13987,7 +13993,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G480" s="1">
-        <x:v>50</x:v>
+        <x:v>514468</x:v>
       </x:c>
     </x:row>
     <x:row r="481" spans="1:7">
@@ -13995,13 +14001,13 @@
         <x:v>536</x:v>
       </x:c>
       <x:c r="B481" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C481" s="1">
-        <x:v>2500</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D481" s="1">
-        <x:v>504020</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E481" s="1">
         <x:v>0</x:v>
@@ -14010,7 +14016,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G481" s="1">
-        <x:v>506520</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="482" spans="1:7">
@@ -14018,10 +14024,10 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="B482" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C482" s="1">
-        <x:v>4050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D482" s="1">
         <x:v>0</x:v>
@@ -14033,7 +14039,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G482" s="1">
-        <x:v>4050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="483" spans="1:7">
@@ -14041,13 +14047,13 @@
         <x:v>538</x:v>
       </x:c>
       <x:c r="B483" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C483" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D483" s="1">
-        <x:v>0</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="E483" s="1">
         <x:v>0</x:v>
@@ -14056,7 +14062,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G483" s="1">
-        <x:v>50</x:v>
+        <x:v>506520</x:v>
       </x:c>
     </x:row>
     <x:row r="484" spans="1:7">
@@ -14064,10 +14070,10 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="B484" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C484" s="1">
-        <x:v>50</x:v>
+        <x:v>4050</x:v>
       </x:c>
       <x:c r="D484" s="1">
         <x:v>0</x:v>
@@ -14079,7 +14085,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G484" s="1">
-        <x:v>50</x:v>
+        <x:v>4050</x:v>
       </x:c>
     </x:row>
     <x:row r="485" spans="1:7">
@@ -14087,10 +14093,10 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="B485" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C485" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D485" s="1">
         <x:v>0</x:v>
@@ -14099,10 +14105,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F485" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G485" s="1">
-        <x:v>3667</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="486" spans="1:7">
@@ -14110,10 +14116,10 @@
         <x:v>541</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C486" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D486" s="1">
         <x:v>0</x:v>
@@ -14125,7 +14131,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G486" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="487" spans="1:7">
@@ -14133,22 +14139,22 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="B487" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C487" s="1">
-        <x:v>500</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D487" s="1">
-        <x:v>107940</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E487" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F487" s="1">
-        <x:v>1500</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G487" s="1">
-        <x:v>109940</x:v>
+        <x:v>3667</x:v>
       </x:c>
     </x:row>
     <x:row r="488" spans="1:7">
@@ -14156,10 +14162,10 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B488" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C488" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D488" s="1">
         <x:v>0</x:v>
@@ -14171,7 +14177,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G488" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="489" spans="1:7">
@@ -14179,22 +14185,22 @@
         <x:v>544</x:v>
       </x:c>
       <x:c r="B489" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C489" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D489" s="1">
-        <x:v>0</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="E489" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F489" s="1">
-        <x:v>6200</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G489" s="1">
-        <x:v>7200</x:v>
+        <x:v>109940</x:v>
       </x:c>
     </x:row>
     <x:row r="490" spans="1:7">
@@ -14202,10 +14208,10 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="B490" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C490" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D490" s="1">
         <x:v>0</x:v>
@@ -14214,10 +14220,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F490" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G490" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="491" spans="1:7">
@@ -14225,10 +14231,10 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="B491" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C491" s="1">
-        <x:v>2500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D491" s="1">
         <x:v>0</x:v>
@@ -14237,10 +14243,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F491" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G491" s="1">
-        <x:v>2500</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="492" spans="1:7">
@@ -14248,10 +14254,10 @@
         <x:v>547</x:v>
       </x:c>
       <x:c r="B492" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C492" s="1">
-        <x:v>5050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D492" s="1">
         <x:v>0</x:v>
@@ -14260,10 +14266,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F492" s="1">
-        <x:v>1000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G492" s="1">
-        <x:v>6050</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="493" spans="1:7">
@@ -14271,10 +14277,10 @@
         <x:v>548</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C493" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D493" s="1">
         <x:v>0</x:v>
@@ -14286,7 +14292,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G493" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="494" spans="1:7">
@@ -14294,22 +14300,22 @@
         <x:v>549</x:v>
       </x:c>
       <x:c r="B494" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C494" s="1">
+        <x:v>5050</x:v>
+      </x:c>
+      <x:c r="D494" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E494" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F494" s="1">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="D494" s="1">
-        <x:v>800044</x:v>
-      </x:c>
-      <x:c r="E494" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F494" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G494" s="1">
-        <x:v>801044</x:v>
+        <x:v>6050</x:v>
       </x:c>
     </x:row>
     <x:row r="495" spans="1:7">
@@ -14317,22 +14323,22 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="B495" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C495" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D495" s="1">
-        <x:v>50315254</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E495" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F495" s="1">
-        <x:v>8000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G495" s="1">
-        <x:v>50326754</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="496" spans="1:7">
@@ -14340,13 +14346,13 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C496" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D496" s="1">
-        <x:v>0</x:v>
+        <x:v>800044</x:v>
       </x:c>
       <x:c r="E496" s="1">
         <x:v>0</x:v>
@@ -14355,7 +14361,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G496" s="1">
-        <x:v>50</x:v>
+        <x:v>801044</x:v>
       </x:c>
     </x:row>
     <x:row r="497" spans="1:7">
@@ -14363,22 +14369,22 @@
         <x:v>552</x:v>
       </x:c>
       <x:c r="B497" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C497" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D497" s="1">
-        <x:v>726377</x:v>
+        <x:v>50315254</x:v>
       </x:c>
       <x:c r="E497" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F497" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G497" s="1">
-        <x:v>726377</x:v>
+        <x:v>50326754</x:v>
       </x:c>
     </x:row>
     <x:row r="498" spans="1:7">
@@ -14386,22 +14392,22 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B498" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C498" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D498" s="1">
-        <x:v>668449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E498" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F498" s="1">
-        <x:v>14600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G498" s="1">
-        <x:v>685549</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="499" spans="1:7">
@@ -14409,13 +14415,13 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B499" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C499" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D499" s="1">
-        <x:v>0</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="E499" s="1">
         <x:v>0</x:v>
@@ -14424,7 +14430,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G499" s="1">
-        <x:v>1000</x:v>
+        <x:v>726377</x:v>
       </x:c>
     </x:row>
     <x:row r="500" spans="1:7">
@@ -14432,22 +14438,22 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B500" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C500" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D500" s="1">
-        <x:v>0</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="E500" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F500" s="1">
-        <x:v>1250</x:v>
+        <x:v>14600</x:v>
       </x:c>
       <x:c r="G500" s="1">
-        <x:v>1300</x:v>
+        <x:v>685549</x:v>
       </x:c>
     </x:row>
     <x:row r="501" spans="1:7">
@@ -14455,10 +14461,10 @@
         <x:v>556</x:v>
       </x:c>
       <x:c r="B501" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C501" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D501" s="1">
         <x:v>0</x:v>
@@ -14470,7 +14476,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G501" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="502" spans="1:7">
@@ -14478,22 +14484,22 @@
         <x:v>557</x:v>
       </x:c>
       <x:c r="B502" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C502" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D502" s="1">
-        <x:v>120404787</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E502" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F502" s="1">
-        <x:v>0</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="G502" s="1">
-        <x:v>120406787</x:v>
+        <x:v>1300</x:v>
       </x:c>
     </x:row>
     <x:row r="503" spans="1:7">
@@ -14501,13 +14507,13 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="B503" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C503" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D503" s="1">
-        <x:v>442806</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E503" s="1">
         <x:v>0</x:v>
@@ -14516,7 +14522,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G503" s="1">
-        <x:v>442806</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="504" spans="1:7">
@@ -14524,22 +14530,22 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C504" s="1">
-        <x:v>1000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D504" s="1">
-        <x:v>0</x:v>
+        <x:v>120404787</x:v>
       </x:c>
       <x:c r="E504" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F504" s="1">
-        <x:v>3333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G504" s="1">
-        <x:v>4333</x:v>
+        <x:v>120406787</x:v>
       </x:c>
     </x:row>
     <x:row r="505" spans="1:7">
@@ -14547,22 +14553,22 @@
         <x:v>560</x:v>
       </x:c>
       <x:c r="B505" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C505" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D505" s="1">
-        <x:v>0</x:v>
+        <x:v>442806</x:v>
       </x:c>
       <x:c r="E505" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F505" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G505" s="1">
-        <x:v>14050</x:v>
+        <x:v>442806</x:v>
       </x:c>
     </x:row>
     <x:row r="506" spans="1:7">
@@ -14573,7 +14579,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="C506" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D506" s="1">
         <x:v>0</x:v>
@@ -14582,10 +14588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F506" s="1">
-        <x:v>0</x:v>
+        <x:v>3333</x:v>
       </x:c>
       <x:c r="G506" s="1">
-        <x:v>50</x:v>
+        <x:v>4333</x:v>
       </x:c>
     </x:row>
     <x:row r="507" spans="1:7">
@@ -14593,10 +14599,10 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C507" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D507" s="1">
         <x:v>0</x:v>
@@ -14605,10 +14611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F507" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G507" s="1">
-        <x:v>5000</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="508" spans="1:7">
@@ -14616,7 +14622,7 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C508" s="1">
         <x:v>50</x:v>
@@ -14628,10 +14634,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F508" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G508" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="509" spans="1:7">
@@ -14639,10 +14645,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C509" s="1">
-        <x:v>2700</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D509" s="1">
         <x:v>0</x:v>
@@ -14651,10 +14657,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F509" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G509" s="1">
-        <x:v>5400</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="510" spans="1:7">
@@ -14662,7 +14668,7 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C510" s="1">
         <x:v>50</x:v>
@@ -14674,10 +14680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F510" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G510" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="511" spans="1:7">
@@ -14685,10 +14691,10 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C511" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D511" s="1">
         <x:v>0</x:v>
@@ -14697,10 +14703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F511" s="1">
-        <x:v>12000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G511" s="1">
-        <x:v>12050</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="512" spans="1:7">
@@ -14708,7 +14714,7 @@
         <x:v>567</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C512" s="1">
         <x:v>50</x:v>
@@ -14731,22 +14737,22 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C513" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D513" s="1">
-        <x:v>151713</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E513" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F513" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G513" s="1">
-        <x:v>151713</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="514" spans="1:7">
@@ -14754,10 +14760,10 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B514" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C514" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D514" s="1">
         <x:v>0</x:v>
@@ -14766,10 +14772,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F514" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G514" s="1">
-        <x:v>250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="515" spans="1:7">
@@ -14780,10 +14786,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="C515" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D515" s="1">
-        <x:v>0</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="E515" s="1">
         <x:v>0</x:v>
@@ -14792,7 +14798,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G515" s="1">
-        <x:v>50</x:v>
+        <x:v>151713</x:v>
       </x:c>
     </x:row>
     <x:row r="516" spans="1:7">
@@ -14800,10 +14806,10 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="B516" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C516" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D516" s="1">
         <x:v>0</x:v>
@@ -14812,10 +14818,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F516" s="1">
-        <x:v>2700</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G516" s="1">
-        <x:v>2750</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="517" spans="1:7">
@@ -14823,10 +14829,10 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="B517" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C517" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D517" s="1">
         <x:v>0</x:v>
@@ -14835,10 +14841,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>4600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>4600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -14846,7 +14852,7 @@
         <x:v>573</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C518" s="1">
         <x:v>50</x:v>
@@ -14858,10 +14864,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>50</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -14869,10 +14875,10 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="B519" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C519" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D519" s="1">
         <x:v>0</x:v>
@@ -14881,10 +14887,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F519" s="1">
-        <x:v>0</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G519" s="1">
-        <x:v>50</x:v>
+        <x:v>4600</x:v>
       </x:c>
     </x:row>
     <x:row r="520" spans="1:7">
@@ -14892,7 +14898,7 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C520" s="1">
         <x:v>50</x:v>
@@ -14915,7 +14921,7 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B521" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C521" s="1">
         <x:v>50</x:v>
@@ -14938,13 +14944,13 @@
         <x:v>577</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C522" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D522" s="1">
-        <x:v>282526</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E522" s="1">
         <x:v>0</x:v>
@@ -14953,7 +14959,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G522" s="1">
-        <x:v>282526</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="523" spans="1:7">
@@ -14961,10 +14967,10 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C523" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D523" s="1">
         <x:v>0</x:v>
@@ -14973,10 +14979,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F523" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G523" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="524" spans="1:7">
@@ -14984,13 +14990,13 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C524" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D524" s="1">
-        <x:v>0</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E524" s="1">
         <x:v>0</x:v>
@@ -14999,7 +15005,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>50</x:v>
+        <x:v>282526</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -15007,22 +15013,22 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C525" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D525" s="1">
-        <x:v>116161</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E525" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F525" s="1">
-        <x:v>4500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>124661</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -15030,7 +15036,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C526" s="1">
         <x:v>50</x:v>
@@ -15053,22 +15059,22 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B527" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C527" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D527" s="1">
-        <x:v>0</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="E527" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F527" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G527" s="1">
-        <x:v>50</x:v>
+        <x:v>124661</x:v>
       </x:c>
     </x:row>
     <x:row r="528" spans="1:7">
@@ -15076,7 +15082,7 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>584</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C528" s="1">
         <x:v>50</x:v>
@@ -15096,10 +15102,10 @@
     </x:row>
     <x:row r="529" spans="1:7">
       <x:c r="A529" s="1" t="s">
-        <x:v>585</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C529" s="1">
         <x:v>50</x:v>
@@ -15119,25 +15125,25 @@
     </x:row>
     <x:row r="530" spans="1:7">
       <x:c r="A530" s="1" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B530" s="1" t="s">
         <x:v>586</x:v>
       </x:c>
-      <x:c r="B530" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="C530" s="1">
-        <x:v>8000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D530" s="1">
-        <x:v>2997852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E530" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F530" s="1">
-        <x:v>6800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G530" s="1">
-        <x:v>3012652</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="531" spans="1:7">
@@ -15145,13 +15151,13 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="B531" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C531" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D531" s="1">
-        <x:v>14446984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E531" s="1">
         <x:v>0</x:v>
@@ -15160,7 +15166,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G531" s="1">
-        <x:v>14446984</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="532" spans="1:7">
@@ -15168,22 +15174,22 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C532" s="1">
-        <x:v>50</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D532" s="1">
-        <x:v>0</x:v>
+        <x:v>2997852</x:v>
       </x:c>
       <x:c r="E532" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F532" s="1">
-        <x:v>0</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G532" s="1">
-        <x:v>50</x:v>
+        <x:v>3012652</x:v>
       </x:c>
     </x:row>
     <x:row r="533" spans="1:7">
@@ -15191,22 +15197,22 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C533" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D533" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E533" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F533" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G533" s="1">
-        <x:v>3550</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="534" spans="1:7">
@@ -15214,10 +15220,10 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="B534" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C534" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D534" s="1">
         <x:v>0</x:v>
@@ -15226,10 +15232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F534" s="1">
-        <x:v>22334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G534" s="1">
-        <x:v>22334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="535" spans="1:7">
@@ -15237,10 +15243,10 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C535" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D535" s="1">
         <x:v>0</x:v>
@@ -15249,10 +15255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F535" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G535" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="536" spans="1:7">
@@ -15260,7 +15266,7 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C536" s="1">
         <x:v>0</x:v>
@@ -15272,10 +15278,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F536" s="1">
-        <x:v>500</x:v>
+        <x:v>22334</x:v>
       </x:c>
       <x:c r="G536" s="1">
-        <x:v>500</x:v>
+        <x:v>22334</x:v>
       </x:c>
     </x:row>
     <x:row r="537" spans="1:7">
@@ -15283,7 +15289,7 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C537" s="1">
         <x:v>50</x:v>
@@ -15306,22 +15312,22 @@
         <x:v>594</x:v>
       </x:c>
       <x:c r="B538" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C538" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D538" s="1">
-        <x:v>209387</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E538" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F538" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G538" s="1">
-        <x:v>209387</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="539" spans="1:7">
@@ -15329,7 +15335,7 @@
         <x:v>595</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C539" s="1">
         <x:v>50</x:v>
@@ -15352,13 +15358,13 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C540" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D540" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="E540" s="1">
         <x:v>0</x:v>
@@ -15367,7 +15373,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -15375,22 +15381,22 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C541" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D541" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E541" s="1">
-        <x:v>40428834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F541" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -15398,22 +15404,22 @@
         <x:v>598</x:v>
       </x:c>
       <x:c r="B542" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C542" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D542" s="1">
-        <x:v>0</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="E542" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F542" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G542" s="1">
-        <x:v>3300</x:v>
+        <x:v>257695</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:7">
@@ -15421,22 +15427,22 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C543" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D543" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E543" s="1">
-        <x:v>0</x:v>
+        <x:v>40428834</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>29800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>34800</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15444,10 +15450,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C544" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D544" s="1">
         <x:v>0</x:v>
@@ -15456,10 +15462,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>50</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -15467,10 +15473,10 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="B545" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C545" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D545" s="1">
         <x:v>0</x:v>
@@ -15479,10 +15485,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F545" s="1">
-        <x:v>5600</x:v>
+        <x:v>29800</x:v>
       </x:c>
       <x:c r="G545" s="1">
-        <x:v>5650</x:v>
+        <x:v>34800</x:v>
       </x:c>
     </x:row>
     <x:row r="546" spans="1:7">
@@ -15490,13 +15496,13 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C546" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D546" s="1">
-        <x:v>149384</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E546" s="1">
         <x:v>0</x:v>
@@ -15505,7 +15511,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G546" s="1">
-        <x:v>151434</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:7">
@@ -15513,7 +15519,7 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C547" s="1">
         <x:v>50</x:v>
@@ -15525,10 +15531,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F547" s="1">
-        <x:v>6834</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G547" s="1">
-        <x:v>6884</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="548" spans="1:7">
@@ -15536,13 +15542,13 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C548" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D548" s="1">
-        <x:v>0</x:v>
+        <x:v>149384</x:v>
       </x:c>
       <x:c r="E548" s="1">
         <x:v>0</x:v>
@@ -15551,7 +15557,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G548" s="1">
-        <x:v>50</x:v>
+        <x:v>151434</x:v>
       </x:c>
     </x:row>
     <x:row r="549" spans="1:7">
@@ -15559,22 +15565,22 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C549" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D549" s="1">
-        <x:v>558813</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E549" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F549" s="1">
-        <x:v>1000</x:v>
+        <x:v>6834</x:v>
       </x:c>
       <x:c r="G549" s="1">
-        <x:v>559813</x:v>
+        <x:v>6884</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:7">
@@ -15582,7 +15588,7 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C550" s="1">
         <x:v>50</x:v>
@@ -15594,10 +15600,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F550" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G550" s="1">
-        <x:v>6650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="551" spans="1:7">
@@ -15605,22 +15611,22 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C551" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D551" s="1">
-        <x:v>8746764</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E551" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F551" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>8746764</x:v>
+        <x:v>559813</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -15628,7 +15634,7 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C552" s="1">
         <x:v>50</x:v>
@@ -15640,10 +15646,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F552" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G552" s="1">
-        <x:v>50</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="553" spans="1:7">
@@ -15651,22 +15657,22 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B553" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C553" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D553" s="1">
-        <x:v>0</x:v>
+        <x:v>8746764</x:v>
       </x:c>
       <x:c r="E553" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F553" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G553" s="1">
-        <x:v>0</x:v>
+        <x:v>8746764</x:v>
       </x:c>
     </x:row>
     <x:row r="554" spans="1:7">
@@ -15674,7 +15680,7 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C554" s="1">
         <x:v>50</x:v>
@@ -15686,10 +15692,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F554" s="1">
-        <x:v>1089100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G554" s="1">
-        <x:v>1089150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="555" spans="1:7">
@@ -15697,22 +15703,22 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C555" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D555" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E555" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F555" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G555" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="556" spans="1:7">
@@ -15720,7 +15726,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>50</x:v>
@@ -15732,10 +15738,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>0</x:v>
+        <x:v>1089100</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>50</x:v>
+        <x:v>1089150</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -15743,22 +15749,22 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C557" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D557" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E557" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F557" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G557" s="1">
-        <x:v>3550</x:v>
+        <x:v>1927706</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:7">
@@ -15766,7 +15772,7 @@
         <x:v>614</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C558" s="1">
         <x:v>50</x:v>
@@ -15789,10 +15795,10 @@
         <x:v>615</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C559" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D559" s="1">
         <x:v>0</x:v>
@@ -15801,10 +15807,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>1000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>1000</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -15812,7 +15818,7 @@
         <x:v>616</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>50</x:v>
@@ -15835,10 +15841,10 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C561" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D561" s="1">
         <x:v>0</x:v>
@@ -15847,10 +15853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F561" s="1">
-        <x:v>10000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G561" s="1">
-        <x:v>10050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:7">
@@ -15858,22 +15864,22 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B562" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C562" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D562" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E562" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F562" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G562" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="563" spans="1:7">
@@ -15881,7 +15887,7 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="B563" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C563" s="1">
         <x:v>50</x:v>
@@ -15893,10 +15899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F563" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G563" s="1">
-        <x:v>50</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="564" spans="1:7">
@@ -15904,22 +15910,22 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C564" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D564" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E564" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F564" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G564" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:7">
@@ -15927,22 +15933,22 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C565" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D565" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E565" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>14866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>117122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -15950,13 +15956,13 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C566" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D566" s="1">
-        <x:v>150000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E566" s="1">
         <x:v>0</x:v>
@@ -15965,7 +15971,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>150000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -15973,22 +15979,22 @@
         <x:v>623</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C567" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D567" s="1">
-        <x:v>0</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E567" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F567" s="1">
-        <x:v>0</x:v>
+        <x:v>14866</x:v>
       </x:c>
       <x:c r="G567" s="1">
-        <x:v>50</x:v>
+        <x:v>117122</x:v>
       </x:c>
     </x:row>
     <x:row r="568" spans="1:7">
@@ -15996,13 +16002,13 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B568" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C568" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D568" s="1">
-        <x:v>0</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="E568" s="1">
         <x:v>0</x:v>
@@ -16011,7 +16017,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G568" s="1">
-        <x:v>50</x:v>
+        <x:v>150000</x:v>
       </x:c>
     </x:row>
     <x:row r="569" spans="1:7">
@@ -16019,7 +16025,7 @@
         <x:v>625</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>626</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>50</x:v>
@@ -16039,10 +16045,10 @@
     </x:row>
     <x:row r="570" spans="1:7">
       <x:c r="A570" s="1" t="s">
-        <x:v>627</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>50</x:v>
@@ -16062,13 +16068,13 @@
     </x:row>
     <x:row r="571" spans="1:7">
       <x:c r="A571" s="1" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="B571" s="1" t="s">
         <x:v>628</x:v>
       </x:c>
-      <x:c r="B571" s="1" t="s">
-        <x:v>185</x:v>
-      </x:c>
       <x:c r="C571" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D571" s="1">
         <x:v>0</x:v>
@@ -16077,10 +16083,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F571" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G571" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:7">
@@ -16088,10 +16094,10 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B572" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C572" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D572" s="1">
         <x:v>0</x:v>
@@ -16100,10 +16106,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F572" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>6000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -16111,22 +16117,22 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C573" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D573" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E573" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F573" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G573" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:7">
@@ -16134,10 +16140,10 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C574" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D574" s="1">
         <x:v>0</x:v>
@@ -16146,10 +16152,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F574" s="1">
-        <x:v>250</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G574" s="1">
-        <x:v>300</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:7">
@@ -16157,7 +16163,7 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C575" s="1">
         <x:v>50</x:v>
@@ -16166,7 +16172,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E575" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F575" s="1">
         <x:v>0</x:v>
@@ -16180,10 +16186,10 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C576" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D576" s="1">
         <x:v>0</x:v>
@@ -16192,10 +16198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F576" s="1">
-        <x:v>1500</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G576" s="1">
-        <x:v>2500</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="577" spans="1:7">
@@ -16203,7 +16209,7 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C577" s="1">
         <x:v>50</x:v>
@@ -16226,10 +16232,10 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C578" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D578" s="1">
         <x:v>0</x:v>
@@ -16238,10 +16244,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F578" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G578" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="579" spans="1:7">
@@ -16249,7 +16255,7 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C579" s="1">
         <x:v>50</x:v>
@@ -16272,10 +16278,10 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C580" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D580" s="1">
         <x:v>0</x:v>
@@ -16284,10 +16290,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F580" s="1">
-        <x:v>-19405</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G580" s="1">
-        <x:v>-19405</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="581" spans="1:7">
@@ -16295,13 +16301,13 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C581" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D581" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E581" s="1">
         <x:v>0</x:v>
@@ -16310,7 +16316,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G581" s="1">
-        <x:v>1491280</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="582" spans="1:7">
@@ -16318,7 +16324,7 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C582" s="1">
         <x:v>0</x:v>
@@ -16330,10 +16336,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F582" s="1">
-        <x:v>500</x:v>
+        <x:v>-19405</x:v>
       </x:c>
       <x:c r="G582" s="1">
-        <x:v>500</x:v>
+        <x:v>-19405</x:v>
       </x:c>
     </x:row>
     <x:row r="583" spans="1:7">
@@ -16341,13 +16347,13 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C583" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D583" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E583" s="1">
         <x:v>0</x:v>
@@ -16356,7 +16362,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G583" s="1">
-        <x:v>50</x:v>
+        <x:v>1491280</x:v>
       </x:c>
     </x:row>
     <x:row r="584" spans="1:7">
@@ -16364,10 +16370,10 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C584" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D584" s="1">
         <x:v>0</x:v>
@@ -16376,10 +16382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F584" s="1">
-        <x:v>250</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>300</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -16387,7 +16393,7 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C585" s="1">
         <x:v>50</x:v>
@@ -16410,7 +16416,7 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>50</x:v>
@@ -16422,10 +16428,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>1287</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>1337</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -16433,10 +16439,10 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C587" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D587" s="1">
         <x:v>0</x:v>
@@ -16445,10 +16451,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F587" s="1">
-        <x:v>6697</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G587" s="1">
-        <x:v>6697</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="588" spans="1:7">
@@ -16456,22 +16462,22 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C588" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D588" s="1">
-        <x:v>151688</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E588" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F588" s="1">
-        <x:v>0</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>151738</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -16479,7 +16485,7 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>0</x:v>
@@ -16491,10 +16497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F589" s="1">
-        <x:v>4000</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>4000</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">
@@ -16502,22 +16508,22 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C590" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D590" s="1">
-        <x:v>0</x:v>
+        <x:v>151688</x:v>
       </x:c>
       <x:c r="E590" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F590" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G590" s="1">
-        <x:v>6500</x:v>
+        <x:v>151738</x:v>
       </x:c>
     </x:row>
     <x:row r="591" spans="1:7">
@@ -16528,7 +16534,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C591" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D591" s="1">
         <x:v>0</x:v>
@@ -16537,10 +16543,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F591" s="1">
-        <x:v>0</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G591" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="592" spans="1:7">
@@ -16548,10 +16554,10 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C592" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D592" s="1">
         <x:v>0</x:v>
@@ -16560,10 +16566,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F592" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G592" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="593" spans="1:7">
@@ -16571,7 +16577,7 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C593" s="1">
         <x:v>50</x:v>
@@ -16594,22 +16600,22 @@
         <x:v>651</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C594" s="1">
-        <x:v>7500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D594" s="1">
-        <x:v>1400000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E594" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F594" s="1">
-        <x:v>10500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G594" s="1">
-        <x:v>1418000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="595" spans="1:7">
@@ -16617,7 +16623,7 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C595" s="1">
         <x:v>50</x:v>
@@ -16640,22 +16646,22 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C596" s="1">
-        <x:v>0</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D596" s="1">
-        <x:v>0</x:v>
+        <x:v>1400000</x:v>
       </x:c>
       <x:c r="E596" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F596" s="1">
-        <x:v>1500</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G596" s="1">
-        <x:v>1500</x:v>
+        <x:v>1418000</x:v>
       </x:c>
     </x:row>
     <x:row r="597" spans="1:7">
@@ -16663,7 +16669,7 @@
         <x:v>654</x:v>
       </x:c>
       <x:c r="B597" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C597" s="1">
         <x:v>50</x:v>
@@ -16675,10 +16681,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F597" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G597" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="598" spans="1:7">
@@ -16686,10 +16692,10 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C598" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D598" s="1">
         <x:v>0</x:v>
@@ -16698,10 +16704,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F598" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G598" s="1">
-        <x:v>50</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="599" spans="1:7">
@@ -16709,7 +16715,7 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C599" s="1">
         <x:v>50</x:v>
@@ -16721,10 +16727,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F599" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G599" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:7">
@@ -16732,7 +16738,7 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C600" s="1">
         <x:v>50</x:v>
@@ -16755,7 +16761,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>50</x:v>
@@ -16778,7 +16784,7 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C602" s="1">
         <x:v>50</x:v>
@@ -16801,13 +16807,13 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C603" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D603" s="1">
-        <x:v>2707641</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E603" s="1">
         <x:v>0</x:v>
@@ -16816,7 +16822,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G603" s="1">
-        <x:v>2707641</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="604" spans="1:7">
@@ -16824,10 +16830,10 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C604" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D604" s="1">
         <x:v>0</x:v>
@@ -16836,10 +16842,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F604" s="1">
-        <x:v>81050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G604" s="1">
-        <x:v>81050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="605" spans="1:7">
@@ -16847,13 +16853,13 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D605" s="1">
-        <x:v>0</x:v>
+        <x:v>2707641</x:v>
       </x:c>
       <x:c r="E605" s="1">
         <x:v>0</x:v>
@@ -16862,7 +16868,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>50</x:v>
+        <x:v>2707641</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16870,10 +16876,10 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16882,10 +16888,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>0</x:v>
+        <x:v>81050</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>50</x:v>
+        <x:v>81050</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -16893,10 +16899,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C607" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D607" s="1">
         <x:v>0</x:v>
@@ -16908,7 +16914,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G607" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:7">
@@ -16916,7 +16922,7 @@
         <x:v>665</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C608" s="1">
         <x:v>50</x:v>
@@ -16939,10 +16945,10 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C609" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D609" s="1">
         <x:v>0</x:v>
@@ -16951,10 +16957,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F609" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G609" s="1">
-        <x:v>14050</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="610" spans="1:7">
@@ -16962,10 +16968,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C610" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D610" s="1">
         <x:v>0</x:v>
@@ -16974,10 +16980,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F610" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G610" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="611" spans="1:7">
@@ -16985,10 +16991,10 @@
         <x:v>668</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C611" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D611" s="1">
         <x:v>0</x:v>
@@ -16997,10 +17003,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F611" s="1">
-        <x:v>1000</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G611" s="1">
-        <x:v>1000</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="612" spans="1:7">
@@ -17008,59 +17014,59 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D612" s="1">
-        <x:v>14446984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E612" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F612" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G612" s="1">
-        <x:v>14446984</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="613" spans="1:7">
       <x:c r="A613" s="1" t="s">
-        <x:v>669</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C613" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D613" s="1">
-        <x:v>14446984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E613" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F613" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>14446984</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
       <x:c r="A614" s="1" t="s">
-        <x:v>670</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="B614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C614" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D614" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E614" s="1">
         <x:v>0</x:v>
@@ -17069,7 +17075,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G614" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:7">
@@ -17077,22 +17083,22 @@
         <x:v>671</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>17050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D615" s="1">
-        <x:v>2470488</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E615" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>11834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>2499372</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17100,13 +17106,13 @@
         <x:v>672</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D616" s="1">
-        <x:v>301208</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E616" s="1">
         <x:v>0</x:v>
@@ -17115,7 +17121,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>301308</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -17123,22 +17129,22 @@
         <x:v>673</x:v>
       </x:c>
       <x:c r="B617" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C617" s="1">
-        <x:v>50</x:v>
+        <x:v>17050</x:v>
       </x:c>
       <x:c r="D617" s="1">
-        <x:v>0</x:v>
+        <x:v>2470488</x:v>
       </x:c>
       <x:c r="E617" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F617" s="1">
-        <x:v>0</x:v>
+        <x:v>11834</x:v>
       </x:c>
       <x:c r="G617" s="1">
-        <x:v>50</x:v>
+        <x:v>2499372</x:v>
       </x:c>
     </x:row>
     <x:row r="618" spans="1:7">
@@ -17146,13 +17152,13 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B618" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C618" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D618" s="1">
-        <x:v>0</x:v>
+        <x:v>301208</x:v>
       </x:c>
       <x:c r="E618" s="1">
         <x:v>0</x:v>
@@ -17161,7 +17167,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G618" s="1">
-        <x:v>50</x:v>
+        <x:v>301308</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:7">
@@ -17169,10 +17175,10 @@
         <x:v>675</x:v>
       </x:c>
       <x:c r="B619" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C619" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D619" s="1">
         <x:v>0</x:v>
@@ -17181,10 +17187,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F619" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G619" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="620" spans="1:7">
@@ -17192,7 +17198,7 @@
         <x:v>676</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C620" s="1">
         <x:v>50</x:v>
@@ -17204,10 +17210,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F620" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G620" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="621" spans="1:7">
@@ -17218,7 +17224,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C621" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D621" s="1">
         <x:v>0</x:v>
@@ -17227,10 +17233,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F621" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G621" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="622" spans="1:7">
@@ -17238,7 +17244,7 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C622" s="1">
         <x:v>50</x:v>
@@ -17250,10 +17256,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F622" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G622" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:7">
@@ -17261,7 +17267,7 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C623" s="1">
         <x:v>50</x:v>
@@ -17284,7 +17290,7 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C624" s="1">
         <x:v>50</x:v>
@@ -17307,22 +17313,22 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D625" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E625" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>6634</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>3982954</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17330,10 +17336,10 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17342,10 +17348,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>22000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>22000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17353,22 +17359,22 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D627" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E627" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>5800</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>5850</x:v>
+        <x:v>3982954</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17376,10 +17382,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>685</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C628" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D628" s="1">
         <x:v>0</x:v>
@@ -17388,21 +17394,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F628" s="1">
-        <x:v>0</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>50</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">
       <x:c r="A629" s="1" t="s">
-        <x:v>686</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C629" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D629" s="1">
         <x:v>0</x:v>
@@ -17411,18 +17417,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F629" s="1">
-        <x:v>5750</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G629" s="1">
-        <x:v>5750</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:7">
       <x:c r="A630" s="1" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="B630" s="1" t="s">
         <x:v>687</x:v>
-      </x:c>
-      <x:c r="B630" s="1" t="s">
-        <x:v>688</x:v>
       </x:c>
       <x:c r="C630" s="1">
         <x:v>50</x:v>
@@ -17442,13 +17448,13 @@
     </x:row>
     <x:row r="631" spans="1:7">
       <x:c r="A631" s="1" t="s">
-        <x:v>689</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17457,21 +17463,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
       <x:c r="A632" s="1" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="B632" s="1" t="s">
         <x:v>690</x:v>
       </x:c>
-      <x:c r="B632" s="1" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="C632" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17480,18 +17486,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
       <x:c r="A633" s="1" t="s">
-        <x:v>690</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C633" s="1">
         <x:v>50</x:v>
@@ -17511,10 +17517,10 @@
     </x:row>
     <x:row r="634" spans="1:7">
       <x:c r="A634" s="1" t="s">
-        <x:v>691</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C634" s="1">
         <x:v>50</x:v>
@@ -17537,10 +17543,10 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C635" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D635" s="1">
         <x:v>0</x:v>
@@ -17549,10 +17555,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F635" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">
@@ -17560,10 +17566,10 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C636" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D636" s="1">
         <x:v>0</x:v>
@@ -17572,10 +17578,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F636" s="1">
-        <x:v>68600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G636" s="1">
-        <x:v>71150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="637" spans="1:7">
@@ -17583,7 +17589,7 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C637" s="1">
         <x:v>50</x:v>
@@ -17606,10 +17612,10 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B638" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C638" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D638" s="1">
         <x:v>0</x:v>
@@ -17618,10 +17624,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F638" s="1">
-        <x:v>0</x:v>
+        <x:v>68600</x:v>
       </x:c>
       <x:c r="G638" s="1">
-        <x:v>50</x:v>
+        <x:v>71150</x:v>
       </x:c>
     </x:row>
     <x:row r="639" spans="1:7">
@@ -17629,10 +17635,10 @@
         <x:v>696</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C639" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D639" s="1">
         <x:v>0</x:v>
@@ -17641,10 +17647,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F639" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17652,7 +17658,7 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C640" s="1">
         <x:v>50</x:v>
@@ -17664,10 +17670,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F640" s="1">
-        <x:v>58000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>58050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">
@@ -17675,10 +17681,10 @@
         <x:v>698</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C641" s="1">
-        <x:v>2050</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D641" s="1">
         <x:v>0</x:v>
@@ -17687,10 +17693,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F641" s="1">
-        <x:v>1666</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G641" s="1">
-        <x:v>3716</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="642" spans="1:7">
@@ -17698,68 +17704,68 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C642" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D642" s="1">
-        <x:v>148764</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E642" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F642" s="1">
-        <x:v>11668</x:v>
+        <x:v>58000</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>160432</x:v>
+        <x:v>58050</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
       <x:c r="A643" s="1" t="s">
-        <x:v>699</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C643" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D643" s="1">
-        <x:v>148764</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E643" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F643" s="1">
-        <x:v>0</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="G643" s="1">
-        <x:v>148764</x:v>
+        <x:v>3716</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:7">
       <x:c r="A644" s="1" t="s">
-        <x:v>700</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>0</x:v>
+        <x:v>148764</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>0</x:v>
+        <x:v>11668</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>50</x:v>
+        <x:v>160432</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17767,13 +17773,13 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>105040</x:v>
+        <x:v>148764</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
@@ -17782,7 +17788,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>105090</x:v>
+        <x:v>148764</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17790,10 +17796,10 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D646" s="1">
         <x:v>0</x:v>
@@ -17802,10 +17808,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
-        <x:v>30600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>33550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -17813,13 +17819,13 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B647" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C647" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D647" s="1">
-        <x:v>0</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="E647" s="1">
         <x:v>0</x:v>
@@ -17828,7 +17834,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G647" s="1">
-        <x:v>2550</x:v>
+        <x:v>105090</x:v>
       </x:c>
     </x:row>
     <x:row r="648" spans="1:7">
@@ -17836,22 +17842,22 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="B648" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C648" s="1">
-        <x:v>50</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D648" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E648" s="1">
-        <x:v>56045</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F648" s="1">
-        <x:v>0</x:v>
+        <x:v>30600</x:v>
       </x:c>
       <x:c r="G648" s="1">
-        <x:v>50</x:v>
+        <x:v>33550</x:v>
       </x:c>
     </x:row>
     <x:row r="649" spans="1:7">
@@ -17859,13 +17865,13 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C649" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D649" s="1">
-        <x:v>301124</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E649" s="1">
         <x:v>0</x:v>
@@ -17874,7 +17880,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>301174</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -17882,22 +17888,22 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C650" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D650" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E650" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F650" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
@@ -17905,13 +17911,13 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C651" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D651" s="1">
-        <x:v>0</x:v>
+        <x:v>301124</x:v>
       </x:c>
       <x:c r="E651" s="1">
         <x:v>0</x:v>
@@ -17920,7 +17926,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>50</x:v>
+        <x:v>301174</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
@@ -17928,10 +17934,10 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>4550</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D652" s="1">
         <x:v>0</x:v>
@@ -17940,24 +17946,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F652" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>5050</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
       <x:c r="A653" s="1" t="s">
-        <x:v>708</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D653" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E653" s="1">
         <x:v>0</x:v>
@@ -17966,30 +17972,30 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>1100000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
       <x:c r="A654" s="1" t="s">
-        <x:v>709</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C654" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D654" s="1">
-        <x:v>852561</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E654" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F654" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G654" s="1">
-        <x:v>852561</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:7">
@@ -17997,13 +18003,13 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C655" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D655" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E655" s="1">
         <x:v>0</x:v>
@@ -18012,7 +18018,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G655" s="1">
-        <x:v>50</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:7">
@@ -18020,13 +18026,13 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C656" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>0</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
@@ -18035,7 +18041,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>50</x:v>
+        <x:v>852561</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -18043,13 +18049,13 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C657" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D657" s="1">
-        <x:v>2200000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E657" s="1">
         <x:v>0</x:v>
@@ -18058,7 +18064,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>2200000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">
@@ -18066,13 +18072,13 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C658" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D658" s="1">
-        <x:v>149704</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E658" s="1">
         <x:v>0</x:v>
@@ -18081,7 +18087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>149754</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
@@ -18089,13 +18095,13 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C659" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D659" s="1">
-        <x:v>0</x:v>
+        <x:v>2200000</x:v>
       </x:c>
       <x:c r="E659" s="1">
         <x:v>0</x:v>
@@ -18104,7 +18110,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>50</x:v>
+        <x:v>2200000</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
@@ -18112,13 +18118,13 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C660" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D660" s="1">
-        <x:v>0</x:v>
+        <x:v>149704</x:v>
       </x:c>
       <x:c r="E660" s="1">
         <x:v>0</x:v>
@@ -18127,7 +18133,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>50</x:v>
+        <x:v>149754</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18135,10 +18141,10 @@
         <x:v>716</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
         <x:v>0</x:v>
@@ -18150,7 +18156,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18158,7 +18164,7 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C662" s="1">
         <x:v>50</x:v>
@@ -18181,10 +18187,10 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C663" s="1">
-        <x:v>10050</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D663" s="1">
         <x:v>0</x:v>
@@ -18196,7 +18202,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>10050</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
@@ -18204,10 +18210,10 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C664" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D664" s="1">
         <x:v>0</x:v>
@@ -18216,10 +18222,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F664" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G664" s="1">
-        <x:v>2717</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:7">
@@ -18227,10 +18233,10 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C665" s="1">
-        <x:v>50</x:v>
+        <x:v>10050</x:v>
       </x:c>
       <x:c r="D665" s="1">
         <x:v>0</x:v>
@@ -18242,7 +18248,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G665" s="1">
-        <x:v>50</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:7">
@@ -18250,22 +18256,22 @@
         <x:v>721</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C666" s="1">
-        <x:v>0</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D666" s="1">
-        <x:v>111599</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E666" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F666" s="1">
-        <x:v>3300</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G666" s="1">
-        <x:v>114899</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:7">
@@ -18273,7 +18279,7 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C667" s="1">
         <x:v>50</x:v>
@@ -18296,36 +18302,36 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D668" s="1">
-        <x:v>0</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="E668" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F668" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>50</x:v>
+        <x:v>114899</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
       <x:c r="A669" s="1" t="s">
-        <x:v>723</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C669" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D669" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E669" s="1">
         <x:v>0</x:v>
@@ -18334,15 +18340,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
       <x:c r="A670" s="1" t="s">
-        <x:v>724</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C670" s="1">
         <x:v>50</x:v>
@@ -18365,22 +18371,22 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C671" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D671" s="1">
-        <x:v>10046680</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E671" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F671" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>10048730</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
@@ -18388,13 +18394,13 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="B672" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C672" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D672" s="1">
-        <x:v>2263800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E672" s="1">
         <x:v>0</x:v>
@@ -18403,7 +18409,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G672" s="1">
-        <x:v>2263850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="673" spans="1:7">
@@ -18411,22 +18417,22 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C673" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D673" s="1">
-        <x:v>0</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E673" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F673" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G673" s="1">
-        <x:v>50</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:7">
@@ -18434,22 +18440,22 @@
         <x:v>728</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C674" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D674" s="1">
-        <x:v>0</x:v>
+        <x:v>2263800</x:v>
       </x:c>
       <x:c r="E674" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F674" s="1">
-        <x:v>19500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G674" s="1">
-        <x:v>19550</x:v>
+        <x:v>2263850</x:v>
       </x:c>
     </x:row>
     <x:row r="675" spans="1:7">
@@ -18457,22 +18463,22 @@
         <x:v>729</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C675" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D675" s="1">
-        <x:v>302468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E675" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F675" s="1">
-        <x:v>55833</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>364351</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
@@ -18480,7 +18486,7 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C676" s="1">
         <x:v>50</x:v>
@@ -18492,10 +18498,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F676" s="1">
-        <x:v>0</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="G676" s="1">
-        <x:v>50</x:v>
+        <x:v>19550</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:7">
@@ -18503,22 +18509,22 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C677" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D677" s="1">
-        <x:v>0</x:v>
+        <x:v>302468</x:v>
       </x:c>
       <x:c r="E677" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F677" s="1">
-        <x:v>0</x:v>
+        <x:v>55833</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>50</x:v>
+        <x:v>364351</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -18526,10 +18532,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C678" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D678" s="1">
         <x:v>0</x:v>
@@ -18538,10 +18544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F678" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G678" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:7">
@@ -18549,13 +18555,13 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C679" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D679" s="1">
-        <x:v>380377</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E679" s="1">
         <x:v>0</x:v>
@@ -18564,7 +18570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>380377</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18572,22 +18578,22 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D680" s="1">
-        <x:v>817169</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E680" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>1668</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>820837</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -18595,22 +18601,22 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>11050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D681" s="1">
-        <x:v>0</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="E681" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>6242</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>17292</x:v>
+        <x:v>380377</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -18618,22 +18624,22 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D682" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E682" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>0</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>50</x:v>
+        <x:v>820837</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -18644,7 +18650,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -18653,10 +18659,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>0</x:v>
+        <x:v>6242</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>50</x:v>
+        <x:v>17292</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -18664,10 +18670,10 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D684" s="1">
         <x:v>0</x:v>
@@ -18676,10 +18682,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -18687,7 +18693,7 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C685" s="1">
         <x:v>50</x:v>
@@ -18699,10 +18705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>25050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -18710,10 +18716,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -18722,64 +18728,64 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
       <x:c r="A687" s="1" t="s">
-        <x:v>740</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D687" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E687" s="1">
-        <x:v>23935803</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F687" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>0</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
       <x:c r="A688" s="1" t="s">
-        <x:v>740</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E688" s="1">
-        <x:v>23935803</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
       <x:c r="A689" s="1" t="s">
-        <x:v>741</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C689" s="1">
         <x:v>0</x:v>
@@ -18788,7 +18794,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E689" s="1">
-        <x:v>1531015</x:v>
+        <x:v>23935803</x:v>
       </x:c>
       <x:c r="F689" s="1">
         <x:v>0</x:v>
@@ -18802,22 +18808,22 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D690" s="1">
-        <x:v>157560</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E690" s="1">
-        <x:v>0</x:v>
+        <x:v>23935803</x:v>
       </x:c>
       <x:c r="F690" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>157610</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -18825,22 +18831,22 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E691" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F691" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -18848,13 +18854,13 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D692" s="1">
-        <x:v>5583432</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="E692" s="1">
         <x:v>0</x:v>
@@ -18863,7 +18869,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>5584432</x:v>
+        <x:v>157610</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -18871,7 +18877,7 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C693" s="1">
         <x:v>50</x:v>
@@ -18894,22 +18900,22 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C694" s="1">
-        <x:v>33050</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D694" s="1">
-        <x:v>1789991</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E694" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F694" s="1">
-        <x:v>20501</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>1843542</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -18917,10 +18923,10 @@
         <x:v>747</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C695" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D695" s="1">
         <x:v>0</x:v>
@@ -18929,10 +18935,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F695" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
@@ -18940,22 +18946,22 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>0</x:v>
+        <x:v>33050</x:v>
       </x:c>
       <x:c r="D696" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1789991</x:v>
       </x:c>
       <x:c r="E696" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>0</x:v>
+        <x:v>20501</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1843542</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18963,10 +18969,10 @@
         <x:v>749</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D697" s="1">
         <x:v>0</x:v>
@@ -18975,10 +18981,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>14500</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>14550</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
@@ -18986,13 +18992,13 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C698" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D698" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E698" s="1">
         <x:v>0</x:v>
@@ -19001,7 +19007,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>50</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
@@ -19009,7 +19015,7 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C699" s="1">
         <x:v>50</x:v>
@@ -19021,10 +19027,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F699" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
@@ -19032,13 +19038,13 @@
         <x:v>752</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C700" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D700" s="1">
-        <x:v>2150512</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E700" s="1">
         <x:v>0</x:v>
@@ -19047,7 +19053,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>2150562</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -19055,22 +19061,22 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D701" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E701" s="1">
-        <x:v>10135449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
@@ -19078,22 +19084,22 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C702" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>103020</x:v>
+        <x:v>2150512</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>106354</x:v>
+        <x:v>2150562</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -19101,59 +19107,59 @@
         <x:v>755</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C703" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D703" s="1">
-        <x:v>150562</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E703" s="1">
-        <x:v>0</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="F703" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>150562</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
       <x:c r="A704" s="1" t="s">
-        <x:v>755</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C704" s="1">
-        <x:v>7500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D704" s="1">
-        <x:v>0</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="E704" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>7500</x:v>
+        <x:v>106354</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
       <x:c r="A705" s="1" t="s">
-        <x:v>756</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C705" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>257611</x:v>
+        <x:v>150562</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
@@ -19162,7 +19168,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>257611</x:v>
+        <x:v>150562</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19170,10 +19176,10 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>2050</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D706" s="1">
         <x:v>0</x:v>
@@ -19182,10 +19188,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>27050</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -19193,22 +19199,22 @@
         <x:v>758</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>1050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D707" s="1">
-        <x:v>902176</x:v>
+        <x:v>257611</x:v>
       </x:c>
       <x:c r="E707" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>910226</x:v>
+        <x:v>257611</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
@@ -19216,10 +19222,10 @@
         <x:v>759</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D708" s="1">
         <x:v>0</x:v>
@@ -19228,10 +19234,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>25500</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>25550</x:v>
+        <x:v>27050</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -19239,22 +19245,22 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D709" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E709" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>50</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -19262,22 +19268,22 @@
         <x:v>761</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C710" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D710" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E710" s="1">
-        <x:v>392890</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>14000</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>14000</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
@@ -19285,10 +19291,10 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C711" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D711" s="1">
         <x:v>0</x:v>
@@ -19297,10 +19303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>6200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
@@ -19311,19 +19317,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E712" s="1">
-        <x:v>0</x:v>
+        <x:v>392890</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19331,10 +19337,10 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19343,10 +19349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>1000</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19354,7 +19360,7 @@
         <x:v>765</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C714" s="1">
         <x:v>50</x:v>
@@ -19366,10 +19372,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>6650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19377,13 +19383,13 @@
         <x:v>766</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>2771797</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
@@ -19392,7 +19398,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>2771797</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
@@ -19400,10 +19406,10 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D716" s="1">
         <x:v>0</x:v>
@@ -19412,10 +19418,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>5000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>5000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19423,13 +19429,13 @@
         <x:v>768</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D717" s="1">
-        <x:v>0</x:v>
+        <x:v>2771797</x:v>
       </x:c>
       <x:c r="E717" s="1">
         <x:v>0</x:v>
@@ -19438,7 +19444,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>50</x:v>
+        <x:v>2771797</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
@@ -19446,22 +19452,22 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C718" s="1">
-        <x:v>6550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D718" s="1">
-        <x:v>147346</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E718" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F718" s="1">
-        <x:v>3300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>157196</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
@@ -19469,7 +19475,7 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C719" s="1">
         <x:v>50</x:v>
@@ -19492,22 +19498,22 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D720" s="1">
-        <x:v>0</x:v>
+        <x:v>147346</x:v>
       </x:c>
       <x:c r="E720" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>50</x:v>
+        <x:v>157196</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
@@ -19515,10 +19521,10 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D721" s="1">
         <x:v>0</x:v>
@@ -19527,10 +19533,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F721" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
@@ -19538,10 +19544,10 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D722" s="1">
         <x:v>0</x:v>
@@ -19550,10 +19556,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F722" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
@@ -19561,10 +19567,10 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D723" s="1">
         <x:v>0</x:v>
@@ -19573,10 +19579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F723" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>50</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
@@ -19584,10 +19590,10 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D724" s="1">
         <x:v>0</x:v>
@@ -19596,24 +19602,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>5800</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>9350</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
       <x:c r="A725" s="1" t="s">
-        <x:v>775</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D725" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E725" s="1">
         <x:v>0</x:v>
@@ -19622,30 +19628,30 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>1100000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
       <x:c r="A726" s="1" t="s">
-        <x:v>776</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D726" s="1">
-        <x:v>2835078</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E726" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>5500</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>2840628</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
@@ -19653,13 +19659,13 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D727" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E727" s="1">
         <x:v>0</x:v>
@@ -19668,7 +19674,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>50</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
@@ -19676,22 +19682,22 @@
         <x:v>778</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C728" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D728" s="1">
-        <x:v>0</x:v>
+        <x:v>2835078</x:v>
       </x:c>
       <x:c r="E728" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>5750</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>5800</x:v>
+        <x:v>2840628</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
@@ -19699,7 +19705,7 @@
         <x:v>779</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C729" s="1">
         <x:v>50</x:v>
@@ -19722,10 +19728,10 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C730" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D730" s="1">
         <x:v>0</x:v>
@@ -19734,10 +19740,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F730" s="1">
-        <x:v>3300</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>3300</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
@@ -19745,7 +19751,7 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C731" s="1">
         <x:v>50</x:v>
@@ -19768,10 +19774,10 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C732" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D732" s="1">
         <x:v>0</x:v>
@@ -19780,10 +19786,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F732" s="1">
-        <x:v>5700</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>5750</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
@@ -19791,7 +19797,7 @@
         <x:v>783</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C733" s="1">
         <x:v>50</x:v>
@@ -19814,7 +19820,7 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C734" s="1">
         <x:v>50</x:v>
@@ -19826,10 +19832,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F734" s="1">
-        <x:v>0</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
@@ -19837,22 +19843,22 @@
         <x:v>785</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D735" s="1">
-        <x:v>2192272</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E735" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>2209772</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19860,10 +19866,10 @@
         <x:v>786</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19872,10 +19878,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
@@ -19883,22 +19889,22 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C737" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D737" s="1">
-        <x:v>0</x:v>
+        <x:v>2192272</x:v>
       </x:c>
       <x:c r="E737" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F737" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G737" s="1">
-        <x:v>50</x:v>
+        <x:v>2209772</x:v>
       </x:c>
     </x:row>
     <x:row r="738" spans="1:7">
@@ -19906,22 +19912,22 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D738" s="1">
-        <x:v>1015758</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E738" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F738" s="1">
-        <x:v>11500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>1029258</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
@@ -19929,7 +19935,7 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C739" s="1">
         <x:v>50</x:v>
@@ -19952,22 +19958,22 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D740" s="1">
-        <x:v>40000</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="E740" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F740" s="1">
-        <x:v>0</x:v>
+        <x:v>11500</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>40000</x:v>
+        <x:v>1029258</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
@@ -19975,10 +19981,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C741" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D741" s="1">
         <x:v>0</x:v>
@@ -19990,7 +19996,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
@@ -19998,22 +20004,22 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C742" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D742" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E742" s="1">
-        <x:v>474362</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F742" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
@@ -20021,10 +20027,10 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C743" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D743" s="1">
         <x:v>0</x:v>
@@ -20036,7 +20042,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G743" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="744" spans="1:7">
@@ -20044,7 +20050,7 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C744" s="1">
         <x:v>0</x:v>
@@ -20053,13 +20059,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E744" s="1">
-        <x:v>0</x:v>
+        <x:v>474362</x:v>
       </x:c>
       <x:c r="F744" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">
@@ -20067,7 +20073,7 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C745" s="1">
         <x:v>50</x:v>
@@ -20090,10 +20096,10 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D746" s="1">
         <x:v>0</x:v>
@@ -20102,10 +20108,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20113,7 +20119,7 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C747" s="1">
         <x:v>50</x:v>
@@ -20125,10 +20131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F747" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
@@ -20136,13 +20142,13 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D748" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E748" s="1">
         <x:v>0</x:v>
@@ -20151,7 +20157,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>3920589</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
@@ -20159,7 +20165,7 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C749" s="1">
         <x:v>50</x:v>
@@ -20171,10 +20177,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F749" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
@@ -20182,13 +20188,13 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D750" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E750" s="1">
         <x:v>0</x:v>
@@ -20197,7 +20203,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>1000</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
@@ -20205,7 +20211,7 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C751" s="1">
         <x:v>50</x:v>
@@ -20228,10 +20234,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20243,7 +20249,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20251,10 +20257,10 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20263,10 +20269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>9334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
@@ -20274,10 +20280,10 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C754" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D754" s="1">
         <x:v>0</x:v>
@@ -20289,7 +20295,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
@@ -20297,10 +20303,10 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>50</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20309,10 +20315,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>50</x:v>
+        <x:v>9334</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -20320,10 +20326,10 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D756" s="1">
         <x:v>0</x:v>
@@ -20335,7 +20341,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
@@ -20343,13 +20349,13 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E757" s="1">
         <x:v>0</x:v>
@@ -20358,7 +20364,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20366,7 +20372,7 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C758" s="1">
         <x:v>50</x:v>
@@ -20389,22 +20395,22 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C759" s="1">
-        <x:v>19600</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D759" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E759" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>36600</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
@@ -20412,13 +20418,13 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C760" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D760" s="1">
-        <x:v>535438</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E760" s="1">
         <x:v>0</x:v>
@@ -20427,7 +20433,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>535438</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
@@ -20435,10 +20441,10 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C761" s="1">
-        <x:v>50</x:v>
+        <x:v>19600</x:v>
       </x:c>
       <x:c r="D761" s="1">
         <x:v>0</x:v>
@@ -20447,10 +20453,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F761" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>50</x:v>
+        <x:v>36600</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
@@ -20458,13 +20464,13 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D762" s="1">
-        <x:v>0</x:v>
+        <x:v>535438</x:v>
       </x:c>
       <x:c r="E762" s="1">
         <x:v>0</x:v>
@@ -20473,7 +20479,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>50</x:v>
+        <x:v>535438</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
@@ -20481,7 +20487,7 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C763" s="1">
         <x:v>50</x:v>
@@ -20504,13 +20510,13 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C764" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D764" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E764" s="1">
         <x:v>0</x:v>
@@ -20519,7 +20525,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G764" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:7">
@@ -20527,7 +20533,7 @@
         <x:v>815</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C765" s="1">
         <x:v>50</x:v>
@@ -20550,22 +20556,22 @@
         <x:v>816</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C766" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D766" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E766" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>30000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
@@ -20573,7 +20579,7 @@
         <x:v>817</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C767" s="1">
         <x:v>50</x:v>
@@ -20596,22 +20602,22 @@
         <x:v>818</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C768" s="1">
-        <x:v>19050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D768" s="1">
-        <x:v>2700000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E768" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>2500</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>2721550</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
@@ -20619,10 +20625,10 @@
         <x:v>819</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C769" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D769" s="1">
         <x:v>0</x:v>
@@ -20634,7 +20640,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
@@ -20642,33 +20648,33 @@
         <x:v>820</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C770" s="1">
-        <x:v>50</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D770" s="1">
-        <x:v>0</x:v>
+        <x:v>2700000</x:v>
       </x:c>
       <x:c r="E770" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F770" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G770" s="1">
-        <x:v>50</x:v>
+        <x:v>2721550</x:v>
       </x:c>
     </x:row>
     <x:row r="771" spans="1:7">
       <x:c r="A771" s="1" t="s">
-        <x:v>820</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C771" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D771" s="1">
         <x:v>0</x:v>
@@ -20677,18 +20683,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F771" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G771" s="1">
-        <x:v>35</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="772" spans="1:7">
       <x:c r="A772" s="1" t="s">
-        <x:v>821</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C772" s="1">
         <x:v>50</x:v>
@@ -20711,10 +20717,10 @@
         <x:v>822</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C773" s="1">
-        <x:v>6450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D773" s="1">
         <x:v>0</x:v>
@@ -20723,10 +20729,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F773" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G773" s="1">
-        <x:v>6450</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="774" spans="1:7">
@@ -20734,7 +20740,7 @@
         <x:v>823</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C774" s="1">
         <x:v>50</x:v>
@@ -20757,10 +20763,10 @@
         <x:v>824</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C775" s="1">
-        <x:v>0</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D775" s="1">
         <x:v>0</x:v>
@@ -20769,10 +20775,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>1000</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
@@ -20780,7 +20786,7 @@
         <x:v>825</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C776" s="1">
         <x:v>50</x:v>
@@ -20792,10 +20798,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
@@ -20803,10 +20809,10 @@
         <x:v>826</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C777" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D777" s="1">
         <x:v>0</x:v>
@@ -20815,10 +20821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F777" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G777" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:7">
@@ -20826,10 +20832,10 @@
         <x:v>827</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C778" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D778" s="1">
         <x:v>0</x:v>
@@ -20838,10 +20844,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F778" s="1">
-        <x:v>13200</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>13200</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
@@ -20849,7 +20855,7 @@
         <x:v>828</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>50</x:v>
@@ -20872,10 +20878,10 @@
         <x:v>829</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C780" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D780" s="1">
         <x:v>0</x:v>
@@ -20884,10 +20890,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F780" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G780" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="781" spans="1:7">
@@ -20895,13 +20901,13 @@
         <x:v>830</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C781" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D781" s="1">
-        <x:v>1962970</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E781" s="1">
         <x:v>0</x:v>
@@ -20910,7 +20916,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>1963020</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
@@ -20918,7 +20924,7 @@
         <x:v>831</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C782" s="1">
         <x:v>50</x:v>
@@ -20941,22 +20947,22 @@
         <x:v>832</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C783" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D783" s="1">
-        <x:v>0</x:v>
+        <x:v>1962970</x:v>
       </x:c>
       <x:c r="E783" s="1">
-        <x:v>23935803</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F783" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G783" s="1">
-        <x:v>50</x:v>
+        <x:v>1963020</x:v>
       </x:c>
     </x:row>
     <x:row r="784" spans="1:7">
@@ -20964,22 +20970,22 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B784" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C784" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D784" s="1">
-        <x:v>487174</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E784" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F784" s="1">
-        <x:v>8500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G784" s="1">
-        <x:v>496674</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="785" spans="1:7">
@@ -20987,7 +20993,7 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="B785" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C785" s="1">
         <x:v>50</x:v>
@@ -20996,7 +21002,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E785" s="1">
-        <x:v>0</x:v>
+        <x:v>23935803</x:v>
       </x:c>
       <x:c r="F785" s="1">
         <x:v>0</x:v>
@@ -21010,22 +21016,22 @@
         <x:v>835</x:v>
       </x:c>
       <x:c r="B786" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C786" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D786" s="1">
-        <x:v>0</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="E786" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F786" s="1">
-        <x:v>4999</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G786" s="1">
-        <x:v>5049</x:v>
+        <x:v>496674</x:v>
       </x:c>
     </x:row>
     <x:row r="787" spans="1:7">
@@ -21033,10 +21039,10 @@
         <x:v>836</x:v>
       </x:c>
       <x:c r="B787" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C787" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D787" s="1">
         <x:v>0</x:v>
@@ -21045,10 +21051,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F787" s="1">
-        <x:v>16500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G787" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="788" spans="1:7">
@@ -21056,7 +21062,7 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B788" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C788" s="1">
         <x:v>50</x:v>
@@ -21068,10 +21074,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F788" s="1">
-        <x:v>0</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G788" s="1">
-        <x:v>50</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="789" spans="1:7">
@@ -21079,10 +21085,10 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="B789" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C789" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D789" s="1">
         <x:v>0</x:v>
@@ -21091,10 +21097,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F789" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G789" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="790" spans="1:7">
@@ -21102,7 +21108,7 @@
         <x:v>839</x:v>
       </x:c>
       <x:c r="B790" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C790" s="1">
         <x:v>50</x:v>
@@ -21125,7 +21131,7 @@
         <x:v>840</x:v>
       </x:c>
       <x:c r="B791" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C791" s="1">
         <x:v>50</x:v>
@@ -21137,10 +21143,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F791" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G791" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="792" spans="1:7">
@@ -21148,7 +21154,7 @@
         <x:v>841</x:v>
       </x:c>
       <x:c r="B792" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C792" s="1">
         <x:v>50</x:v>
@@ -21160,10 +21166,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F792" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G792" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="793" spans="1:7">
@@ -21171,7 +21177,7 @@
         <x:v>842</x:v>
       </x:c>
       <x:c r="B793" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C793" s="1">
         <x:v>50</x:v>
@@ -21183,10 +21189,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F793" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G793" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="794" spans="1:7">
@@ -21194,10 +21200,10 @@
         <x:v>843</x:v>
       </x:c>
       <x:c r="B794" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C794" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D794" s="1">
         <x:v>0</x:v>
@@ -21206,10 +21212,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F794" s="1">
-        <x:v>37300</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G794" s="1">
-        <x:v>48150</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="795" spans="1:7">
@@ -21217,10 +21223,10 @@
         <x:v>844</x:v>
       </x:c>
       <x:c r="B795" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C795" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D795" s="1">
         <x:v>0</x:v>
@@ -21229,10 +21235,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F795" s="1">
-        <x:v>83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G795" s="1">
-        <x:v>83</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="796" spans="1:7">
@@ -21240,33 +21246,33 @@
         <x:v>845</x:v>
       </x:c>
       <x:c r="B796" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C796" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D796" s="1">
-        <x:v>149704</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E796" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F796" s="1">
-        <x:v>0</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G796" s="1">
-        <x:v>149704</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="797" spans="1:7">
       <x:c r="A797" s="1" t="s">
-        <x:v>845</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="B797" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C797" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D797" s="1">
         <x:v>0</x:v>
@@ -21275,24 +21281,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F797" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G797" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="798" spans="1:7">
       <x:c r="A798" s="1" t="s">
-        <x:v>846</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="B798" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C798" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D798" s="1">
-        <x:v>0</x:v>
+        <x:v>149704</x:v>
       </x:c>
       <x:c r="E798" s="1">
         <x:v>0</x:v>
@@ -21301,7 +21307,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G798" s="1">
-        <x:v>50</x:v>
+        <x:v>149704</x:v>
       </x:c>
     </x:row>
     <x:row r="799" spans="1:7">
@@ -21309,7 +21315,7 @@
         <x:v>847</x:v>
       </x:c>
       <x:c r="B799" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C799" s="1">
         <x:v>50</x:v>
@@ -21332,10 +21338,10 @@
         <x:v>848</x:v>
       </x:c>
       <x:c r="B800" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C800" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D800" s="1">
         <x:v>0</x:v>
@@ -21344,10 +21350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F800" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G800" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="801" spans="1:7">
@@ -21355,21 +21361,67 @@
         <x:v>849</x:v>
       </x:c>
       <x:c r="B801" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C801" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D801" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E801" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F801" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G801" s="1">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="802" spans="1:7">
+      <x:c r="A802" s="1" t="s">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="B802" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C802" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D802" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E802" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F802" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G802" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="803" spans="1:7">
+      <x:c r="A803" s="1" t="s">
+        <x:v>851</x:v>
+      </x:c>
+      <x:c r="B803" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C801" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D801" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E801" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F801" s="1">
+      <x:c r="C803" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D803" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E803" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F803" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G801" s="1">
+      <x:c r="G803" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>
